--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122899836</v>
+        <v>122899356</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480517</v>
+        <v>480479</v>
       </c>
       <c r="R5" t="n">
-        <v>6790688</v>
+        <v>6790722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122899356</v>
+        <v>122899836</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480479</v>
+        <v>480517</v>
       </c>
       <c r="R6" t="n">
-        <v>6790722</v>
+        <v>6790688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122913871</v>
+        <v>122905949</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1980,17 +1980,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481264</v>
+        <v>480710</v>
       </c>
       <c r="R14" t="n">
-        <v>6790709</v>
+        <v>6790729</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,19 +2017,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,19 +2034,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122906825</v>
+        <v>122906898</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2092,14 +2082,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480638</v>
+        <v>480720</v>
       </c>
       <c r="R15" t="n">
-        <v>6790783</v>
+        <v>6790668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,19 +2119,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,19 +2136,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122907981</v>
+        <v>122906825</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2208,13 +2188,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480580</v>
+        <v>480638</v>
       </c>
       <c r="R16" t="n">
-        <v>6790754</v>
+        <v>6790783</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122907941</v>
+        <v>122907981</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2316,17 +2296,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480736</v>
+        <v>480580</v>
       </c>
       <c r="R17" t="n">
-        <v>6790589</v>
+        <v>6790754</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2353,9 +2333,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,19 +2360,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122905949</v>
+        <v>122907941</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2422,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480710</v>
+        <v>480736</v>
       </c>
       <c r="R18" t="n">
-        <v>6790729</v>
+        <v>6790589</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122910507</v>
+        <v>122908430</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2520,17 +2510,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480751</v>
+        <v>480722</v>
       </c>
       <c r="R19" t="n">
-        <v>6790806</v>
+        <v>6790508</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,19 +2547,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,22 +2564,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122911766</v>
+        <v>122908737</v>
       </c>
       <c r="B20" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481068</v>
+        <v>480772</v>
       </c>
       <c r="R20" t="n">
-        <v>6790734</v>
+        <v>6790501</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,19 +2649,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,19 +2666,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122913854</v>
+        <v>122916963</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2744,17 +2714,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481200</v>
+        <v>481367</v>
       </c>
       <c r="R21" t="n">
-        <v>6790675</v>
+        <v>6790497</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2781,19 +2751,14 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I området här återkommer garnlaven konstant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,19 +2773,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908737</v>
+        <v>122913871</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2860,13 +2825,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480772</v>
+        <v>481264</v>
       </c>
       <c r="R22" t="n">
-        <v>6790501</v>
+        <v>6790709</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2893,9 +2858,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,19 +2885,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122908430</v>
+        <v>122910737</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2962,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480722</v>
+        <v>480800</v>
       </c>
       <c r="R23" t="n">
-        <v>6790508</v>
+        <v>6790542</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122906898</v>
+        <v>122914493</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3060,17 +3035,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480720</v>
+        <v>481040</v>
       </c>
       <c r="R24" t="n">
-        <v>6790668</v>
+        <v>6790686</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3097,9 +3072,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3114,19 +3099,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122910737</v>
+        <v>122910507</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3162,17 +3147,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480800</v>
+        <v>480751</v>
       </c>
       <c r="R25" t="n">
-        <v>6790542</v>
+        <v>6790806</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3199,9 +3184,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,22 +3211,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122914493</v>
+        <v>122911766</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,13 +3263,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481040</v>
+        <v>481068</v>
       </c>
       <c r="R26" t="n">
-        <v>6790686</v>
+        <v>6790734</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3303,7 +3298,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3308,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,19 +3323,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122916963</v>
+        <v>122913854</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3376,17 +3371,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481367</v>
+        <v>481200</v>
       </c>
       <c r="R27" t="n">
-        <v>6790497</v>
+        <v>6790675</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3413,14 +3408,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I området här återkommer garnlaven konstant.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,12 +3435,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122908857</v>
+        <v>122910046</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480766</v>
+        <v>480725</v>
       </c>
       <c r="R30" t="n">
-        <v>6790505</v>
+        <v>6790756</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122915163</v>
+        <v>122914046</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3765,38 +3765,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480988</v>
+        <v>480839</v>
       </c>
       <c r="R31" t="n">
-        <v>6790673</v>
+        <v>6790677</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122908626</v>
+        <v>122908857</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3895,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480639</v>
+        <v>480766</v>
       </c>
       <c r="R32" t="n">
-        <v>6790797</v>
+        <v>6790505</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3928,19 +3933,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,22 +3950,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122915083</v>
+        <v>122910531</v>
       </c>
       <c r="B33" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,46 +3974,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480681</v>
+        <v>480772</v>
       </c>
       <c r="R33" t="n">
-        <v>6790816</v>
+        <v>6790619</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4048,19 +4035,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,19 +4052,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910046</v>
+        <v>122911922</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4123,17 +4100,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480725</v>
+        <v>481068</v>
       </c>
       <c r="R34" t="n">
-        <v>6790756</v>
+        <v>6790734</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4160,9 +4137,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4177,19 +4164,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910531</v>
+        <v>122915163</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4229,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480772</v>
+        <v>480988</v>
       </c>
       <c r="R35" t="n">
-        <v>6790619</v>
+        <v>6790673</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4291,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122911922</v>
+        <v>122908626</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4327,17 +4314,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481068</v>
+        <v>480639</v>
       </c>
       <c r="R36" t="n">
-        <v>6790734</v>
+        <v>6790797</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4366,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4376,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4391,19 +4378,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122914046</v>
+        <v>122915083</v>
       </c>
       <c r="B37" t="n">
         <v>56688</v>
@@ -4437,21 +4424,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480839</v>
+        <v>480681</v>
       </c>
       <c r="R37" t="n">
-        <v>6790677</v>
+        <v>6790816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4481,9 +4471,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4498,19 +4498,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908480</v>
+        <v>122907044</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480744</v>
+        <v>480733</v>
       </c>
       <c r="R38" t="n">
-        <v>6790521</v>
+        <v>6790651</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122905786</v>
+        <v>122913869</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4628,34 +4628,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480687</v>
+        <v>480861</v>
       </c>
       <c r="R39" t="n">
-        <v>6790754</v>
+        <v>6790634</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4719,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122907044</v>
+        <v>122914086</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4754,10 +4759,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480733</v>
+        <v>480839</v>
       </c>
       <c r="R40" t="n">
-        <v>6790651</v>
+        <v>6790677</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,10 +4821,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122913869</v>
+        <v>122913938</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4832,42 +4837,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480861</v>
+        <v>481291</v>
       </c>
       <c r="R41" t="n">
-        <v>6790634</v>
+        <v>6790740</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4894,9 +4894,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4911,19 +4921,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122908244</v>
+        <v>122911585</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4963,13 +4973,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480606</v>
+        <v>481035</v>
       </c>
       <c r="R42" t="n">
-        <v>6790682</v>
+        <v>6790750</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4998,7 +5008,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5008,7 +5018,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5023,19 +5033,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122908333</v>
+        <v>122907326</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5071,17 +5081,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480628</v>
+        <v>480712</v>
       </c>
       <c r="R43" t="n">
-        <v>6790661</v>
+        <v>6790625</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5108,19 +5118,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5135,19 +5135,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122911585</v>
+        <v>122908244</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5187,13 +5187,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481035</v>
+        <v>480606</v>
       </c>
       <c r="R44" t="n">
-        <v>6790750</v>
+        <v>6790682</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5247,19 +5247,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122908525</v>
+        <v>122908333</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480648</v>
+        <v>480628</v>
       </c>
       <c r="R45" t="n">
-        <v>6790546</v>
+        <v>6790661</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5371,7 +5371,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122914086</v>
+        <v>122910625</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480839</v>
+        <v>480776</v>
       </c>
       <c r="R46" t="n">
-        <v>6790677</v>
+        <v>6790600</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5473,7 +5473,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122913938</v>
+        <v>122910753</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5509,17 +5509,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481291</v>
+        <v>480802</v>
       </c>
       <c r="R47" t="n">
-        <v>6790740</v>
+        <v>6790516</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5546,19 +5546,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5573,19 +5563,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122907326</v>
+        <v>122905786</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5625,10 +5615,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480712</v>
+        <v>480687</v>
       </c>
       <c r="R48" t="n">
-        <v>6790625</v>
+        <v>6790754</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5687,7 +5677,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122910625</v>
+        <v>122908480</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5727,10 +5717,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480776</v>
+        <v>480744</v>
       </c>
       <c r="R49" t="n">
-        <v>6790600</v>
+        <v>6790521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5789,7 +5779,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122910753</v>
+        <v>122908525</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5825,17 +5815,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480802</v>
+        <v>480648</v>
       </c>
       <c r="R50" t="n">
-        <v>6790516</v>
+        <v>6790546</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5862,9 +5852,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5879,12 +5879,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7705,10 +7705,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122915277</v>
+        <v>122916590</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7721,37 +7721,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480729</v>
+        <v>481290</v>
       </c>
       <c r="R68" t="n">
-        <v>6790767</v>
+        <v>6790576</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7778,19 +7778,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7805,22 +7795,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122907325</v>
+        <v>122917610</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7829,38 +7819,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480575</v>
+        <v>480786</v>
       </c>
       <c r="R69" t="n">
-        <v>6790808</v>
+        <v>6790628</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7890,19 +7885,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7917,19 +7902,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122911611</v>
+        <v>122915277</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7969,13 +7954,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481072</v>
+        <v>480729</v>
       </c>
       <c r="R70" t="n">
-        <v>6790731</v>
+        <v>6790767</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8004,7 +7989,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8014,7 +7999,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8029,22 +8014,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122916590</v>
+        <v>122907325</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8057,34 +8042,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481290</v>
+        <v>480575</v>
       </c>
       <c r="R71" t="n">
-        <v>6790576</v>
+        <v>6790808</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8114,9 +8099,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8131,22 +8126,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122917610</v>
+        <v>122911611</v>
       </c>
       <c r="B72" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8155,46 +8150,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480786</v>
+        <v>481072</v>
       </c>
       <c r="R72" t="n">
-        <v>6790628</v>
+        <v>6790731</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8221,9 +8211,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8238,12 +8238,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8688,7 +8688,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122908311</v>
+        <v>122913943</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8728,10 +8728,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480715</v>
+        <v>480817</v>
       </c>
       <c r="R77" t="n">
-        <v>6790533</v>
+        <v>6790670</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8790,7 +8790,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122914812</v>
+        <v>122908311</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8830,10 +8830,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480982</v>
+        <v>480715</v>
       </c>
       <c r="R78" t="n">
-        <v>6790653</v>
+        <v>6790533</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8892,7 +8892,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122913943</v>
+        <v>122914812</v>
       </c>
       <c r="B79" t="n">
         <v>78766</v>
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480817</v>
+        <v>480982</v>
       </c>
       <c r="R79" t="n">
-        <v>6790670</v>
+        <v>6790653</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122915404</v>
+        <v>122906759</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481062</v>
+        <v>480726</v>
       </c>
       <c r="R80" t="n">
-        <v>6790666</v>
+        <v>6790689</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9096,10 +9096,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122908784</v>
+        <v>122915404</v>
       </c>
       <c r="B81" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9112,21 +9112,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480639</v>
+        <v>481062</v>
       </c>
       <c r="R81" t="n">
-        <v>6790797</v>
+        <v>6790666</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9169,19 +9169,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9196,12 +9186,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9310,7 +9300,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122906759</v>
+        <v>122908933</v>
       </c>
       <c r="B83" t="n">
         <v>78766</v>
@@ -9350,10 +9340,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480726</v>
+        <v>480772</v>
       </c>
       <c r="R83" t="n">
-        <v>6790689</v>
+        <v>6790602</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9412,10 +9402,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122908933</v>
+        <v>122908784</v>
       </c>
       <c r="B84" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9428,21 +9418,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9452,10 +9442,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480772</v>
+        <v>480639</v>
       </c>
       <c r="R84" t="n">
-        <v>6790602</v>
+        <v>6790797</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9485,9 +9475,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9502,19 +9502,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122911477</v>
+        <v>122910493</v>
       </c>
       <c r="B85" t="n">
         <v>78766</v>
@@ -9554,10 +9554,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481096</v>
+        <v>480755</v>
       </c>
       <c r="R85" t="n">
-        <v>6790743</v>
+        <v>6790775</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9626,7 +9626,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122907348</v>
+        <v>122916212</v>
       </c>
       <c r="B86" t="n">
         <v>78766</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480716</v>
+        <v>481263</v>
       </c>
       <c r="R86" t="n">
-        <v>6790617</v>
+        <v>6790561</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122910493</v>
+        <v>122907348</v>
       </c>
       <c r="B87" t="n">
         <v>78766</v>
@@ -9764,14 +9764,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480755</v>
+        <v>480716</v>
       </c>
       <c r="R87" t="n">
-        <v>6790775</v>
+        <v>6790617</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9801,19 +9801,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9828,19 +9818,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122916212</v>
+        <v>122907225</v>
       </c>
       <c r="B88" t="n">
         <v>78766</v>
@@ -9876,17 +9866,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481263</v>
+        <v>480622</v>
       </c>
       <c r="R88" t="n">
-        <v>6790561</v>
+        <v>6790776</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9913,9 +9903,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9930,19 +9930,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122916780</v>
+        <v>122911477</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -9978,14 +9978,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481324</v>
+        <v>481096</v>
       </c>
       <c r="R89" t="n">
-        <v>6790518</v>
+        <v>6790743</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10015,9 +10015,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10032,19 +10042,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122917077</v>
+        <v>122916780</v>
       </c>
       <c r="B90" t="n">
         <v>78766</v>
@@ -10084,10 +10094,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481414</v>
+        <v>481324</v>
       </c>
       <c r="R90" t="n">
-        <v>6790487</v>
+        <v>6790518</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10146,7 +10156,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122907225</v>
+        <v>122917077</v>
       </c>
       <c r="B91" t="n">
         <v>78766</v>
@@ -10182,17 +10192,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480622</v>
+        <v>481414</v>
       </c>
       <c r="R91" t="n">
-        <v>6790776</v>
+        <v>6790487</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10219,19 +10229,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10246,19 +10246,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122913909</v>
+        <v>122913714</v>
       </c>
       <c r="B92" t="n">
         <v>78766</v>
@@ -10298,10 +10298,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480837</v>
+        <v>480860</v>
       </c>
       <c r="R92" t="n">
-        <v>6790651</v>
+        <v>6790660</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10360,7 +10360,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122913893</v>
+        <v>122915141</v>
       </c>
       <c r="B93" t="n">
         <v>78766</v>
@@ -10396,17 +10396,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481268</v>
+        <v>480999</v>
       </c>
       <c r="R93" t="n">
-        <v>6790734</v>
+        <v>6790659</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10433,19 +10433,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10460,19 +10450,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122914153</v>
+        <v>122914964</v>
       </c>
       <c r="B94" t="n">
         <v>78766</v>
@@ -10508,17 +10498,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480850</v>
+        <v>480805</v>
       </c>
       <c r="R94" t="n">
-        <v>6790697</v>
+        <v>6790675</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10545,9 +10535,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10562,19 +10562,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122913714</v>
+        <v>122913909</v>
       </c>
       <c r="B95" t="n">
         <v>78766</v>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480860</v>
+        <v>480837</v>
       </c>
       <c r="R95" t="n">
-        <v>6790660</v>
+        <v>6790651</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122914964</v>
+        <v>122913893</v>
       </c>
       <c r="B96" t="n">
         <v>78766</v>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480805</v>
+        <v>481268</v>
       </c>
       <c r="R96" t="n">
-        <v>6790675</v>
+        <v>6790734</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10788,7 +10788,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122915141</v>
+        <v>122914153</v>
       </c>
       <c r="B97" t="n">
         <v>78766</v>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480999</v>
+        <v>480850</v>
       </c>
       <c r="R97" t="n">
-        <v>6790659</v>
+        <v>6790697</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10890,7 +10890,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122908048</v>
+        <v>122913967</v>
       </c>
       <c r="B98" t="n">
         <v>78766</v>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480735</v>
+        <v>480823</v>
       </c>
       <c r="R98" t="n">
-        <v>6790566</v>
+        <v>6790672</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122908658</v>
+        <v>122914256</v>
       </c>
       <c r="B99" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11004,41 +11004,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>480701</v>
+        <v>480858</v>
       </c>
       <c r="R99" t="n">
-        <v>6790532</v>
+        <v>6790672</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11065,19 +11065,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11092,19 +11082,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122910312</v>
+        <v>122914177</v>
       </c>
       <c r="B100" t="n">
         <v>78766</v>
@@ -11140,17 +11130,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480759</v>
+        <v>481318</v>
       </c>
       <c r="R100" t="n">
-        <v>6790654</v>
+        <v>6790679</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11177,9 +11167,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11194,19 +11194,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122910124</v>
+        <v>122914370</v>
       </c>
       <c r="B101" t="n">
         <v>78766</v>
@@ -11242,17 +11242,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480730</v>
+        <v>481130</v>
       </c>
       <c r="R101" t="n">
-        <v>6790750</v>
+        <v>6790661</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11279,9 +11279,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11296,19 +11306,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122911564</v>
+        <v>122910124</v>
       </c>
       <c r="B102" t="n">
         <v>78766</v>
@@ -11344,17 +11354,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>481081</v>
+        <v>480730</v>
       </c>
       <c r="R102" t="n">
-        <v>6790749</v>
+        <v>6790750</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11381,19 +11391,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11408,19 +11408,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122914256</v>
+        <v>122910312</v>
       </c>
       <c r="B103" t="n">
         <v>78766</v>
@@ -11460,10 +11460,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>480858</v>
+        <v>480759</v>
       </c>
       <c r="R103" t="n">
-        <v>6790672</v>
+        <v>6790654</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11522,7 +11522,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122914370</v>
+        <v>122908048</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11558,17 +11558,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>481130</v>
+        <v>480735</v>
       </c>
       <c r="R104" t="n">
-        <v>6790661</v>
+        <v>6790566</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11595,19 +11595,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:36</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11622,22 +11612,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122913967</v>
+        <v>122908658</v>
       </c>
       <c r="B105" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11646,41 +11636,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480823</v>
+        <v>480701</v>
       </c>
       <c r="R105" t="n">
-        <v>6790672</v>
+        <v>6790532</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11707,9 +11697,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11724,19 +11724,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122914177</v>
+        <v>122911564</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -11776,10 +11776,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>481318</v>
+        <v>481081</v>
       </c>
       <c r="R106" t="n">
-        <v>6790679</v>
+        <v>6790749</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13060,7 +13060,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122907632</v>
+        <v>122910439</v>
       </c>
       <c r="B118" t="n">
         <v>78766</v>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>480720</v>
+        <v>480761</v>
       </c>
       <c r="R118" t="n">
-        <v>6790586</v>
+        <v>6790650</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122908242</v>
+        <v>122909092</v>
       </c>
       <c r="B119" t="n">
         <v>78766</v>
@@ -13198,14 +13198,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>480743</v>
+        <v>480626</v>
       </c>
       <c r="R119" t="n">
-        <v>6790542</v>
+        <v>6790648</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13235,9 +13235,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13252,19 +13262,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122913997</v>
+        <v>122907632</v>
       </c>
       <c r="B120" t="n">
         <v>78766</v>
@@ -13300,17 +13310,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>481407</v>
+        <v>480720</v>
       </c>
       <c r="R120" t="n">
-        <v>6790724</v>
+        <v>6790586</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13337,19 +13347,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13364,19 +13364,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122916381</v>
+        <v>122908242</v>
       </c>
       <c r="B121" t="n">
         <v>78766</v>
@@ -13416,10 +13416,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>481294</v>
+        <v>480743</v>
       </c>
       <c r="R121" t="n">
-        <v>6790587</v>
+        <v>6790542</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122916304</v>
+        <v>122913997</v>
       </c>
       <c r="B122" t="n">
         <v>78766</v>
@@ -13514,17 +13514,17 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>481273</v>
+        <v>481407</v>
       </c>
       <c r="R122" t="n">
-        <v>6790567</v>
+        <v>6790724</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13551,9 +13551,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13568,19 +13578,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122910439</v>
+        <v>122916381</v>
       </c>
       <c r="B123" t="n">
         <v>78766</v>
@@ -13620,10 +13630,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>480761</v>
+        <v>481294</v>
       </c>
       <c r="R123" t="n">
-        <v>6790650</v>
+        <v>6790587</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13682,7 +13692,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122909092</v>
+        <v>122916304</v>
       </c>
       <c r="B124" t="n">
         <v>78766</v>
@@ -13718,14 +13728,14 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480626</v>
+        <v>481273</v>
       </c>
       <c r="R124" t="n">
-        <v>6790648</v>
+        <v>6790567</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13755,19 +13765,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13782,12 +13782,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14970,7 +14970,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122907899</v>
+        <v>122916802</v>
       </c>
       <c r="B136" t="n">
         <v>78766</v>
@@ -15010,10 +15010,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>480754</v>
+        <v>481344</v>
       </c>
       <c r="R136" t="n">
-        <v>6790590</v>
+        <v>6790501</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122916802</v>
+        <v>122905918</v>
       </c>
       <c r="B137" t="n">
         <v>78766</v>
@@ -15112,10 +15112,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>481344</v>
+        <v>480680</v>
       </c>
       <c r="R137" t="n">
-        <v>6790501</v>
+        <v>6790718</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15174,7 +15174,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122905918</v>
+        <v>122907899</v>
       </c>
       <c r="B138" t="n">
         <v>78766</v>
@@ -15214,10 +15214,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480680</v>
+        <v>480754</v>
       </c>
       <c r="R138" t="n">
-        <v>6790718</v>
+        <v>6790590</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15276,7 +15276,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122916175</v>
+        <v>122908102</v>
       </c>
       <c r="B139" t="n">
         <v>78766</v>
@@ -15312,17 +15312,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>481253</v>
+        <v>480607</v>
       </c>
       <c r="R139" t="n">
-        <v>6790554</v>
+        <v>6790683</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15349,9 +15349,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15366,22 +15376,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122910277</v>
+        <v>122908063</v>
       </c>
       <c r="B140" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15390,25 +15400,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15418,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480738</v>
+        <v>480571</v>
       </c>
       <c r="R140" t="n">
-        <v>6790786</v>
+        <v>6790798</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15453,7 +15463,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15463,7 +15473,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15478,22 +15488,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122908102</v>
+        <v>122908588</v>
       </c>
       <c r="B141" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15506,21 +15516,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15530,13 +15540,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>480607</v>
+        <v>480638</v>
       </c>
       <c r="R141" t="n">
-        <v>6790683</v>
+        <v>6790738</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15565,7 +15575,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15575,7 +15585,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15590,22 +15600,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122914414</v>
+        <v>122908121</v>
       </c>
       <c r="B142" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15614,25 +15624,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15642,13 +15652,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>481039</v>
+        <v>480638</v>
       </c>
       <c r="R142" t="n">
-        <v>6790686</v>
+        <v>6790738</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15677,7 +15687,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15687,7 +15697,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15702,12 +15712,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15826,10 +15836,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122908063</v>
+        <v>122916175</v>
       </c>
       <c r="B144" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15838,38 +15848,38 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>480571</v>
+        <v>481253</v>
       </c>
       <c r="R144" t="n">
-        <v>6790798</v>
+        <v>6790554</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15899,19 +15909,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15926,22 +15926,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122908588</v>
+        <v>122910277</v>
       </c>
       <c r="B145" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15954,21 +15954,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15978,10 +15978,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>480638</v>
+        <v>480738</v>
       </c>
       <c r="R145" t="n">
-        <v>6790738</v>
+        <v>6790786</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16038,22 +16038,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122908121</v>
+        <v>122914414</v>
       </c>
       <c r="B146" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16062,25 +16062,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16090,13 +16090,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>480638</v>
+        <v>481039</v>
       </c>
       <c r="R146" t="n">
-        <v>6790738</v>
+        <v>6790686</v>
       </c>
       <c r="S146" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16150,22 +16150,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122912740</v>
+        <v>122908690</v>
       </c>
       <c r="B147" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16178,21 +16178,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16202,13 +16202,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>481151</v>
+        <v>480626</v>
       </c>
       <c r="R147" t="n">
-        <v>6790720</v>
+        <v>6790648</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16262,22 +16262,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122913095</v>
+        <v>122914997</v>
       </c>
       <c r="B148" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16286,41 +16286,49 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480874</v>
+        <v>480873</v>
       </c>
       <c r="R148" t="n">
-        <v>6790659</v>
+        <v>6790694</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16347,9 +16355,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16364,22 +16382,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122915104</v>
+        <v>122912740</v>
       </c>
       <c r="B149" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16388,43 +16406,38 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480783</v>
+        <v>481151</v>
       </c>
       <c r="R149" t="n">
-        <v>6790712</v>
+        <v>6790720</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16456,7 +16469,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16466,7 +16479,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16493,7 +16506,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122915881</v>
+        <v>122913095</v>
       </c>
       <c r="B150" t="n">
         <v>78766</v>
@@ -16533,10 +16546,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>481164</v>
+        <v>480874</v>
       </c>
       <c r="R150" t="n">
-        <v>6790573</v>
+        <v>6790659</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16595,10 +16608,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122917031</v>
+        <v>122915104</v>
       </c>
       <c r="B151" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16607,41 +16620,46 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>481382</v>
+        <v>480783</v>
       </c>
       <c r="R151" t="n">
-        <v>6790485</v>
+        <v>6790712</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16668,9 +16686,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16685,22 +16713,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122908690</v>
+        <v>122915881</v>
       </c>
       <c r="B152" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16713,37 +16741,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480626</v>
+        <v>481164</v>
       </c>
       <c r="R152" t="n">
-        <v>6790648</v>
+        <v>6790573</v>
       </c>
       <c r="S152" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16770,19 +16798,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16797,22 +16815,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122914997</v>
+        <v>122917031</v>
       </c>
       <c r="B153" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16821,49 +16839,41 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480873</v>
+        <v>481382</v>
       </c>
       <c r="R153" t="n">
-        <v>6790694</v>
+        <v>6790485</v>
       </c>
       <c r="S153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16890,19 +16900,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16917,19 +16917,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122911259</v>
+        <v>122916548</v>
       </c>
       <c r="B154" t="n">
         <v>78766</v>
@@ -16965,14 +16965,14 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>481008</v>
+        <v>481290</v>
       </c>
       <c r="R154" t="n">
-        <v>6790695</v>
+        <v>6790576</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17002,19 +17002,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17029,19 +17019,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122910695</v>
+        <v>122906123</v>
       </c>
       <c r="B155" t="n">
         <v>78766</v>
@@ -17081,10 +17071,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480801</v>
+        <v>480697</v>
       </c>
       <c r="R155" t="n">
-        <v>6790557</v>
+        <v>6790703</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17143,7 +17133,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122915272</v>
+        <v>122905974</v>
       </c>
       <c r="B156" t="n">
         <v>78766</v>
@@ -17183,10 +17173,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>481024</v>
+        <v>480711</v>
       </c>
       <c r="R156" t="n">
-        <v>6790673</v>
+        <v>6790714</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17245,7 +17235,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122905974</v>
+        <v>122914058</v>
       </c>
       <c r="B157" t="n">
         <v>78766</v>
@@ -17285,10 +17275,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480711</v>
+        <v>480832</v>
       </c>
       <c r="R157" t="n">
-        <v>6790714</v>
+        <v>6790668</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17347,10 +17337,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122906123</v>
+        <v>122913790</v>
       </c>
       <c r="B158" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17359,41 +17349,49 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480697</v>
+        <v>481264</v>
       </c>
       <c r="R158" t="n">
-        <v>6790703</v>
+        <v>6790709</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17420,9 +17418,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17437,22 +17445,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122914058</v>
+        <v>122909048</v>
       </c>
       <c r="B159" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17461,38 +17469,47 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>480832</v>
+        <v>480660</v>
       </c>
       <c r="R159" t="n">
-        <v>6790668</v>
+        <v>6790681</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17522,39 +17539,50 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122913790</v>
+        <v>122915538</v>
       </c>
       <c r="B160" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17563,49 +17591,41 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>481264</v>
+        <v>481062</v>
       </c>
       <c r="R160" t="n">
-        <v>6790709</v>
+        <v>6790598</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17632,19 +17652,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17659,19 +17669,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122909048</v>
+        <v>122907535</v>
       </c>
       <c r="B161" t="n">
         <v>8441</v>
@@ -17705,25 +17715,16 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>480660</v>
+        <v>480604</v>
       </c>
       <c r="R161" t="n">
-        <v>6790681</v>
+        <v>6790798</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17755,7 +17756,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17765,7 +17766,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17774,26 +17775,25 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122915538</v>
+        <v>122910695</v>
       </c>
       <c r="B162" t="n">
         <v>78766</v>
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>481062</v>
+        <v>480801</v>
       </c>
       <c r="R162" t="n">
-        <v>6790598</v>
+        <v>6790557</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17895,7 +17895,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122916548</v>
+        <v>122911259</v>
       </c>
       <c r="B163" t="n">
         <v>78766</v>
@@ -17931,14 +17931,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>481290</v>
+        <v>481008</v>
       </c>
       <c r="R163" t="n">
-        <v>6790576</v>
+        <v>6790695</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17968,9 +17968,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17985,22 +17995,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122907535</v>
+        <v>122915272</v>
       </c>
       <c r="B164" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18009,25 +18019,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18037,10 +18047,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>480604</v>
+        <v>481024</v>
       </c>
       <c r="R164" t="n">
-        <v>6790798</v>
+        <v>6790673</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18070,19 +18080,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>11:29</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18097,22 +18097,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122907615</v>
+        <v>122908892</v>
       </c>
       <c r="B165" t="n">
-        <v>90964</v>
+        <v>8441</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18121,25 +18121,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>480730</v>
+        <v>480771</v>
       </c>
       <c r="R165" t="n">
-        <v>6790601</v>
+        <v>6790522</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18211,10 +18211,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122907777</v>
+        <v>122909144</v>
       </c>
       <c r="B166" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18227,21 +18227,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18251,10 +18251,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>480728</v>
+        <v>480738</v>
       </c>
       <c r="R166" t="n">
-        <v>6790595</v>
+        <v>6790666</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18313,10 +18313,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122913744</v>
+        <v>122907615</v>
       </c>
       <c r="B167" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18329,37 +18329,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>481158</v>
+        <v>480730</v>
       </c>
       <c r="R167" t="n">
-        <v>6790716</v>
+        <v>6790601</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18386,19 +18386,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18413,22 +18403,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122915938</v>
+        <v>122907777</v>
       </c>
       <c r="B168" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18441,21 +18431,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18465,10 +18455,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>481166</v>
+        <v>480728</v>
       </c>
       <c r="R168" t="n">
-        <v>6790560</v>
+        <v>6790595</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18527,7 +18517,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122907901</v>
+        <v>122910424</v>
       </c>
       <c r="B169" t="n">
         <v>78766</v>
@@ -18563,14 +18553,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>480604</v>
+        <v>480743</v>
       </c>
       <c r="R169" t="n">
-        <v>6790798</v>
+        <v>6790781</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18602,7 +18592,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18612,7 +18602,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18627,19 +18617,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122909144</v>
+        <v>122913744</v>
       </c>
       <c r="B170" t="n">
         <v>78766</v>
@@ -18675,17 +18665,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>480738</v>
+        <v>481158</v>
       </c>
       <c r="R170" t="n">
-        <v>6790666</v>
+        <v>6790716</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18712,9 +18702,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18729,22 +18729,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122908892</v>
+        <v>122915938</v>
       </c>
       <c r="B171" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18753,25 +18753,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18781,10 +18781,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>480771</v>
+        <v>481166</v>
       </c>
       <c r="R171" t="n">
-        <v>6790522</v>
+        <v>6790560</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18843,7 +18843,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122910424</v>
+        <v>122907901</v>
       </c>
       <c r="B172" t="n">
         <v>78766</v>
@@ -18879,14 +18879,14 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>480743</v>
+        <v>480604</v>
       </c>
       <c r="R172" t="n">
-        <v>6790781</v>
+        <v>6790798</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18928,7 +18928,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18943,12 +18943,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122899266</v>
+        <v>122899017</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480455</v>
+        <v>480617</v>
       </c>
       <c r="R3" t="n">
-        <v>6790754</v>
+        <v>6790810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Otroliga mängder med garnlav vilket jag ser runt omkring mig där jag står.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122899017</v>
+        <v>122899266</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480617</v>
+        <v>480455</v>
       </c>
       <c r="R4" t="n">
-        <v>6790810</v>
+        <v>6790754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Otroliga mängder med garnlav vilket jag ser runt omkring mig där jag står.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122908448</v>
+        <v>122906990</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1878,17 +1878,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480628</v>
+        <v>480725</v>
       </c>
       <c r="R13" t="n">
-        <v>6790661</v>
+        <v>6790654</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,19 +1915,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,19 +1932,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122910257</v>
+        <v>122908368</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1990,17 +1980,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480680</v>
+        <v>480704</v>
       </c>
       <c r="R14" t="n">
-        <v>6790662</v>
+        <v>6790523</v>
       </c>
       <c r="S14" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2027,19 +2017,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,19 +2034,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122906990</v>
+        <v>122912843</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2102,17 +2082,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480725</v>
+        <v>481068</v>
       </c>
       <c r="R15" t="n">
-        <v>6790654</v>
+        <v>6790734</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,9 +2119,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,19 +2146,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122908368</v>
+        <v>122915538</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2208,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480704</v>
+        <v>481062</v>
       </c>
       <c r="R16" t="n">
-        <v>6790523</v>
+        <v>6790598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122912843</v>
+        <v>122907426</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2306,17 +2296,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481068</v>
+        <v>480611</v>
       </c>
       <c r="R17" t="n">
-        <v>6790734</v>
+        <v>6790803</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2345,7 +2335,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2345,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,19 +2360,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122915538</v>
+        <v>122910462</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2418,14 +2408,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481062</v>
+        <v>480753</v>
       </c>
       <c r="R18" t="n">
-        <v>6790598</v>
+        <v>6790776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,9 +2445,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,19 +2472,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122907426</v>
+        <v>122908082</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2520,17 +2520,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480611</v>
+        <v>480607</v>
       </c>
       <c r="R19" t="n">
-        <v>6790803</v>
+        <v>6790687</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,19 +2584,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122910462</v>
+        <v>122908448</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480753</v>
+        <v>480628</v>
       </c>
       <c r="R20" t="n">
-        <v>6790776</v>
+        <v>6790661</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122908082</v>
+        <v>122910257</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480607</v>
+        <v>480680</v>
       </c>
       <c r="R21" t="n">
-        <v>6790687</v>
+        <v>6790662</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,12 +2808,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122916728</v>
+        <v>122914153</v>
       </c>
       <c r="B136" t="n">
         <v>78766</v>
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>481324</v>
+        <v>480850</v>
       </c>
       <c r="R136" t="n">
-        <v>6790518</v>
+        <v>6790697</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15092,7 +15092,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122905989</v>
+        <v>122916728</v>
       </c>
       <c r="B137" t="n">
         <v>78766</v>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>480688</v>
+        <v>481324</v>
       </c>
       <c r="R137" t="n">
-        <v>6790702</v>
+        <v>6790518</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15194,7 +15194,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122915007</v>
+        <v>122905989</v>
       </c>
       <c r="B138" t="n">
         <v>78766</v>
@@ -15230,17 +15230,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480873</v>
+        <v>480688</v>
       </c>
       <c r="R138" t="n">
-        <v>6790694</v>
+        <v>6790702</v>
       </c>
       <c r="S138" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15267,19 +15267,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15294,19 +15284,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122914846</v>
+        <v>122915007</v>
       </c>
       <c r="B139" t="n">
         <v>78766</v>
@@ -15346,13 +15336,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480895</v>
+        <v>480873</v>
       </c>
       <c r="R139" t="n">
-        <v>6790735</v>
+        <v>6790694</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15381,7 +15371,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15391,7 +15381,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15406,19 +15396,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122914153</v>
+        <v>122914846</v>
       </c>
       <c r="B140" t="n">
         <v>78766</v>
@@ -15454,17 +15444,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480850</v>
+        <v>480895</v>
       </c>
       <c r="R140" t="n">
-        <v>6790697</v>
+        <v>6790735</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15491,9 +15481,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15508,12 +15508,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -17885,10 +17885,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122914178</v>
+        <v>122910464</v>
       </c>
       <c r="B163" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17897,38 +17897,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>480864</v>
+        <v>480751</v>
       </c>
       <c r="R163" t="n">
-        <v>6790682</v>
+        <v>6790806</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17958,9 +17958,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17975,19 +17985,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122910505</v>
+        <v>122914178</v>
       </c>
       <c r="B164" t="n">
         <v>78766</v>
@@ -18027,10 +18037,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>480770</v>
+        <v>480864</v>
       </c>
       <c r="R164" t="n">
-        <v>6790637</v>
+        <v>6790682</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18089,10 +18099,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122915104</v>
+        <v>122910505</v>
       </c>
       <c r="B165" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18101,46 +18111,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>480783</v>
+        <v>480770</v>
       </c>
       <c r="R165" t="n">
-        <v>6790712</v>
+        <v>6790637</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18167,19 +18172,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18194,22 +18189,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122910464</v>
+        <v>122915104</v>
       </c>
       <c r="B166" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18222,37 +18217,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>480751</v>
+        <v>480783</v>
       </c>
       <c r="R166" t="n">
-        <v>6790806</v>
+        <v>6790712</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18306,22 +18306,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122914092</v>
+        <v>122905650</v>
       </c>
       <c r="B167" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18330,41 +18330,41 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>481216</v>
+        <v>480698</v>
       </c>
       <c r="R167" t="n">
-        <v>6790675</v>
+        <v>6790762</v>
       </c>
       <c r="S167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18391,19 +18391,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18418,22 +18408,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122908121</v>
+        <v>122905949</v>
       </c>
       <c r="B168" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18442,41 +18432,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>480638</v>
+        <v>480710</v>
       </c>
       <c r="R168" t="n">
-        <v>6790738</v>
+        <v>6790729</v>
       </c>
       <c r="S168" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18503,19 +18493,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18530,22 +18510,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122908063</v>
+        <v>122911611</v>
       </c>
       <c r="B169" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18554,25 +18534,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18582,13 +18562,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>480571</v>
+        <v>481072</v>
       </c>
       <c r="R169" t="n">
-        <v>6790798</v>
+        <v>6790731</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18617,7 +18597,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18627,7 +18607,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18654,10 +18634,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122905650</v>
+        <v>122914092</v>
       </c>
       <c r="B170" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18666,41 +18646,41 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>480698</v>
+        <v>481216</v>
       </c>
       <c r="R170" t="n">
-        <v>6790762</v>
+        <v>6790675</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18727,9 +18707,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18744,22 +18734,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122905949</v>
+        <v>122908121</v>
       </c>
       <c r="B171" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18768,41 +18758,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>480710</v>
+        <v>480638</v>
       </c>
       <c r="R171" t="n">
-        <v>6790729</v>
+        <v>6790738</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18829,9 +18819,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18846,22 +18846,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122911611</v>
+        <v>122908063</v>
       </c>
       <c r="B172" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18870,25 +18870,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18898,13 +18898,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>481072</v>
+        <v>480571</v>
       </c>
       <c r="R172" t="n">
-        <v>6790731</v>
+        <v>6790798</v>
       </c>
       <c r="S172" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18970,7 +18970,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122908564</v>
+        <v>122915404</v>
       </c>
       <c r="B173" t="n">
         <v>78766</v>
@@ -19006,17 +19006,17 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>480648</v>
+        <v>481062</v>
       </c>
       <c r="R173" t="n">
-        <v>6790546</v>
+        <v>6790666</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19043,19 +19043,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19070,22 +19060,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122915404</v>
+        <v>122907615</v>
       </c>
       <c r="B174" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19098,21 +19088,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19122,10 +19112,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>481062</v>
+        <v>480730</v>
       </c>
       <c r="R174" t="n">
-        <v>6790666</v>
+        <v>6790601</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19184,10 +19174,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122907615</v>
+        <v>122911259</v>
       </c>
       <c r="B175" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19200,34 +19190,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>480730</v>
+        <v>481008</v>
       </c>
       <c r="R175" t="n">
-        <v>6790601</v>
+        <v>6790695</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19257,9 +19247,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19274,12 +19274,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -19388,7 +19388,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122907981</v>
+        <v>122908564</v>
       </c>
       <c r="B177" t="n">
         <v>78766</v>
@@ -19428,10 +19428,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>480580</v>
+        <v>480648</v>
       </c>
       <c r="R177" t="n">
-        <v>6790754</v>
+        <v>6790546</v>
       </c>
       <c r="S177" t="n">
         <v>15</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19500,7 +19500,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122915163</v>
+        <v>122907981</v>
       </c>
       <c r="B178" t="n">
         <v>78766</v>
@@ -19536,17 +19536,17 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>480988</v>
+        <v>480580</v>
       </c>
       <c r="R178" t="n">
-        <v>6790673</v>
+        <v>6790754</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19573,9 +19573,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19590,19 +19600,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122911259</v>
+        <v>122915163</v>
       </c>
       <c r="B179" t="n">
         <v>78766</v>
@@ -19638,14 +19648,14 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>481008</v>
+        <v>480988</v>
       </c>
       <c r="R179" t="n">
-        <v>6790695</v>
+        <v>6790673</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19675,19 +19685,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19702,12 +19702,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -25144,7 +25144,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122963417</v>
+        <v>122962067</v>
       </c>
       <c r="B230" t="n">
         <v>78766</v>
@@ -25180,17 +25180,17 @@
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>481011</v>
+        <v>480821</v>
       </c>
       <c r="R230" t="n">
-        <v>6790699</v>
+        <v>6790633</v>
       </c>
       <c r="S230" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -25217,9 +25217,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25234,19 +25244,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>122962067</v>
+        <v>122978123</v>
       </c>
       <c r="B231" t="n">
         <v>78766</v>
@@ -25286,10 +25296,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>480821</v>
+        <v>481144</v>
       </c>
       <c r="R231" t="n">
-        <v>6790633</v>
+        <v>6790730</v>
       </c>
       <c r="S231" t="n">
         <v>9</v>
@@ -25321,7 +25331,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -25331,7 +25341,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25358,7 +25368,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>122978123</v>
+        <v>122968517</v>
       </c>
       <c r="B232" t="n">
         <v>78766</v>
@@ -25398,10 +25408,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>481144</v>
+        <v>481434</v>
       </c>
       <c r="R232" t="n">
-        <v>6790730</v>
+        <v>6790535</v>
       </c>
       <c r="S232" t="n">
         <v>9</v>
@@ -25433,7 +25443,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -25443,7 +25453,12 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25470,7 +25485,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>122967445</v>
+        <v>122963417</v>
       </c>
       <c r="B233" t="n">
         <v>78766</v>
@@ -25506,17 +25521,17 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>481249</v>
+        <v>481011</v>
       </c>
       <c r="R233" t="n">
-        <v>6790669</v>
+        <v>6790699</v>
       </c>
       <c r="S233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -25543,19 +25558,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25570,19 +25575,19 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>122967506</v>
+        <v>122967445</v>
       </c>
       <c r="B234" t="n">
         <v>78766</v>
@@ -25622,7 +25627,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>481250</v>
+        <v>481249</v>
       </c>
       <c r="R234" t="n">
         <v>6790669</v>
@@ -25657,7 +25662,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -25667,7 +25672,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25694,7 +25699,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>122968666</v>
+        <v>122967506</v>
       </c>
       <c r="B235" t="n">
         <v>78766</v>
@@ -25734,10 +25739,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>481436</v>
+        <v>481250</v>
       </c>
       <c r="R235" t="n">
-        <v>6790540</v>
+        <v>6790669</v>
       </c>
       <c r="S235" t="n">
         <v>9</v>
@@ -25769,7 +25774,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -25779,12 +25784,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25811,7 +25811,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>122968517</v>
+        <v>122968666</v>
       </c>
       <c r="B236" t="n">
         <v>78766</v>
@@ -25851,10 +25851,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>481434</v>
+        <v>481436</v>
       </c>
       <c r="R236" t="n">
-        <v>6790535</v>
+        <v>6790540</v>
       </c>
       <c r="S236" t="n">
         <v>9</v>
@@ -25886,7 +25886,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -25896,7 +25896,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC236" t="inlineStr">
@@ -30014,10 +30014,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122964962</v>
+        <v>122970211</v>
       </c>
       <c r="B275" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -30026,25 +30026,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -30054,10 +30054,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>481026</v>
+        <v>481559</v>
       </c>
       <c r="R275" t="n">
-        <v>6790700</v>
+        <v>6790521</v>
       </c>
       <c r="S275" t="n">
         <v>9</v>
@@ -30089,7 +30089,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -30099,7 +30099,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -30126,7 +30126,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122970211</v>
+        <v>122968577</v>
       </c>
       <c r="B276" t="n">
         <v>78766</v>
@@ -30166,10 +30166,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>481559</v>
+        <v>481434</v>
       </c>
       <c r="R276" t="n">
-        <v>6790521</v>
+        <v>6790538</v>
       </c>
       <c r="S276" t="n">
         <v>9</v>
@@ -30201,7 +30201,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -30238,10 +30238,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122968577</v>
+        <v>122964962</v>
       </c>
       <c r="B277" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -30250,25 +30250,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -30278,10 +30278,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>481434</v>
+        <v>481026</v>
       </c>
       <c r="R277" t="n">
-        <v>6790538</v>
+        <v>6790700</v>
       </c>
       <c r="S277" t="n">
         <v>9</v>
@@ -30313,7 +30313,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -30323,7 +30323,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -30350,10 +30350,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122965865</v>
+        <v>122961494</v>
       </c>
       <c r="B278" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -30366,42 +30366,37 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>481118</v>
+        <v>480772</v>
       </c>
       <c r="R278" t="n">
-        <v>6790699</v>
+        <v>6790705</v>
       </c>
       <c r="S278" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -30428,19 +30423,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30455,12 +30440,12 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
@@ -30579,10 +30564,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122961494</v>
+        <v>122965865</v>
       </c>
       <c r="B280" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -30595,37 +30580,42 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>480772</v>
+        <v>481118</v>
       </c>
       <c r="R280" t="n">
-        <v>6790705</v>
+        <v>6790699</v>
       </c>
       <c r="S280" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -30652,9 +30642,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30669,22 +30669,22 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122969848</v>
+        <v>122968533</v>
       </c>
       <c r="B281" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -30697,16 +30697,16 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -30717,17 +30717,17 @@
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>481544</v>
+        <v>481432</v>
       </c>
       <c r="R281" t="n">
-        <v>6790494</v>
+        <v>6790537</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -30754,14 +30754,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30776,19 +30781,19 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122968533</v>
+        <v>122968051</v>
       </c>
       <c r="B282" t="n">
         <v>78766</v>
@@ -30828,10 +30833,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>481432</v>
+        <v>481370</v>
       </c>
       <c r="R282" t="n">
-        <v>6790537</v>
+        <v>6790557</v>
       </c>
       <c r="S282" t="n">
         <v>9</v>
@@ -30863,7 +30868,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -30873,7 +30878,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30900,7 +30905,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122968051</v>
+        <v>122973653</v>
       </c>
       <c r="B283" t="n">
         <v>78766</v>
@@ -30936,17 +30941,17 @@
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>481370</v>
+        <v>481479</v>
       </c>
       <c r="R283" t="n">
-        <v>6790557</v>
+        <v>6790535</v>
       </c>
       <c r="S283" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -30973,19 +30978,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB283" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -31000,19 +30995,19 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122973653</v>
+        <v>122959889</v>
       </c>
       <c r="B284" t="n">
         <v>78766</v>
@@ -31052,10 +31047,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>481479</v>
+        <v>480792</v>
       </c>
       <c r="R284" t="n">
-        <v>6790535</v>
+        <v>6790812</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -31114,10 +31109,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122959889</v>
+        <v>122962565</v>
       </c>
       <c r="B285" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31130,37 +31125,37 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>480792</v>
+        <v>480854</v>
       </c>
       <c r="R285" t="n">
-        <v>6790812</v>
+        <v>6790625</v>
       </c>
       <c r="S285" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -31187,9 +31182,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -31204,22 +31209,22 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122962565</v>
+        <v>122967628</v>
       </c>
       <c r="B286" t="n">
-        <v>78502</v>
+        <v>57631</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -31232,37 +31237,42 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>480854</v>
+        <v>481264</v>
       </c>
       <c r="R286" t="n">
-        <v>6790625</v>
+        <v>6790665</v>
       </c>
       <c r="S286" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -31291,7 +31301,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -31301,7 +31311,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -31328,10 +31338,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122967628</v>
+        <v>122969848</v>
       </c>
       <c r="B287" t="n">
-        <v>57631</v>
+        <v>78767</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -31344,42 +31354,37 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>103021</v>
+        <v>230405</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>481264</v>
+        <v>481544</v>
       </c>
       <c r="R287" t="n">
-        <v>6790665</v>
+        <v>6790494</v>
       </c>
       <c r="S287" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -31406,19 +31411,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>13:07</t>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -31433,12 +31433,12 @@
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
@@ -33299,7 +33299,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122974755</v>
+        <v>122975396</v>
       </c>
       <c r="B305" t="n">
         <v>78766</v>
@@ -33335,17 +33335,17 @@
       <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>481461</v>
+        <v>481394</v>
       </c>
       <c r="R305" t="n">
-        <v>6790683</v>
+        <v>6790771</v>
       </c>
       <c r="S305" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -33372,14 +33372,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA305" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC305" t="inlineStr">
-        <is>
-          <t>Fuktig miljö med äldre tallar och granar, hackhål i stamm, tall. Miljöbilder.</t>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -33394,19 +33399,19 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122968541</v>
+        <v>122976607</v>
       </c>
       <c r="B306" t="n">
         <v>78766</v>
@@ -33442,17 +33447,17 @@
       <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>481406</v>
+        <v>481343</v>
       </c>
       <c r="R306" t="n">
-        <v>6790500</v>
+        <v>6790726</v>
       </c>
       <c r="S306" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -33479,14 +33484,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA306" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC306" t="inlineStr">
-        <is>
-          <t>Garnlav så långt jag ser i en radie av 50 meter.</t>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -33501,19 +33511,19 @@
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122965887</v>
+        <v>122968143</v>
       </c>
       <c r="B307" t="n">
         <v>78766</v>
@@ -33549,17 +33559,17 @@
       <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>481195</v>
+        <v>481374</v>
       </c>
       <c r="R307" t="n">
-        <v>6790707</v>
+        <v>6790558</v>
       </c>
       <c r="S307" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -33586,14 +33596,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA307" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC307" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig så långt jag kan se!</t>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33608,22 +33623,22 @@
       <c r="AT307" t="inlineStr"/>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122968130</v>
+        <v>122974755</v>
       </c>
       <c r="B308" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -33632,41 +33647,41 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>481374</v>
+        <v>481461</v>
       </c>
       <c r="R308" t="n">
-        <v>6790558</v>
+        <v>6790683</v>
       </c>
       <c r="S308" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -33693,19 +33708,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>13:23</t>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>Fuktig miljö med äldre tallar och granar, hackhål i stamm, tall. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33720,19 +33730,19 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122975396</v>
+        <v>122968541</v>
       </c>
       <c r="B309" t="n">
         <v>78766</v>
@@ -33768,17 +33778,17 @@
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>481394</v>
+        <v>481406</v>
       </c>
       <c r="R309" t="n">
-        <v>6790771</v>
+        <v>6790500</v>
       </c>
       <c r="S309" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -33805,19 +33815,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB309" t="inlineStr">
-        <is>
-          <t>16:32</t>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>Garnlav så långt jag ser i en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33832,19 +33837,19 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122976607</v>
+        <v>122965887</v>
       </c>
       <c r="B310" t="n">
         <v>78766</v>
@@ -33880,17 +33885,17 @@
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>481343</v>
+        <v>481195</v>
       </c>
       <c r="R310" t="n">
-        <v>6790726</v>
+        <v>6790707</v>
       </c>
       <c r="S310" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -33917,19 +33922,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig så långt jag kan se!</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33944,22 +33944,22 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122968143</v>
+        <v>122968130</v>
       </c>
       <c r="B311" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -33968,25 +33968,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -34987,10 +34987,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122972633</v>
+        <v>122971698</v>
       </c>
       <c r="B320" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -34999,38 +34999,38 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>481748</v>
+        <v>481661</v>
       </c>
       <c r="R320" t="n">
-        <v>6790465</v>
+        <v>6790503</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -35089,10 +35089,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122971698</v>
+        <v>122971770</v>
       </c>
       <c r="B321" t="n">
-        <v>8441</v>
+        <v>78792</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -35105,37 +35105,37 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>481661</v>
+        <v>481677</v>
       </c>
       <c r="R321" t="n">
-        <v>6790503</v>
+        <v>6790565</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -35162,9 +35162,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -35179,22 +35189,22 @@
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122971770</v>
+        <v>122972843</v>
       </c>
       <c r="B322" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -35203,41 +35213,41 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>481677</v>
+        <v>481748</v>
       </c>
       <c r="R322" t="n">
-        <v>6790565</v>
+        <v>6790465</v>
       </c>
       <c r="S322" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -35264,19 +35274,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -35291,12 +35291,12 @@
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
@@ -35420,10 +35420,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122972089</v>
+        <v>122972025</v>
       </c>
       <c r="B324" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -35432,38 +35432,43 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P324" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>481695</v>
+        <v>481687</v>
       </c>
       <c r="R324" t="n">
-        <v>6790593</v>
+        <v>6790643</v>
       </c>
       <c r="S324" t="n">
         <v>9</v>
@@ -35495,7 +35500,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -35505,7 +35510,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -35532,10 +35537,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122972025</v>
+        <v>122972089</v>
       </c>
       <c r="B325" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -35544,43 +35549,38 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P325" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>481687</v>
+        <v>481695</v>
       </c>
       <c r="R325" t="n">
-        <v>6790643</v>
+        <v>6790593</v>
       </c>
       <c r="S325" t="n">
         <v>9</v>
@@ -35612,7 +35612,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD325" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122906990</v>
+        <v>122908448</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1878,17 +1878,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480725</v>
+        <v>480628</v>
       </c>
       <c r="R13" t="n">
-        <v>6790654</v>
+        <v>6790661</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,9 +1915,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,19 +1942,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122908368</v>
+        <v>122910257</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1980,17 +1990,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480704</v>
+        <v>480680</v>
       </c>
       <c r="R14" t="n">
-        <v>6790523</v>
+        <v>6790662</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,9 +2027,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,19 +2054,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122912843</v>
+        <v>122906990</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2082,17 +2102,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481068</v>
+        <v>480725</v>
       </c>
       <c r="R15" t="n">
-        <v>6790734</v>
+        <v>6790654</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2119,19 +2139,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,19 +2156,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122915538</v>
+        <v>122908368</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481062</v>
+        <v>480704</v>
       </c>
       <c r="R16" t="n">
-        <v>6790598</v>
+        <v>6790523</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122907426</v>
+        <v>122912843</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2296,17 +2306,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480611</v>
+        <v>481068</v>
       </c>
       <c r="R17" t="n">
-        <v>6790803</v>
+        <v>6790734</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2335,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2345,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,19 +2370,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122910462</v>
+        <v>122915538</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2408,14 +2418,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480753</v>
+        <v>481062</v>
       </c>
       <c r="R18" t="n">
-        <v>6790776</v>
+        <v>6790598</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,19 +2455,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,19 +2472,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122908082</v>
+        <v>122907426</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2520,17 +2520,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480607</v>
+        <v>480611</v>
       </c>
       <c r="R19" t="n">
-        <v>6790687</v>
+        <v>6790803</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,19 +2584,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122908448</v>
+        <v>122910462</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480628</v>
+        <v>480753</v>
       </c>
       <c r="R20" t="n">
-        <v>6790661</v>
+        <v>6790776</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122910257</v>
+        <v>122908082</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480680</v>
+        <v>480607</v>
       </c>
       <c r="R21" t="n">
-        <v>6790662</v>
+        <v>6790687</v>
       </c>
       <c r="S21" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,12 +2808,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122910507</v>
+        <v>122909085</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5186,25 +5186,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5214,13 +5214,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480751</v>
+        <v>480626</v>
       </c>
       <c r="R44" t="n">
-        <v>6790806</v>
+        <v>6790648</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5286,7 +5286,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122914329</v>
+        <v>122910507</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5326,13 +5326,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481184</v>
+        <v>480751</v>
       </c>
       <c r="R45" t="n">
-        <v>6790659</v>
+        <v>6790806</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,19 +5386,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122908626</v>
+        <v>122914329</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5434,17 +5434,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480639</v>
+        <v>481184</v>
       </c>
       <c r="R46" t="n">
-        <v>6790797</v>
+        <v>6790659</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5498,19 +5498,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122908091</v>
+        <v>122908626</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5546,17 +5546,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480631</v>
+        <v>480639</v>
       </c>
       <c r="R47" t="n">
-        <v>6790746</v>
+        <v>6790797</v>
       </c>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5610,19 +5610,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122913095</v>
+        <v>122908091</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5658,17 +5658,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480874</v>
+        <v>480631</v>
       </c>
       <c r="R48" t="n">
-        <v>6790659</v>
+        <v>6790746</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5695,9 +5695,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5712,19 +5722,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122911334</v>
+        <v>122913095</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5760,14 +5770,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481021</v>
+        <v>480874</v>
       </c>
       <c r="R49" t="n">
-        <v>6790761</v>
+        <v>6790659</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5797,19 +5807,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5824,19 +5824,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122908184</v>
+        <v>122911334</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5872,14 +5872,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480755</v>
+        <v>481021</v>
       </c>
       <c r="R50" t="n">
-        <v>6790542</v>
+        <v>6790761</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5909,9 +5909,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,19 +5936,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122914293</v>
+        <v>122908184</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5974,17 +5984,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481318</v>
+        <v>480755</v>
       </c>
       <c r="R51" t="n">
-        <v>6790679</v>
+        <v>6790542</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6011,19 +6021,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6038,22 +6038,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122915259</v>
+        <v>122914293</v>
       </c>
       <c r="B52" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6066,40 +6066,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480813</v>
+        <v>481318</v>
       </c>
       <c r="R52" t="n">
-        <v>6790675</v>
+        <v>6790679</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6128,7 +6125,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6138,7 +6135,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6147,29 +6144,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122908311</v>
+        <v>122915259</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6182,37 +6178,40 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480715</v>
+        <v>480813</v>
       </c>
       <c r="R53" t="n">
-        <v>6790533</v>
+        <v>6790675</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6239,36 +6238,47 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122916963</v>
+        <v>122908311</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6308,10 +6318,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481367</v>
+        <v>480715</v>
       </c>
       <c r="R54" t="n">
-        <v>6790497</v>
+        <v>6790533</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,11 +6354,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I området här återkommer garnlaven konstant.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6375,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122908784</v>
+        <v>122916963</v>
       </c>
       <c r="B55" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6391,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6415,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480639</v>
+        <v>481367</v>
       </c>
       <c r="R55" t="n">
-        <v>6790797</v>
+        <v>6790497</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6448,19 +6453,14 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:32</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I området här återkommer garnlaven konstant.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6475,22 +6475,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122909085</v>
+        <v>122908784</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6499,38 +6499,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480626</v>
+        <v>480639</v>
       </c>
       <c r="R56" t="n">
-        <v>6790648</v>
+        <v>6790797</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6587,12 +6587,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -10755,7 +10755,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122914138</v>
+        <v>122907225</v>
       </c>
       <c r="B96" t="n">
         <v>78766</v>
@@ -10791,17 +10791,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480858</v>
+        <v>480622</v>
       </c>
       <c r="R96" t="n">
-        <v>6790672</v>
+        <v>6790776</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10828,9 +10828,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10845,22 +10855,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122907225</v>
+        <v>122907291</v>
       </c>
       <c r="B97" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10873,37 +10883,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480622</v>
+        <v>480712</v>
       </c>
       <c r="R97" t="n">
-        <v>6790776</v>
+        <v>6790625</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10930,19 +10940,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10957,22 +10957,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122907291</v>
+        <v>122916381</v>
       </c>
       <c r="B98" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480712</v>
+        <v>481294</v>
       </c>
       <c r="R98" t="n">
-        <v>6790625</v>
+        <v>6790587</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122916381</v>
+        <v>122908412</v>
       </c>
       <c r="B99" t="n">
         <v>78766</v>
@@ -11111,10 +11111,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481294</v>
+        <v>480722</v>
       </c>
       <c r="R99" t="n">
-        <v>6790587</v>
+        <v>6790508</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11173,10 +11173,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122908412</v>
+        <v>122908658</v>
       </c>
       <c r="B100" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11185,41 +11185,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480722</v>
+        <v>480701</v>
       </c>
       <c r="R100" t="n">
-        <v>6790508</v>
+        <v>6790532</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11246,9 +11246,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11263,22 +11273,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122908658</v>
+        <v>122914138</v>
       </c>
       <c r="B101" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11287,41 +11297,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480701</v>
+        <v>480858</v>
       </c>
       <c r="R101" t="n">
-        <v>6790532</v>
+        <v>6790672</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11348,19 +11358,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11375,12 +11375,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122909048</v>
+        <v>122915938</v>
       </c>
       <c r="B111" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12357,47 +12357,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480660</v>
+        <v>481166</v>
       </c>
       <c r="R111" t="n">
-        <v>6790681</v>
+        <v>6790560</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12427,47 +12418,36 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122915938</v>
+        <v>122914812</v>
       </c>
       <c r="B112" t="n">
         <v>78766</v>
@@ -12507,10 +12487,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>481166</v>
+        <v>480982</v>
       </c>
       <c r="R112" t="n">
-        <v>6790560</v>
+        <v>6790653</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12569,7 +12549,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122914812</v>
+        <v>122913854</v>
       </c>
       <c r="B113" t="n">
         <v>78766</v>
@@ -12605,17 +12585,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480982</v>
+        <v>481200</v>
       </c>
       <c r="R113" t="n">
-        <v>6790653</v>
+        <v>6790675</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12642,9 +12622,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12659,19 +12649,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122913854</v>
+        <v>122905918</v>
       </c>
       <c r="B114" t="n">
         <v>78766</v>
@@ -12707,17 +12697,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>481200</v>
+        <v>480680</v>
       </c>
       <c r="R114" t="n">
-        <v>6790675</v>
+        <v>6790718</v>
       </c>
       <c r="S114" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12744,19 +12734,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12771,19 +12751,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122905918</v>
+        <v>122906898</v>
       </c>
       <c r="B115" t="n">
         <v>78766</v>
@@ -12823,10 +12803,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>480680</v>
+        <v>480720</v>
       </c>
       <c r="R115" t="n">
-        <v>6790718</v>
+        <v>6790668</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12885,7 +12865,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122906898</v>
+        <v>122917077</v>
       </c>
       <c r="B116" t="n">
         <v>78766</v>
@@ -12925,10 +12905,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>480720</v>
+        <v>481414</v>
       </c>
       <c r="R116" t="n">
-        <v>6790668</v>
+        <v>6790487</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12987,7 +12967,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122917077</v>
+        <v>122911564</v>
       </c>
       <c r="B117" t="n">
         <v>78766</v>
@@ -13023,17 +13003,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>481414</v>
+        <v>481081</v>
       </c>
       <c r="R117" t="n">
-        <v>6790487</v>
+        <v>6790749</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13060,9 +13040,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13077,19 +13067,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122911564</v>
+        <v>122914493</v>
       </c>
       <c r="B118" t="n">
         <v>78766</v>
@@ -13129,10 +13119,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>481081</v>
+        <v>481040</v>
       </c>
       <c r="R118" t="n">
-        <v>6790749</v>
+        <v>6790686</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13164,7 +13154,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13174,7 +13164,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13201,7 +13191,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122914493</v>
+        <v>122915272</v>
       </c>
       <c r="B119" t="n">
         <v>78766</v>
@@ -13237,17 +13227,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>481040</v>
+        <v>481024</v>
       </c>
       <c r="R119" t="n">
-        <v>6790686</v>
+        <v>6790673</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13274,19 +13264,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>15:47</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13301,19 +13281,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122915272</v>
+        <v>122907348</v>
       </c>
       <c r="B120" t="n">
         <v>78766</v>
@@ -13353,10 +13333,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>481024</v>
+        <v>480716</v>
       </c>
       <c r="R120" t="n">
-        <v>6790673</v>
+        <v>6790617</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13415,10 +13395,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122907348</v>
+        <v>122909048</v>
       </c>
       <c r="B121" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13427,38 +13407,47 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>480716</v>
+        <v>480660</v>
       </c>
       <c r="R121" t="n">
-        <v>6790617</v>
+        <v>6790681</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13488,29 +13477,40 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -17885,10 +17885,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122910464</v>
+        <v>122914178</v>
       </c>
       <c r="B163" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17897,38 +17897,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>480751</v>
+        <v>480864</v>
       </c>
       <c r="R163" t="n">
-        <v>6790806</v>
+        <v>6790682</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17958,19 +17958,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17985,19 +17975,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122914178</v>
+        <v>122910505</v>
       </c>
       <c r="B164" t="n">
         <v>78766</v>
@@ -18037,10 +18027,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>480864</v>
+        <v>480770</v>
       </c>
       <c r="R164" t="n">
-        <v>6790682</v>
+        <v>6790637</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18099,10 +18089,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122910505</v>
+        <v>122915104</v>
       </c>
       <c r="B165" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18111,41 +18101,46 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>480770</v>
+        <v>480783</v>
       </c>
       <c r="R165" t="n">
-        <v>6790637</v>
+        <v>6790712</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18172,9 +18167,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18189,22 +18194,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122915104</v>
+        <v>122910464</v>
       </c>
       <c r="B166" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18217,42 +18222,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>480783</v>
+        <v>480751</v>
       </c>
       <c r="R166" t="n">
-        <v>6790712</v>
+        <v>6790806</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18306,22 +18306,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122905650</v>
+        <v>122914092</v>
       </c>
       <c r="B167" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18330,41 +18330,41 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>480698</v>
+        <v>481216</v>
       </c>
       <c r="R167" t="n">
-        <v>6790762</v>
+        <v>6790675</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18391,9 +18391,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18408,22 +18418,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122905949</v>
+        <v>122908121</v>
       </c>
       <c r="B168" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18432,41 +18442,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>480710</v>
+        <v>480638</v>
       </c>
       <c r="R168" t="n">
-        <v>6790729</v>
+        <v>6790738</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18493,9 +18503,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18510,22 +18530,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122911611</v>
+        <v>122908063</v>
       </c>
       <c r="B169" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18534,25 +18554,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18562,13 +18582,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>481072</v>
+        <v>480571</v>
       </c>
       <c r="R169" t="n">
-        <v>6790731</v>
+        <v>6790798</v>
       </c>
       <c r="S169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18597,7 +18617,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18607,7 +18627,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18634,10 +18654,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122914092</v>
+        <v>122905650</v>
       </c>
       <c r="B170" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18646,41 +18666,41 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>481216</v>
+        <v>480698</v>
       </c>
       <c r="R170" t="n">
-        <v>6790675</v>
+        <v>6790762</v>
       </c>
       <c r="S170" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18707,19 +18727,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18734,22 +18744,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122908121</v>
+        <v>122905949</v>
       </c>
       <c r="B171" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18758,41 +18768,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>480638</v>
+        <v>480710</v>
       </c>
       <c r="R171" t="n">
-        <v>6790738</v>
+        <v>6790729</v>
       </c>
       <c r="S171" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18819,19 +18829,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18846,22 +18846,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122908063</v>
+        <v>122911611</v>
       </c>
       <c r="B172" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18870,25 +18870,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18898,13 +18898,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>480571</v>
+        <v>481072</v>
       </c>
       <c r="R172" t="n">
-        <v>6790798</v>
+        <v>6790731</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21110,7 +21110,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122962209</v>
+        <v>122977907</v>
       </c>
       <c r="B193" t="n">
         <v>78766</v>
@@ -21146,17 +21146,17 @@
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>480818</v>
+        <v>481302</v>
       </c>
       <c r="R193" t="n">
-        <v>6790633</v>
+        <v>6790744</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21183,9 +21183,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21200,19 +21210,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122978156</v>
+        <v>122961980</v>
       </c>
       <c r="B194" t="n">
         <v>78766</v>
@@ -21252,10 +21262,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>481151</v>
+        <v>480790</v>
       </c>
       <c r="R194" t="n">
-        <v>6790744</v>
+        <v>6790654</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21288,11 +21298,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Garn synligt i radie 50 meter.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21319,7 +21324,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122970352</v>
+        <v>122959766</v>
       </c>
       <c r="B195" t="n">
         <v>78766</v>
@@ -21359,10 +21364,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>481566</v>
+        <v>480779</v>
       </c>
       <c r="R195" t="n">
-        <v>6790511</v>
+        <v>6790803</v>
       </c>
       <c r="S195" t="n">
         <v>9</v>
@@ -21394,7 +21399,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21404,7 +21409,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21548,10 +21553,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122961952</v>
+        <v>122962209</v>
       </c>
       <c r="B197" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21560,46 +21565,41 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>480782</v>
+        <v>480818</v>
       </c>
       <c r="R197" t="n">
-        <v>6790637</v>
+        <v>6790633</v>
       </c>
       <c r="S197" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21626,24 +21626,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Grov tall</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21658,22 +21643,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122970166</v>
+        <v>122978156</v>
       </c>
       <c r="B198" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21682,46 +21667,41 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>481546</v>
+        <v>481151</v>
       </c>
       <c r="R198" t="n">
-        <v>6790501</v>
+        <v>6790744</v>
       </c>
       <c r="S198" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21748,19 +21728,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>14:08</t>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Garn synligt i radie 50 meter.</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21775,19 +21750,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122977907</v>
+        <v>122970352</v>
       </c>
       <c r="B199" t="n">
         <v>78766</v>
@@ -21827,10 +21802,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>481302</v>
+        <v>481566</v>
       </c>
       <c r="R199" t="n">
-        <v>6790744</v>
+        <v>6790511</v>
       </c>
       <c r="S199" t="n">
         <v>9</v>
@@ -21862,7 +21837,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21872,7 +21847,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21899,10 +21874,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122961980</v>
+        <v>122961952</v>
       </c>
       <c r="B200" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21911,41 +21886,46 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>480790</v>
+        <v>480782</v>
       </c>
       <c r="R200" t="n">
-        <v>6790654</v>
+        <v>6790637</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21972,9 +21952,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Grov tall</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21989,22 +21984,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122959766</v>
+        <v>122970166</v>
       </c>
       <c r="B201" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22013,38 +22008,43 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>480779</v>
+        <v>481546</v>
       </c>
       <c r="R201" t="n">
-        <v>6790803</v>
+        <v>6790501</v>
       </c>
       <c r="S201" t="n">
         <v>9</v>
@@ -22076,7 +22076,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27874,10 +27874,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122978194</v>
+        <v>122960352</v>
       </c>
       <c r="B255" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -27886,46 +27886,41 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>481090</v>
+        <v>480778</v>
       </c>
       <c r="R255" t="n">
-        <v>6790709</v>
+        <v>6790784</v>
       </c>
       <c r="S255" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -27952,19 +27947,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>17:25</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27979,19 +27964,19 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122960352</v>
+        <v>122966180</v>
       </c>
       <c r="B256" t="n">
         <v>78766</v>
@@ -28027,17 +28012,17 @@
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>480778</v>
+        <v>481151</v>
       </c>
       <c r="R256" t="n">
-        <v>6790784</v>
+        <v>6790709</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -28064,9 +28049,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -28081,19 +28076,19 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122966180</v>
+        <v>122965694</v>
       </c>
       <c r="B257" t="n">
         <v>78766</v>
@@ -28133,10 +28128,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>481151</v>
+        <v>481111</v>
       </c>
       <c r="R257" t="n">
-        <v>6790709</v>
+        <v>6790702</v>
       </c>
       <c r="S257" t="n">
         <v>9</v>
@@ -28168,7 +28163,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -28178,7 +28173,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -28205,7 +28200,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122965694</v>
+        <v>122970196</v>
       </c>
       <c r="B258" t="n">
         <v>78766</v>
@@ -28241,17 +28236,17 @@
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>481111</v>
+        <v>481598</v>
       </c>
       <c r="R258" t="n">
-        <v>6790702</v>
+        <v>6790481</v>
       </c>
       <c r="S258" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -28278,19 +28273,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -28305,19 +28290,19 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122975526</v>
+        <v>122960406</v>
       </c>
       <c r="B259" t="n">
         <v>78766</v>
@@ -28353,14 +28338,14 @@
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>481420</v>
+        <v>480766</v>
       </c>
       <c r="R259" t="n">
-        <v>6790760</v>
+        <v>6790785</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28419,7 +28404,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122961172</v>
+        <v>122960562</v>
       </c>
       <c r="B260" t="n">
         <v>78766</v>
@@ -28459,10 +28444,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>480745</v>
+        <v>480756</v>
       </c>
       <c r="R260" t="n">
-        <v>6790759</v>
+        <v>6790775</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28521,10 +28506,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122970196</v>
+        <v>122978194</v>
       </c>
       <c r="B261" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -28533,41 +28518,46 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>481598</v>
+        <v>481090</v>
       </c>
       <c r="R261" t="n">
-        <v>6790481</v>
+        <v>6790709</v>
       </c>
       <c r="S261" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -28594,9 +28584,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -28611,22 +28611,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122960406</v>
+        <v>122965792</v>
       </c>
       <c r="B262" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -28635,41 +28635,46 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>480766</v>
+        <v>481118</v>
       </c>
       <c r="R262" t="n">
-        <v>6790785</v>
+        <v>6790699</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -28696,9 +28701,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28713,19 +28728,19 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122960562</v>
+        <v>122975526</v>
       </c>
       <c r="B263" t="n">
         <v>78766</v>
@@ -28761,14 +28776,14 @@
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>480756</v>
+        <v>481420</v>
       </c>
       <c r="R263" t="n">
-        <v>6790775</v>
+        <v>6790760</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28827,10 +28842,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122965792</v>
+        <v>122961172</v>
       </c>
       <c r="B264" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -28839,46 +28854,41 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>481118</v>
+        <v>480745</v>
       </c>
       <c r="R264" t="n">
-        <v>6790699</v>
+        <v>6790759</v>
       </c>
       <c r="S264" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -28905,19 +28915,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28932,12 +28932,12 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
@@ -30014,10 +30014,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122970211</v>
+        <v>122964962</v>
       </c>
       <c r="B275" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -30026,25 +30026,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -30054,10 +30054,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>481559</v>
+        <v>481026</v>
       </c>
       <c r="R275" t="n">
-        <v>6790521</v>
+        <v>6790700</v>
       </c>
       <c r="S275" t="n">
         <v>9</v>
@@ -30089,7 +30089,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -30099,7 +30099,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -30126,7 +30126,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122968577</v>
+        <v>122970211</v>
       </c>
       <c r="B276" t="n">
         <v>78766</v>
@@ -30166,10 +30166,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>481434</v>
+        <v>481559</v>
       </c>
       <c r="R276" t="n">
-        <v>6790538</v>
+        <v>6790521</v>
       </c>
       <c r="S276" t="n">
         <v>9</v>
@@ -30201,7 +30201,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -30238,10 +30238,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122964962</v>
+        <v>122968577</v>
       </c>
       <c r="B277" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -30250,25 +30250,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -30278,10 +30278,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>481026</v>
+        <v>481434</v>
       </c>
       <c r="R277" t="n">
-        <v>6790700</v>
+        <v>6790538</v>
       </c>
       <c r="S277" t="n">
         <v>9</v>
@@ -30313,7 +30313,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -30323,7 +30323,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -30350,10 +30350,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122961494</v>
+        <v>122965865</v>
       </c>
       <c r="B278" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -30366,37 +30366,42 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>480772</v>
+        <v>481118</v>
       </c>
       <c r="R278" t="n">
-        <v>6790705</v>
+        <v>6790699</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -30423,9 +30428,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30440,12 +30455,12 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
@@ -30564,10 +30579,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122965865</v>
+        <v>122961494</v>
       </c>
       <c r="B280" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -30580,42 +30595,37 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>481118</v>
+        <v>480772</v>
       </c>
       <c r="R280" t="n">
-        <v>6790699</v>
+        <v>6790705</v>
       </c>
       <c r="S280" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -30642,19 +30652,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30669,19 +30669,19 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122968533</v>
+        <v>122959889</v>
       </c>
       <c r="B281" t="n">
         <v>78766</v>
@@ -30717,17 +30717,17 @@
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>481432</v>
+        <v>480792</v>
       </c>
       <c r="R281" t="n">
-        <v>6790537</v>
+        <v>6790812</v>
       </c>
       <c r="S281" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -30754,19 +30754,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>13:34</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30781,22 +30771,22 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122968051</v>
+        <v>122962565</v>
       </c>
       <c r="B282" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -30809,21 +30799,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -30833,10 +30823,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>481370</v>
+        <v>480854</v>
       </c>
       <c r="R282" t="n">
-        <v>6790557</v>
+        <v>6790625</v>
       </c>
       <c r="S282" t="n">
         <v>9</v>
@@ -30868,7 +30858,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -30878,7 +30868,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30905,10 +30895,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122973653</v>
+        <v>122967628</v>
       </c>
       <c r="B283" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -30921,37 +30911,42 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>481479</v>
+        <v>481264</v>
       </c>
       <c r="R283" t="n">
-        <v>6790535</v>
+        <v>6790665</v>
       </c>
       <c r="S283" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -30978,9 +30973,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -30995,22 +31000,22 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122959889</v>
+        <v>122969848</v>
       </c>
       <c r="B284" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -31023,16 +31028,16 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -31047,10 +31052,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>480792</v>
+        <v>481544</v>
       </c>
       <c r="R284" t="n">
-        <v>6790812</v>
+        <v>6790494</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -31083,6 +31088,11 @@
       <c r="AA284" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -31109,10 +31119,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122962565</v>
+        <v>122968533</v>
       </c>
       <c r="B285" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31125,21 +31135,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -31149,10 +31159,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>480854</v>
+        <v>481432</v>
       </c>
       <c r="R285" t="n">
-        <v>6790625</v>
+        <v>6790537</v>
       </c>
       <c r="S285" t="n">
         <v>9</v>
@@ -31184,7 +31194,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -31194,7 +31204,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -31221,10 +31231,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122967628</v>
+        <v>122968051</v>
       </c>
       <c r="B286" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -31237,42 +31247,37 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>481264</v>
+        <v>481370</v>
       </c>
       <c r="R286" t="n">
-        <v>6790665</v>
+        <v>6790557</v>
       </c>
       <c r="S286" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -31301,7 +31306,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -31311,7 +31316,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -31338,10 +31343,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122969848</v>
+        <v>122973653</v>
       </c>
       <c r="B287" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -31354,16 +31359,16 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -31378,10 +31383,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>481544</v>
+        <v>481479</v>
       </c>
       <c r="R287" t="n">
-        <v>6790494</v>
+        <v>6790535</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -31414,11 +31419,6 @@
       <c r="AA287" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC287" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD287" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122913962</v>
+        <v>122916590</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,37 +1858,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481216</v>
+        <v>481290</v>
       </c>
       <c r="R13" t="n">
-        <v>6790675</v>
+        <v>6790576</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,19 +1915,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,19 +1932,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122909092</v>
+        <v>122913962</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1994,13 +1984,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480626</v>
+        <v>481216</v>
       </c>
       <c r="R14" t="n">
-        <v>6790648</v>
+        <v>6790675</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122905837</v>
+        <v>122909092</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2102,14 +2092,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480679</v>
+        <v>480626</v>
       </c>
       <c r="R15" t="n">
-        <v>6790740</v>
+        <v>6790648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,9 +2129,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,19 +2156,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122910548</v>
+        <v>122905837</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480772</v>
+        <v>480679</v>
       </c>
       <c r="R16" t="n">
-        <v>6790619</v>
+        <v>6790740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122905869</v>
+        <v>122910548</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480680</v>
+        <v>480772</v>
       </c>
       <c r="R17" t="n">
-        <v>6790718</v>
+        <v>6790619</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122908448</v>
+        <v>122905869</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2408,17 +2408,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480628</v>
+        <v>480680</v>
       </c>
       <c r="R18" t="n">
-        <v>6790661</v>
+        <v>6790718</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,19 +2445,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,19 +2462,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122914072</v>
+        <v>122908448</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2520,17 +2510,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480839</v>
+        <v>480628</v>
       </c>
       <c r="R19" t="n">
-        <v>6790677</v>
+        <v>6790661</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,9 +2547,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,19 +2574,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122908724</v>
+        <v>122914072</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480766</v>
+        <v>480839</v>
       </c>
       <c r="R20" t="n">
-        <v>6790505</v>
+        <v>6790677</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122913997</v>
+        <v>122908724</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2724,17 +2724,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481407</v>
+        <v>480766</v>
       </c>
       <c r="R21" t="n">
-        <v>6790724</v>
+        <v>6790505</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2761,19 +2761,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2788,19 +2778,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122916356</v>
+        <v>122913997</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2836,17 +2826,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481274</v>
+        <v>481407</v>
       </c>
       <c r="R22" t="n">
-        <v>6790592</v>
+        <v>6790724</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2873,9 +2863,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,19 +2890,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122909144</v>
+        <v>122916356</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480738</v>
+        <v>481274</v>
       </c>
       <c r="R23" t="n">
-        <v>6790666</v>
+        <v>6790592</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122914177</v>
+        <v>122909144</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3040,17 +3040,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481318</v>
+        <v>480738</v>
       </c>
       <c r="R24" t="n">
-        <v>6790679</v>
+        <v>6790666</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3077,19 +3077,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3104,19 +3094,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122914120</v>
+        <v>122914177</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3156,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481399</v>
+        <v>481318</v>
       </c>
       <c r="R25" t="n">
-        <v>6790701</v>
+        <v>6790679</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3191,7 +3181,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3201,7 +3191,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122915091</v>
+        <v>122914120</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3264,17 +3254,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480681</v>
+        <v>481399</v>
       </c>
       <c r="R26" t="n">
-        <v>6790816</v>
+        <v>6790701</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3303,7 +3293,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3303,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,22 +3318,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122916590</v>
+        <v>122915091</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481290</v>
+        <v>480681</v>
       </c>
       <c r="R27" t="n">
-        <v>6790576</v>
+        <v>6790816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,9 +3403,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,12 +3430,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122911564</v>
+        <v>122907818</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481081</v>
+        <v>480545</v>
       </c>
       <c r="R29" t="n">
-        <v>6790749</v>
+        <v>6790776</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122914046</v>
+        <v>122910507</v>
       </c>
       <c r="B30" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,46 +3668,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480839</v>
+        <v>480751</v>
       </c>
       <c r="R30" t="n">
-        <v>6790677</v>
+        <v>6790806</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3734,9 +3729,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,19 +3756,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122910507</v>
+        <v>122916780</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3799,17 +3804,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480751</v>
+        <v>481324</v>
       </c>
       <c r="R31" t="n">
-        <v>6790806</v>
+        <v>6790518</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3836,19 +3841,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,19 +3858,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122916780</v>
+        <v>122915292</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3911,17 +3906,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481324</v>
+        <v>480729</v>
       </c>
       <c r="R32" t="n">
-        <v>6790518</v>
+        <v>6790767</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3948,9 +3943,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3965,19 +3970,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122915292</v>
+        <v>122913918</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4017,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480729</v>
+        <v>481291</v>
       </c>
       <c r="R33" t="n">
-        <v>6790767</v>
+        <v>6790740</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,7 +4057,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4062,7 +4067,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4089,7 +4094,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122913918</v>
+        <v>122910443</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4129,13 +4134,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481291</v>
+        <v>480743</v>
       </c>
       <c r="R34" t="n">
-        <v>6790740</v>
+        <v>6790781</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4164,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4174,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4201,7 +4206,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122907818</v>
+        <v>122917054</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4237,17 +4242,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480545</v>
+        <v>481414</v>
       </c>
       <c r="R35" t="n">
-        <v>6790776</v>
+        <v>6790487</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4274,19 +4279,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4301,22 +4296,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122910443</v>
+        <v>122914046</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4325,38 +4320,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480743</v>
+        <v>480839</v>
       </c>
       <c r="R36" t="n">
-        <v>6790781</v>
+        <v>6790677</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4386,19 +4386,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4413,19 +4403,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122917054</v>
+        <v>122907468</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4465,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481414</v>
+        <v>480739</v>
       </c>
       <c r="R37" t="n">
-        <v>6790487</v>
+        <v>6790609</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4527,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122907468</v>
+        <v>122911564</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4563,17 +4553,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480739</v>
+        <v>481081</v>
       </c>
       <c r="R38" t="n">
-        <v>6790609</v>
+        <v>6790749</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4600,9 +4590,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4617,12 +4617,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122908690</v>
+        <v>122911238</v>
       </c>
       <c r="B57" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6581,21 +6581,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480626</v>
+        <v>481009</v>
       </c>
       <c r="R57" t="n">
-        <v>6790648</v>
+        <v>6790696</v>
       </c>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6665,19 +6665,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122911238</v>
+        <v>122905949</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6713,14 +6713,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481009</v>
+        <v>480710</v>
       </c>
       <c r="R58" t="n">
-        <v>6790696</v>
+        <v>6790729</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,19 +6750,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,19 +6767,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122905949</v>
+        <v>122911477</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6825,14 +6815,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480710</v>
+        <v>481096</v>
       </c>
       <c r="R59" t="n">
-        <v>6790729</v>
+        <v>6790743</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6862,9 +6852,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6879,19 +6879,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122911477</v>
+        <v>122908184</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6927,14 +6927,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481096</v>
+        <v>480755</v>
       </c>
       <c r="R60" t="n">
-        <v>6790743</v>
+        <v>6790542</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,19 +6964,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,19 +6981,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122908184</v>
+        <v>122910493</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -7039,14 +7029,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>480755</v>
       </c>
       <c r="R61" t="n">
-        <v>6790542</v>
+        <v>6790775</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,9 +7066,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7093,19 +7093,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122910493</v>
+        <v>122908087</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -7141,14 +7141,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480755</v>
+        <v>480758</v>
       </c>
       <c r="R62" t="n">
-        <v>6790775</v>
+        <v>6790557</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,19 +7178,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7205,19 +7195,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122908087</v>
+        <v>122910277</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -7253,14 +7243,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480758</v>
+        <v>480738</v>
       </c>
       <c r="R63" t="n">
-        <v>6790557</v>
+        <v>6790786</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7290,9 +7280,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7307,19 +7307,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122910277</v>
+        <v>122908626</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7355,14 +7355,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480738</v>
+        <v>480639</v>
       </c>
       <c r="R64" t="n">
-        <v>6790786</v>
+        <v>6790797</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7419,19 +7419,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122908626</v>
+        <v>122906741</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480639</v>
+        <v>480726</v>
       </c>
       <c r="R65" t="n">
-        <v>6790797</v>
+        <v>6790689</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7504,19 +7504,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7531,22 +7521,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122906741</v>
+        <v>122908690</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7559,37 +7549,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480726</v>
+        <v>480626</v>
       </c>
       <c r="R66" t="n">
-        <v>6790689</v>
+        <v>6790648</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7616,9 +7606,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7633,22 +7633,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122915083</v>
+        <v>122906797</v>
       </c>
       <c r="B67" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7657,46 +7657,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480681</v>
+        <v>480720</v>
       </c>
       <c r="R67" t="n">
-        <v>6790816</v>
+        <v>6790668</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7726,19 +7718,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7753,19 +7735,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122910575</v>
+        <v>122915163</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7805,10 +7787,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480772</v>
+        <v>480988</v>
       </c>
       <c r="R68" t="n">
-        <v>6790602</v>
+        <v>6790673</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7867,7 +7849,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122908102</v>
+        <v>122913871</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7907,10 +7889,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480607</v>
+        <v>481264</v>
       </c>
       <c r="R69" t="n">
-        <v>6790683</v>
+        <v>6790709</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7942,7 +7924,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7952,7 +7934,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7979,7 +7961,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122908412</v>
+        <v>122916548</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -8019,10 +8001,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480722</v>
+        <v>481290</v>
       </c>
       <c r="R70" t="n">
-        <v>6790508</v>
+        <v>6790576</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8081,7 +8063,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122910326</v>
+        <v>122915938</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8121,10 +8103,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480759</v>
+        <v>481166</v>
       </c>
       <c r="R71" t="n">
-        <v>6790654</v>
+        <v>6790560</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8183,7 +8165,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122906797</v>
+        <v>122910575</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -8223,10 +8205,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480720</v>
+        <v>480772</v>
       </c>
       <c r="R72" t="n">
-        <v>6790668</v>
+        <v>6790602</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8285,7 +8267,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122915163</v>
+        <v>122908102</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -8321,17 +8303,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480988</v>
+        <v>480607</v>
       </c>
       <c r="R73" t="n">
-        <v>6790673</v>
+        <v>6790683</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8358,9 +8340,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8375,19 +8367,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122913871</v>
+        <v>122914256</v>
       </c>
       <c r="B74" t="n">
         <v>78766</v>
@@ -8423,17 +8415,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481264</v>
+        <v>480858</v>
       </c>
       <c r="R74" t="n">
-        <v>6790709</v>
+        <v>6790672</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8460,19 +8452,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8487,19 +8469,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122916548</v>
+        <v>122908412</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8539,10 +8521,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481290</v>
+        <v>480722</v>
       </c>
       <c r="R75" t="n">
-        <v>6790576</v>
+        <v>6790508</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8601,7 +8583,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122915938</v>
+        <v>122910326</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -8641,10 +8623,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481166</v>
+        <v>480759</v>
       </c>
       <c r="R76" t="n">
-        <v>6790560</v>
+        <v>6790654</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8703,10 +8685,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122914256</v>
+        <v>122915083</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8715,38 +8697,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480858</v>
+        <v>480681</v>
       </c>
       <c r="R77" t="n">
-        <v>6790672</v>
+        <v>6790816</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8776,9 +8766,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8793,12 +8793,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122913869</v>
+        <v>122907941</v>
       </c>
       <c r="B101" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11276,39 +11276,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480861</v>
+        <v>480736</v>
       </c>
       <c r="R101" t="n">
-        <v>6790634</v>
+        <v>6790589</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11367,10 +11362,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122913735</v>
+        <v>122910488</v>
       </c>
       <c r="B102" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11383,37 +11378,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>481068</v>
+        <v>480764</v>
       </c>
       <c r="R102" t="n">
-        <v>6790734</v>
+        <v>6790646</v>
       </c>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11440,19 +11435,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11467,19 +11452,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122907941</v>
+        <v>122912843</v>
       </c>
       <c r="B103" t="n">
         <v>78766</v>
@@ -11515,17 +11500,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>480736</v>
+        <v>481068</v>
       </c>
       <c r="R103" t="n">
-        <v>6790589</v>
+        <v>6790734</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11552,9 +11537,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11569,19 +11564,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122910488</v>
+        <v>122916802</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11621,10 +11616,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>480764</v>
+        <v>481344</v>
       </c>
       <c r="R104" t="n">
-        <v>6790646</v>
+        <v>6790501</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11683,7 +11678,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122912843</v>
+        <v>122905737</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -11719,17 +11714,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>481068</v>
+        <v>480697</v>
       </c>
       <c r="R105" t="n">
-        <v>6790734</v>
+        <v>6790747</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11756,19 +11751,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11783,19 +11768,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122916802</v>
+        <v>122915404</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -11835,10 +11820,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>481344</v>
+        <v>481062</v>
       </c>
       <c r="R106" t="n">
-        <v>6790501</v>
+        <v>6790666</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11897,7 +11882,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122905737</v>
+        <v>122908311</v>
       </c>
       <c r="B107" t="n">
         <v>78766</v>
@@ -11937,10 +11922,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480697</v>
+        <v>480715</v>
       </c>
       <c r="R107" t="n">
-        <v>6790747</v>
+        <v>6790533</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11999,7 +11984,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122915404</v>
+        <v>122914926</v>
       </c>
       <c r="B108" t="n">
         <v>78766</v>
@@ -12035,17 +12020,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>481062</v>
+        <v>480847</v>
       </c>
       <c r="R108" t="n">
-        <v>6790666</v>
+        <v>6790698</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12072,9 +12057,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12089,19 +12084,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122908311</v>
+        <v>122914178</v>
       </c>
       <c r="B109" t="n">
         <v>78766</v>
@@ -12141,10 +12136,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480715</v>
+        <v>480864</v>
       </c>
       <c r="R109" t="n">
-        <v>6790533</v>
+        <v>6790682</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12203,10 +12198,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122914926</v>
+        <v>122913735</v>
       </c>
       <c r="B110" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12219,21 +12214,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12243,13 +12238,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480847</v>
+        <v>481068</v>
       </c>
       <c r="R110" t="n">
-        <v>6790698</v>
+        <v>6790734</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12278,7 +12273,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12288,7 +12283,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12303,22 +12298,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122914178</v>
+        <v>122913869</v>
       </c>
       <c r="B111" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12331,34 +12326,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480864</v>
+        <v>480861</v>
       </c>
       <c r="R111" t="n">
-        <v>6790682</v>
+        <v>6790634</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15110,10 +15110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122915881</v>
+        <v>122914997</v>
       </c>
       <c r="B137" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15122,41 +15122,49 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>481164</v>
+        <v>480873</v>
       </c>
       <c r="R137" t="n">
-        <v>6790573</v>
+        <v>6790694</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15183,9 +15191,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15200,19 +15218,19 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>122911334</v>
+        <v>122915881</v>
       </c>
       <c r="B138" t="n">
         <v>78766</v>
@@ -15248,14 +15266,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>481021</v>
+        <v>481164</v>
       </c>
       <c r="R138" t="n">
-        <v>6790761</v>
+        <v>6790573</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15285,19 +15303,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15312,19 +15320,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122915272</v>
+        <v>122911334</v>
       </c>
       <c r="B139" t="n">
         <v>78766</v>
@@ -15360,14 +15368,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>481024</v>
+        <v>481021</v>
       </c>
       <c r="R139" t="n">
-        <v>6790673</v>
+        <v>6790761</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15397,9 +15405,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15414,22 +15432,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122911766</v>
+        <v>122915272</v>
       </c>
       <c r="B140" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15442,34 +15460,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>481068</v>
+        <v>481024</v>
       </c>
       <c r="R140" t="n">
-        <v>6790734</v>
+        <v>6790673</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15499,19 +15517,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15526,22 +15534,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122913943</v>
+        <v>122911766</v>
       </c>
       <c r="B141" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15554,34 +15562,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>480817</v>
+        <v>481068</v>
       </c>
       <c r="R141" t="n">
-        <v>6790670</v>
+        <v>6790734</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15611,9 +15619,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15628,19 +15646,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>122908242</v>
+        <v>122913943</v>
       </c>
       <c r="B142" t="n">
         <v>78766</v>
@@ -15680,10 +15698,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>480743</v>
+        <v>480817</v>
       </c>
       <c r="R142" t="n">
-        <v>6790542</v>
+        <v>6790670</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15742,10 +15760,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122914997</v>
+        <v>122908242</v>
       </c>
       <c r="B143" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15754,49 +15772,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>480873</v>
+        <v>480743</v>
       </c>
       <c r="R143" t="n">
-        <v>6790694</v>
+        <v>6790542</v>
       </c>
       <c r="S143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15823,19 +15833,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15850,12 +15850,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -17696,10 +17696,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122915104</v>
+        <v>122908196</v>
       </c>
       <c r="B161" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17712,42 +17712,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>480783</v>
+        <v>480681</v>
       </c>
       <c r="R161" t="n">
-        <v>6790712</v>
+        <v>6790816</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17776,7 +17771,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17786,7 +17781,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17801,22 +17796,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122908196</v>
+        <v>122912665</v>
       </c>
       <c r="B162" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17825,25 +17820,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17853,10 +17848,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>480681</v>
+        <v>480861</v>
       </c>
       <c r="R162" t="n">
-        <v>6790816</v>
+        <v>6790634</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17886,19 +17881,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17913,19 +17898,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122912665</v>
+        <v>122914329</v>
       </c>
       <c r="B163" t="n">
         <v>78766</v>
@@ -17961,17 +17946,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>480861</v>
+        <v>481184</v>
       </c>
       <c r="R163" t="n">
-        <v>6790634</v>
+        <v>6790659</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17998,9 +17983,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18015,19 +18010,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122914329</v>
+        <v>122908480</v>
       </c>
       <c r="B164" t="n">
         <v>78766</v>
@@ -18063,17 +18058,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>481184</v>
+        <v>480744</v>
       </c>
       <c r="R164" t="n">
-        <v>6790659</v>
+        <v>6790521</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18100,19 +18095,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18127,19 +18112,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122908480</v>
+        <v>122914058</v>
       </c>
       <c r="B165" t="n">
         <v>78766</v>
@@ -18179,10 +18164,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>480744</v>
+        <v>480832</v>
       </c>
       <c r="R165" t="n">
-        <v>6790521</v>
+        <v>6790668</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18241,7 +18226,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122914058</v>
+        <v>122913893</v>
       </c>
       <c r="B166" t="n">
         <v>78766</v>
@@ -18277,17 +18262,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>480832</v>
+        <v>481268</v>
       </c>
       <c r="R166" t="n">
-        <v>6790668</v>
+        <v>6790734</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18314,9 +18299,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18331,22 +18326,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122913893</v>
+        <v>122915104</v>
       </c>
       <c r="B167" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18355,38 +18350,43 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>481268</v>
+        <v>480783</v>
       </c>
       <c r="R167" t="n">
-        <v>6790734</v>
+        <v>6790712</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -18418,7 +18418,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18455,7 +18455,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122908512</v>
+        <v>122908368</v>
       </c>
       <c r="B168" t="n">
         <v>78766</v>
@@ -18495,10 +18495,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>480749</v>
+        <v>480704</v>
       </c>
       <c r="R168" t="n">
-        <v>6790500</v>
+        <v>6790523</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18557,7 +18557,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122915490</v>
+        <v>122908512</v>
       </c>
       <c r="B169" t="n">
         <v>78766</v>
@@ -18597,10 +18597,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>481062</v>
+        <v>480749</v>
       </c>
       <c r="R169" t="n">
-        <v>6790617</v>
+        <v>6790500</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18659,7 +18659,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122905650</v>
+        <v>122915490</v>
       </c>
       <c r="B170" t="n">
         <v>78766</v>
@@ -18699,10 +18699,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>480698</v>
+        <v>481062</v>
       </c>
       <c r="R170" t="n">
-        <v>6790762</v>
+        <v>6790617</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18761,7 +18761,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122908368</v>
+        <v>122905650</v>
       </c>
       <c r="B171" t="n">
         <v>78766</v>
@@ -18801,10 +18801,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>480704</v>
+        <v>480698</v>
       </c>
       <c r="R171" t="n">
-        <v>6790523</v>
+        <v>6790762</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19602,10 +19602,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122908737</v>
+        <v>122913790</v>
       </c>
       <c r="B179" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19614,41 +19614,49 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>480772</v>
+        <v>481264</v>
       </c>
       <c r="R179" t="n">
-        <v>6790501</v>
+        <v>6790709</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19675,9 +19683,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19692,19 +19710,19 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122912740</v>
+        <v>122908737</v>
       </c>
       <c r="B180" t="n">
         <v>78766</v>
@@ -19744,13 +19762,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>481151</v>
+        <v>480772</v>
       </c>
       <c r="R180" t="n">
-        <v>6790720</v>
+        <v>6790501</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19777,19 +19795,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19804,19 +19812,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122914370</v>
+        <v>122912740</v>
       </c>
       <c r="B181" t="n">
         <v>78766</v>
@@ -19856,10 +19864,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>481130</v>
+        <v>481151</v>
       </c>
       <c r="R181" t="n">
-        <v>6790661</v>
+        <v>6790720</v>
       </c>
       <c r="S181" t="n">
         <v>15</v>
@@ -19891,7 +19899,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19901,7 +19909,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19928,10 +19936,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122907615</v>
+        <v>122914370</v>
       </c>
       <c r="B182" t="n">
-        <v>90972</v>
+        <v>78766</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19944,37 +19952,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>480730</v>
+        <v>481130</v>
       </c>
       <c r="R182" t="n">
-        <v>6790601</v>
+        <v>6790661</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20001,9 +20009,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20018,19 +20036,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122907291</v>
+        <v>122907615</v>
       </c>
       <c r="B183" t="n">
         <v>90972</v>
@@ -20070,10 +20088,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>480712</v>
+        <v>480730</v>
       </c>
       <c r="R183" t="n">
-        <v>6790625</v>
+        <v>6790601</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20132,10 +20150,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122913790</v>
+        <v>122907291</v>
       </c>
       <c r="B184" t="n">
-        <v>56688</v>
+        <v>90972</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20144,49 +20162,41 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>481264</v>
+        <v>480712</v>
       </c>
       <c r="R184" t="n">
-        <v>6790709</v>
+        <v>6790625</v>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20213,19 +20223,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20240,12 +20240,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -20364,7 +20364,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122969601</v>
+        <v>122970352</v>
       </c>
       <c r="B186" t="n">
         <v>78766</v>
@@ -20400,17 +20400,17 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>481528</v>
+        <v>481566</v>
       </c>
       <c r="R186" t="n">
-        <v>6790490</v>
+        <v>6790511</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20437,9 +20437,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20454,19 +20464,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122970352</v>
+        <v>122969601</v>
       </c>
       <c r="B187" t="n">
         <v>78766</v>
@@ -20502,17 +20512,17 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>481566</v>
+        <v>481528</v>
       </c>
       <c r="R187" t="n">
-        <v>6790511</v>
+        <v>6790490</v>
       </c>
       <c r="S187" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20539,19 +20549,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20566,12 +20566,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -22111,10 +22111,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122961172</v>
+        <v>122975322</v>
       </c>
       <c r="B202" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22123,41 +22123,41 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>480745</v>
+        <v>481394</v>
       </c>
       <c r="R202" t="n">
-        <v>6790759</v>
+        <v>6790771</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22184,9 +22184,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22201,22 +22211,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122968065</v>
+        <v>122969981</v>
       </c>
       <c r="B203" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22229,16 +22239,16 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -22249,17 +22259,17 @@
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>481371</v>
+        <v>481565</v>
       </c>
       <c r="R203" t="n">
-        <v>6790559</v>
+        <v>6790484</v>
       </c>
       <c r="S203" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22286,19 +22296,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>13:21</t>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22313,19 +22318,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122969543</v>
+        <v>122961172</v>
       </c>
       <c r="B204" t="n">
         <v>78766</v>
@@ -22365,10 +22370,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>481496</v>
+        <v>480745</v>
       </c>
       <c r="R204" t="n">
-        <v>6790486</v>
+        <v>6790759</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22401,11 +22406,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav.</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22432,7 +22432,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122965760</v>
+        <v>122968065</v>
       </c>
       <c r="B205" t="n">
         <v>78766</v>
@@ -22472,10 +22472,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>481118</v>
+        <v>481371</v>
       </c>
       <c r="R205" t="n">
-        <v>6790699</v>
+        <v>6790559</v>
       </c>
       <c r="S205" t="n">
         <v>9</v>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22544,10 +22544,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122969981</v>
+        <v>122969543</v>
       </c>
       <c r="B206" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22560,16 +22560,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -22584,10 +22584,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>481565</v>
+        <v>481496</v>
       </c>
       <c r="R206" t="n">
-        <v>6790484</v>
+        <v>6790486</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22624,7 +22624,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+          <t>Miljöbilder och garnlav.</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22651,10 +22651,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122975322</v>
+        <v>122965760</v>
       </c>
       <c r="B207" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22663,25 +22663,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22691,10 +22691,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>481394</v>
+        <v>481118</v>
       </c>
       <c r="R207" t="n">
-        <v>6790771</v>
+        <v>6790699</v>
       </c>
       <c r="S207" t="n">
         <v>9</v>
@@ -22726,7 +22726,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22736,7 +22736,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26991,10 +26991,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122960414</v>
+        <v>122974351</v>
       </c>
       <c r="B247" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27007,37 +27007,37 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>480766</v>
+        <v>481398</v>
       </c>
       <c r="R247" t="n">
-        <v>6790785</v>
+        <v>6790689</v>
       </c>
       <c r="S247" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -27064,9 +27064,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27081,19 +27091,19 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122960562</v>
+        <v>122960414</v>
       </c>
       <c r="B248" t="n">
         <v>78766</v>
@@ -27133,10 +27143,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>480756</v>
+        <v>480766</v>
       </c>
       <c r="R248" t="n">
-        <v>6790775</v>
+        <v>6790785</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -27195,10 +27205,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122974351</v>
+        <v>122960562</v>
       </c>
       <c r="B249" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -27211,37 +27221,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>481398</v>
+        <v>480756</v>
       </c>
       <c r="R249" t="n">
-        <v>6790689</v>
+        <v>6790775</v>
       </c>
       <c r="S249" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -27268,19 +27278,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27295,12 +27295,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
@@ -32966,10 +32966,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122978194</v>
+        <v>122965865</v>
       </c>
       <c r="B302" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -32978,31 +32978,31 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
@@ -33011,10 +33011,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>481090</v>
+        <v>481118</v>
       </c>
       <c r="R302" t="n">
-        <v>6790709</v>
+        <v>6790699</v>
       </c>
       <c r="S302" t="n">
         <v>9</v>
@@ -33046,7 +33046,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -33083,10 +33083,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122967628</v>
+        <v>122978194</v>
       </c>
       <c r="B303" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -33095,31 +33095,31 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
@@ -33128,13 +33128,13 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>481264</v>
+        <v>481090</v>
       </c>
       <c r="R303" t="n">
-        <v>6790665</v>
+        <v>6790709</v>
       </c>
       <c r="S303" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -33173,7 +33173,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -33200,10 +33200,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122970166</v>
+        <v>122975526</v>
       </c>
       <c r="B304" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -33212,46 +33212,41 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>481546</v>
+        <v>481420</v>
       </c>
       <c r="R304" t="n">
-        <v>6790501</v>
+        <v>6790760</v>
       </c>
       <c r="S304" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -33278,19 +33273,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB304" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -33305,19 +33290,19 @@
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122975526</v>
+        <v>122962209</v>
       </c>
       <c r="B305" t="n">
         <v>78766</v>
@@ -33353,14 +33338,14 @@
       <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>481420</v>
+        <v>480818</v>
       </c>
       <c r="R305" t="n">
-        <v>6790760</v>
+        <v>6790633</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -33419,7 +33404,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122962209</v>
+        <v>122978123</v>
       </c>
       <c r="B306" t="n">
         <v>78766</v>
@@ -33455,17 +33440,17 @@
       <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>480818</v>
+        <v>481144</v>
       </c>
       <c r="R306" t="n">
-        <v>6790633</v>
+        <v>6790730</v>
       </c>
       <c r="S306" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -33492,9 +33477,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA306" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -33509,19 +33504,19 @@
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122978123</v>
+        <v>122966180</v>
       </c>
       <c r="B307" t="n">
         <v>78766</v>
@@ -33561,10 +33556,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>481144</v>
+        <v>481151</v>
       </c>
       <c r="R307" t="n">
-        <v>6790730</v>
+        <v>6790709</v>
       </c>
       <c r="S307" t="n">
         <v>9</v>
@@ -33596,7 +33591,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -33606,7 +33601,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33633,7 +33628,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122966180</v>
+        <v>122965694</v>
       </c>
       <c r="B308" t="n">
         <v>78766</v>
@@ -33673,10 +33668,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>481151</v>
+        <v>481111</v>
       </c>
       <c r="R308" t="n">
-        <v>6790709</v>
+        <v>6790702</v>
       </c>
       <c r="S308" t="n">
         <v>9</v>
@@ -33708,7 +33703,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -33718,7 +33713,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33745,7 +33740,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122965694</v>
+        <v>122960001</v>
       </c>
       <c r="B309" t="n">
         <v>78766</v>
@@ -33781,17 +33776,17 @@
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>481111</v>
+        <v>480805</v>
       </c>
       <c r="R309" t="n">
-        <v>6790702</v>
+        <v>6790809</v>
       </c>
       <c r="S309" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -33818,19 +33813,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB309" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33845,22 +33830,22 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122960001</v>
+        <v>122967628</v>
       </c>
       <c r="B310" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -33873,37 +33858,42 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>480805</v>
+        <v>481264</v>
       </c>
       <c r="R310" t="n">
-        <v>6790809</v>
+        <v>6790665</v>
       </c>
       <c r="S310" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -33930,9 +33920,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33947,22 +33947,22 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122965865</v>
+        <v>122970166</v>
       </c>
       <c r="B311" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -33971,31 +33971,31 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
@@ -34004,10 +34004,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>481118</v>
+        <v>481546</v>
       </c>
       <c r="R311" t="n">
-        <v>6790699</v>
+        <v>6790501</v>
       </c>
       <c r="S311" t="n">
         <v>9</v>
@@ -34039,7 +34039,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -35199,10 +35199,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122972843</v>
+        <v>122971852</v>
       </c>
       <c r="B322" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -35211,41 +35211,46 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>481748</v>
+        <v>481678</v>
       </c>
       <c r="R322" t="n">
-        <v>6790465</v>
+        <v>6790570</v>
       </c>
       <c r="S322" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -35272,9 +35277,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -35289,22 +35304,22 @@
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122971852</v>
+        <v>122972843</v>
       </c>
       <c r="B323" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -35313,46 +35328,41 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>481678</v>
+        <v>481748</v>
       </c>
       <c r="R323" t="n">
-        <v>6790570</v>
+        <v>6790465</v>
       </c>
       <c r="S323" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -35379,19 +35389,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB323" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -35406,12 +35406,12 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -3154,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122917610</v>
+        <v>122908784</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>78411</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,43 +3166,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480786</v>
+        <v>480639</v>
       </c>
       <c r="R25" t="n">
-        <v>6790628</v>
+        <v>6790797</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,9 +3227,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3249,22 +3254,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122913869</v>
+        <v>122907867</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3277,39 +3282,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480861</v>
+        <v>480744</v>
       </c>
       <c r="R26" t="n">
-        <v>6790634</v>
+        <v>6790595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,7 +3368,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122905638</v>
+        <v>122914964</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3404,17 +3404,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480687</v>
+        <v>480805</v>
       </c>
       <c r="R27" t="n">
-        <v>6790754</v>
+        <v>6790675</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3441,9 +3441,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3458,22 +3468,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122908658</v>
+        <v>122906981</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,41 +3492,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480701</v>
+        <v>480725</v>
       </c>
       <c r="R28" t="n">
-        <v>6790532</v>
+        <v>6790654</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3543,19 +3553,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3570,22 +3570,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908784</v>
+        <v>122908392</v>
       </c>
       <c r="B29" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3598,37 +3598,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480639</v>
+        <v>480628</v>
       </c>
       <c r="R29" t="n">
-        <v>6790797</v>
+        <v>6790661</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,19 +3682,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122907867</v>
+        <v>122912843</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3730,17 +3730,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480744</v>
+        <v>481068</v>
       </c>
       <c r="R30" t="n">
-        <v>6790595</v>
+        <v>6790734</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3767,9 +3767,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3784,19 +3794,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122914964</v>
+        <v>122908033</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3832,17 +3842,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480805</v>
+        <v>480735</v>
       </c>
       <c r="R31" t="n">
-        <v>6790675</v>
+        <v>6790566</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3869,19 +3879,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3896,19 +3896,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122906981</v>
+        <v>122910046</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3951,7 +3951,7 @@
         <v>480725</v>
       </c>
       <c r="R32" t="n">
-        <v>6790654</v>
+        <v>6790756</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122908392</v>
+        <v>122916802</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4046,17 +4046,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480628</v>
+        <v>481344</v>
       </c>
       <c r="R33" t="n">
-        <v>6790661</v>
+        <v>6790501</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4083,19 +4083,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,19 +4100,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122912843</v>
+        <v>122915538</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4158,17 +4148,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481068</v>
+        <v>481062</v>
       </c>
       <c r="R34" t="n">
-        <v>6790734</v>
+        <v>6790598</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4195,19 +4185,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4222,19 +4202,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122908033</v>
+        <v>122914138</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4274,10 +4254,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480735</v>
+        <v>480858</v>
       </c>
       <c r="R35" t="n">
-        <v>6790566</v>
+        <v>6790672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4336,10 +4316,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122910046</v>
+        <v>122917610</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4348,38 +4328,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480725</v>
+        <v>480786</v>
       </c>
       <c r="R36" t="n">
-        <v>6790756</v>
+        <v>6790628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4438,10 +4423,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122916802</v>
+        <v>122913869</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4454,34 +4439,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481344</v>
+        <v>480861</v>
       </c>
       <c r="R37" t="n">
-        <v>6790501</v>
+        <v>6790634</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,7 +4530,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122915538</v>
+        <v>122905638</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4580,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481062</v>
+        <v>480687</v>
       </c>
       <c r="R38" t="n">
-        <v>6790598</v>
+        <v>6790754</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4642,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122914138</v>
+        <v>122908658</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4654,41 +4644,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480858</v>
+        <v>480701</v>
       </c>
       <c r="R39" t="n">
-        <v>6790672</v>
+        <v>6790532</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4715,9 +4705,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4732,12 +4732,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122905949</v>
+        <v>122905560</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480710</v>
+        <v>480689</v>
       </c>
       <c r="R46" t="n">
-        <v>6790729</v>
+        <v>6790776</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122905769</v>
+        <v>122910737</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480697</v>
+        <v>480800</v>
       </c>
       <c r="R47" t="n">
-        <v>6790747</v>
+        <v>6790542</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122907225</v>
+        <v>122913871</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480622</v>
+        <v>481264</v>
       </c>
       <c r="R48" t="n">
-        <v>6790776</v>
+        <v>6790709</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5680,19 +5680,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122907981</v>
+        <v>122914302</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5728,17 +5728,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480580</v>
+        <v>480864</v>
       </c>
       <c r="R49" t="n">
-        <v>6790754</v>
+        <v>6790682</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5765,19 +5765,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5792,19 +5782,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122914293</v>
+        <v>122905949</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5840,17 +5830,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481318</v>
+        <v>480710</v>
       </c>
       <c r="R50" t="n">
-        <v>6790679</v>
+        <v>6790729</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5877,19 +5867,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5904,19 +5884,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122910257</v>
+        <v>122905769</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5952,17 +5932,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480680</v>
+        <v>480697</v>
       </c>
       <c r="R51" t="n">
-        <v>6790662</v>
+        <v>6790747</v>
       </c>
       <c r="S51" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5989,19 +5969,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6016,19 +5986,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122906759</v>
+        <v>122907225</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6064,17 +6034,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480726</v>
+        <v>480622</v>
       </c>
       <c r="R52" t="n">
-        <v>6790689</v>
+        <v>6790776</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6101,9 +6071,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6118,19 +6098,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122907426</v>
+        <v>122907981</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6166,17 +6146,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480611</v>
+        <v>480580</v>
       </c>
       <c r="R53" t="n">
-        <v>6790803</v>
+        <v>6790754</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6205,7 +6185,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6215,7 +6195,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6230,19 +6210,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122910531</v>
+        <v>122914293</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6278,17 +6258,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480772</v>
+        <v>481318</v>
       </c>
       <c r="R54" t="n">
-        <v>6790619</v>
+        <v>6790679</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6315,9 +6295,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6332,19 +6322,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122914414</v>
+        <v>122910257</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6384,13 +6374,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481039</v>
+        <v>480680</v>
       </c>
       <c r="R55" t="n">
-        <v>6790686</v>
+        <v>6790662</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6419,7 +6409,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6429,7 +6419,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6444,19 +6434,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122911585</v>
+        <v>122906759</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6492,17 +6482,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481035</v>
+        <v>480726</v>
       </c>
       <c r="R56" t="n">
-        <v>6790750</v>
+        <v>6790689</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6529,19 +6519,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6556,22 +6536,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122909085</v>
+        <v>122907426</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6580,38 +6560,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480626</v>
+        <v>480611</v>
       </c>
       <c r="R57" t="n">
-        <v>6790648</v>
+        <v>6790803</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6623,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6653,7 +6633,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6668,19 +6648,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122905560</v>
+        <v>122910531</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6720,10 +6700,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480689</v>
+        <v>480772</v>
       </c>
       <c r="R58" t="n">
-        <v>6790776</v>
+        <v>6790619</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6782,7 +6762,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122910737</v>
+        <v>122914414</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6818,17 +6798,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480800</v>
+        <v>481039</v>
       </c>
       <c r="R59" t="n">
-        <v>6790542</v>
+        <v>6790686</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6855,9 +6835,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6872,19 +6862,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122913871</v>
+        <v>122911585</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6924,13 +6914,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481264</v>
+        <v>481035</v>
       </c>
       <c r="R60" t="n">
-        <v>6790709</v>
+        <v>6790750</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6959,7 +6949,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6969,7 +6959,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6984,22 +6974,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122914302</v>
+        <v>122909085</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7008,38 +6998,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480864</v>
+        <v>480626</v>
       </c>
       <c r="R61" t="n">
-        <v>6790682</v>
+        <v>6790648</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7069,9 +7059,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7086,12 +7086,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8581,7 +8581,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122906205</v>
+        <v>122905989</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -8621,10 +8621,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480708</v>
+        <v>480688</v>
       </c>
       <c r="R76" t="n">
-        <v>6790701</v>
+        <v>6790702</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8683,7 +8683,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122912740</v>
+        <v>122914913</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481151</v>
+        <v>480848</v>
       </c>
       <c r="R77" t="n">
-        <v>6790720</v>
+        <v>6790704</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8795,7 +8795,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122907575</v>
+        <v>122906205</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8831,17 +8831,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480571</v>
+        <v>480708</v>
       </c>
       <c r="R78" t="n">
-        <v>6790798</v>
+        <v>6790701</v>
       </c>
       <c r="S78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8868,19 +8868,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8895,19 +8885,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122908626</v>
+        <v>122912740</v>
       </c>
       <c r="B79" t="n">
         <v>78766</v>
@@ -8943,17 +8933,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480639</v>
+        <v>481151</v>
       </c>
       <c r="R79" t="n">
-        <v>6790797</v>
+        <v>6790720</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8982,7 +8972,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8992,7 +8982,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9007,19 +8997,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122905989</v>
+        <v>122907575</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -9055,17 +9045,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480688</v>
+        <v>480571</v>
       </c>
       <c r="R80" t="n">
-        <v>6790702</v>
+        <v>6790798</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9092,9 +9082,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9109,19 +9109,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122914913</v>
+        <v>122908626</v>
       </c>
       <c r="B81" t="n">
         <v>78766</v>
@@ -9157,17 +9157,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480848</v>
+        <v>480639</v>
       </c>
       <c r="R81" t="n">
-        <v>6790704</v>
+        <v>6790797</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9221,22 +9221,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122908368</v>
+        <v>122916590</v>
       </c>
       <c r="B82" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480704</v>
+        <v>481290</v>
       </c>
       <c r="R82" t="n">
-        <v>6790523</v>
+        <v>6790576</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122915141</v>
+        <v>122907579</v>
       </c>
       <c r="B83" t="n">
         <v>78766</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480999</v>
+        <v>480739</v>
       </c>
       <c r="R83" t="n">
-        <v>6790659</v>
+        <v>6790609</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122908430</v>
+        <v>122913923</v>
       </c>
       <c r="B84" t="n">
         <v>78766</v>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480722</v>
+        <v>480817</v>
       </c>
       <c r="R84" t="n">
-        <v>6790508</v>
+        <v>6790670</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9539,7 +9539,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122907562</v>
+        <v>122915252</v>
       </c>
       <c r="B85" t="n">
         <v>78766</v>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480739</v>
+        <v>481010</v>
       </c>
       <c r="R85" t="n">
-        <v>6790609</v>
+        <v>6790656</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9641,10 +9641,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122913909</v>
+        <v>122908690</v>
       </c>
       <c r="B86" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9657,37 +9657,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480837</v>
+        <v>480626</v>
       </c>
       <c r="R86" t="n">
-        <v>6790651</v>
+        <v>6790648</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9714,9 +9714,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9731,22 +9741,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122913714</v>
+        <v>122913735</v>
       </c>
       <c r="B87" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9759,37 +9769,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480860</v>
+        <v>481068</v>
       </c>
       <c r="R87" t="n">
-        <v>6790660</v>
+        <v>6790734</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9816,9 +9826,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9833,22 +9853,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122908177</v>
+        <v>122908368</v>
       </c>
       <c r="B88" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9861,37 +9881,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480606</v>
+        <v>480704</v>
       </c>
       <c r="R88" t="n">
-        <v>6790682</v>
+        <v>6790523</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9918,19 +9938,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9945,19 +9955,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122910695</v>
+        <v>122915141</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -9997,10 +10007,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480801</v>
+        <v>480999</v>
       </c>
       <c r="R89" t="n">
-        <v>6790557</v>
+        <v>6790659</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10059,10 +10069,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122916590</v>
+        <v>122908430</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10075,21 +10085,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10099,10 +10109,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481290</v>
+        <v>480722</v>
       </c>
       <c r="R90" t="n">
-        <v>6790576</v>
+        <v>6790508</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10161,7 +10171,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122913923</v>
+        <v>122913909</v>
       </c>
       <c r="B91" t="n">
         <v>78766</v>
@@ -10201,10 +10211,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480817</v>
+        <v>480837</v>
       </c>
       <c r="R91" t="n">
-        <v>6790670</v>
+        <v>6790651</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10263,7 +10273,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122915252</v>
+        <v>122913714</v>
       </c>
       <c r="B92" t="n">
         <v>78766</v>
@@ -10303,10 +10313,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481010</v>
+        <v>480860</v>
       </c>
       <c r="R92" t="n">
-        <v>6790656</v>
+        <v>6790660</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10365,10 +10375,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122908690</v>
+        <v>122908177</v>
       </c>
       <c r="B93" t="n">
-        <v>78411</v>
+        <v>78502</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10381,21 +10391,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10405,13 +10415,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480626</v>
+        <v>480606</v>
       </c>
       <c r="R93" t="n">
-        <v>6790648</v>
+        <v>6790682</v>
       </c>
       <c r="S93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10440,7 +10450,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10450,7 +10460,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10465,22 +10475,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122913735</v>
+        <v>122910695</v>
       </c>
       <c r="B94" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10493,37 +10503,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481068</v>
+        <v>480801</v>
       </c>
       <c r="R94" t="n">
-        <v>6790734</v>
+        <v>6790557</v>
       </c>
       <c r="S94" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10550,19 +10560,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10577,12 +10577,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11216,10 +11216,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122914058</v>
+        <v>122914997</v>
       </c>
       <c r="B101" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11228,41 +11228,49 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480832</v>
+        <v>480873</v>
       </c>
       <c r="R101" t="n">
-        <v>6790668</v>
+        <v>6790694</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11289,9 +11297,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11306,19 +11324,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122911564</v>
+        <v>122914058</v>
       </c>
       <c r="B102" t="n">
         <v>78766</v>
@@ -11354,17 +11372,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>481081</v>
+        <v>480832</v>
       </c>
       <c r="R102" t="n">
-        <v>6790749</v>
+        <v>6790668</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11391,19 +11409,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11418,22 +11426,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122914997</v>
+        <v>122911564</v>
       </c>
       <c r="B103" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11442,49 +11450,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>480873</v>
+        <v>481081</v>
       </c>
       <c r="R103" t="n">
-        <v>6790694</v>
+        <v>6790749</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11538,19 +11538,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122914329</v>
+        <v>122907941</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11586,17 +11586,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>481184</v>
+        <v>480736</v>
       </c>
       <c r="R104" t="n">
-        <v>6790659</v>
+        <v>6790589</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11623,19 +11623,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11650,19 +11640,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122908564</v>
+        <v>122905837</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -11698,17 +11688,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480648</v>
+        <v>480679</v>
       </c>
       <c r="R105" t="n">
-        <v>6790546</v>
+        <v>6790740</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11735,19 +11725,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11762,19 +11742,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122914370</v>
+        <v>122914257</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -11814,13 +11794,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>481130</v>
+        <v>481217</v>
       </c>
       <c r="R106" t="n">
-        <v>6790661</v>
+        <v>6790566</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11849,7 +11829,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11859,7 +11839,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11874,19 +11854,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122915272</v>
+        <v>122914329</v>
       </c>
       <c r="B107" t="n">
         <v>78766</v>
@@ -11922,17 +11902,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>481024</v>
+        <v>481184</v>
       </c>
       <c r="R107" t="n">
-        <v>6790673</v>
+        <v>6790659</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11959,9 +11939,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11976,19 +11966,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122907818</v>
+        <v>122908564</v>
       </c>
       <c r="B108" t="n">
         <v>78766</v>
@@ -12028,10 +12018,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480545</v>
+        <v>480648</v>
       </c>
       <c r="R108" t="n">
-        <v>6790776</v>
+        <v>6790546</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12063,7 +12053,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12073,7 +12063,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12100,7 +12090,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122908082</v>
+        <v>122914370</v>
       </c>
       <c r="B109" t="n">
         <v>78766</v>
@@ -12140,10 +12130,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480607</v>
+        <v>481130</v>
       </c>
       <c r="R109" t="n">
-        <v>6790687</v>
+        <v>6790661</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12175,7 +12165,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12185,7 +12175,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12212,7 +12202,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122908696</v>
+        <v>122915272</v>
       </c>
       <c r="B110" t="n">
         <v>78766</v>
@@ -12248,17 +12238,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480701</v>
+        <v>481024</v>
       </c>
       <c r="R110" t="n">
-        <v>6790532</v>
+        <v>6790673</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12285,19 +12275,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>12:25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12312,22 +12292,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122908121</v>
+        <v>122907818</v>
       </c>
       <c r="B111" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12336,25 +12316,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12364,13 +12344,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480638</v>
+        <v>480545</v>
       </c>
       <c r="R111" t="n">
-        <v>6790738</v>
+        <v>6790776</v>
       </c>
       <c r="S111" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12399,7 +12379,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12409,7 +12389,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12424,19 +12404,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122907941</v>
+        <v>122908082</v>
       </c>
       <c r="B112" t="n">
         <v>78766</v>
@@ -12472,17 +12452,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480736</v>
+        <v>480607</v>
       </c>
       <c r="R112" t="n">
-        <v>6790589</v>
+        <v>6790687</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12509,9 +12489,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12526,19 +12516,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122905837</v>
+        <v>122908696</v>
       </c>
       <c r="B113" t="n">
         <v>78766</v>
@@ -12574,17 +12564,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480679</v>
+        <v>480701</v>
       </c>
       <c r="R113" t="n">
-        <v>6790740</v>
+        <v>6790532</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12611,9 +12601,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12628,22 +12628,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122914257</v>
+        <v>122908121</v>
       </c>
       <c r="B114" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12652,25 +12652,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12680,10 +12680,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>481217</v>
+        <v>480638</v>
       </c>
       <c r="R114" t="n">
-        <v>6790566</v>
+        <v>6790738</v>
       </c>
       <c r="S114" t="n">
         <v>11</v>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -16681,10 +16681,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122916175</v>
+        <v>122915190</v>
       </c>
       <c r="B152" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16697,37 +16697,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>481253</v>
+        <v>480830</v>
       </c>
       <c r="R152" t="n">
-        <v>6790554</v>
+        <v>6790684</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16754,9 +16754,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16771,19 +16781,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122916996</v>
+        <v>122910652</v>
       </c>
       <c r="B153" t="n">
         <v>78766</v>
@@ -16823,10 +16833,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>481382</v>
+        <v>480780</v>
       </c>
       <c r="R153" t="n">
-        <v>6790485</v>
+        <v>6790598</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16885,7 +16895,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122909144</v>
+        <v>122914846</v>
       </c>
       <c r="B154" t="n">
         <v>78766</v>
@@ -16921,17 +16931,17 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480738</v>
+        <v>480895</v>
       </c>
       <c r="R154" t="n">
-        <v>6790666</v>
+        <v>6790735</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16958,9 +16968,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16975,22 +16995,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122915190</v>
+        <v>122910462</v>
       </c>
       <c r="B155" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17003,21 +17023,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17027,13 +17047,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480830</v>
+        <v>480753</v>
       </c>
       <c r="R155" t="n">
-        <v>6790684</v>
+        <v>6790776</v>
       </c>
       <c r="S155" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17062,7 +17082,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17072,7 +17092,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17087,19 +17107,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122910652</v>
+        <v>122916175</v>
       </c>
       <c r="B156" t="n">
         <v>78766</v>
@@ -17139,10 +17159,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480780</v>
+        <v>481253</v>
       </c>
       <c r="R156" t="n">
-        <v>6790598</v>
+        <v>6790554</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17201,7 +17221,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122914846</v>
+        <v>122916996</v>
       </c>
       <c r="B157" t="n">
         <v>78766</v>
@@ -17237,17 +17257,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480895</v>
+        <v>481382</v>
       </c>
       <c r="R157" t="n">
-        <v>6790735</v>
+        <v>6790485</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17274,19 +17294,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17301,19 +17311,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122910462</v>
+        <v>122909144</v>
       </c>
       <c r="B158" t="n">
         <v>78766</v>
@@ -17349,14 +17359,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480753</v>
+        <v>480738</v>
       </c>
       <c r="R158" t="n">
-        <v>6790776</v>
+        <v>6790666</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17386,19 +17396,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17413,22 +17413,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122911238</v>
+        <v>122914092</v>
       </c>
       <c r="B159" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17437,25 +17437,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17465,13 +17465,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>481009</v>
+        <v>481216</v>
       </c>
       <c r="R159" t="n">
-        <v>6790696</v>
+        <v>6790675</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17525,22 +17525,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122909092</v>
+        <v>122908196</v>
       </c>
       <c r="B160" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17549,38 +17549,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>480626</v>
+        <v>480681</v>
       </c>
       <c r="R160" t="n">
-        <v>6790648</v>
+        <v>6790816</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17612,7 +17612,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17637,19 +17637,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122913997</v>
+        <v>122911238</v>
       </c>
       <c r="B161" t="n">
         <v>78766</v>
@@ -17689,13 +17689,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>481407</v>
+        <v>481009</v>
       </c>
       <c r="R161" t="n">
-        <v>6790724</v>
+        <v>6790696</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17761,7 +17761,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122910124</v>
+        <v>122909092</v>
       </c>
       <c r="B162" t="n">
         <v>78766</v>
@@ -17797,14 +17797,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>480730</v>
+        <v>480626</v>
       </c>
       <c r="R162" t="n">
-        <v>6790750</v>
+        <v>6790648</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17834,9 +17834,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17851,19 +17861,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122914420</v>
+        <v>122913997</v>
       </c>
       <c r="B163" t="n">
         <v>78766</v>
@@ -17903,10 +17913,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>481040</v>
+        <v>481407</v>
       </c>
       <c r="R163" t="n">
-        <v>6790687</v>
+        <v>6790724</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -17938,7 +17948,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17948,7 +17958,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17975,10 +17985,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122914092</v>
+        <v>122910124</v>
       </c>
       <c r="B164" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17987,41 +17997,41 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>481216</v>
+        <v>480730</v>
       </c>
       <c r="R164" t="n">
-        <v>6790675</v>
+        <v>6790750</v>
       </c>
       <c r="S164" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18048,19 +18058,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18075,22 +18075,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122908196</v>
+        <v>122913790</v>
       </c>
       <c r="B165" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18103,37 +18103,45 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>480681</v>
+        <v>481264</v>
       </c>
       <c r="R165" t="n">
-        <v>6790816</v>
+        <v>6790709</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18162,7 +18170,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18172,7 +18180,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18187,22 +18195,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122913790</v>
+        <v>122914420</v>
       </c>
       <c r="B166" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18211,46 +18219,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>481264</v>
+        <v>481040</v>
       </c>
       <c r="R166" t="n">
-        <v>6790709</v>
+        <v>6790687</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18319,10 +18319,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122915104</v>
+        <v>122913967</v>
       </c>
       <c r="B167" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18331,46 +18331,41 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>480783</v>
+        <v>480823</v>
       </c>
       <c r="R167" t="n">
-        <v>6790712</v>
+        <v>6790672</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18397,19 +18392,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18424,19 +18409,19 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122913967</v>
+        <v>122913893</v>
       </c>
       <c r="B168" t="n">
         <v>78766</v>
@@ -18472,17 +18457,17 @@
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>480823</v>
+        <v>481268</v>
       </c>
       <c r="R168" t="n">
-        <v>6790672</v>
+        <v>6790734</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18509,9 +18494,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18526,19 +18521,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122913893</v>
+        <v>122908108</v>
       </c>
       <c r="B169" t="n">
         <v>78766</v>
@@ -18574,17 +18569,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>481268</v>
+        <v>480758</v>
       </c>
       <c r="R169" t="n">
-        <v>6790734</v>
+        <v>6790557</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18611,19 +18606,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18638,19 +18623,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>122908108</v>
+        <v>122908896</v>
       </c>
       <c r="B170" t="n">
         <v>78766</v>
@@ -18690,10 +18675,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>480758</v>
+        <v>480771</v>
       </c>
       <c r="R170" t="n">
-        <v>6790557</v>
+        <v>6790522</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18752,10 +18737,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>122908896</v>
+        <v>122911766</v>
       </c>
       <c r="B171" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18768,34 +18753,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>480771</v>
+        <v>481068</v>
       </c>
       <c r="R171" t="n">
-        <v>6790522</v>
+        <v>6790734</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18825,9 +18810,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18842,19 +18837,19 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>122911766</v>
+        <v>122915259</v>
       </c>
       <c r="B172" t="n">
         <v>78502</v>
@@ -18888,19 +18883,22 @@
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>481068</v>
+        <v>480813</v>
       </c>
       <c r="R172" t="n">
-        <v>6790734</v>
+        <v>6790675</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18929,7 +18927,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18939,7 +18937,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18948,6 +18946,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18966,10 +18965,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122915259</v>
+        <v>122916212</v>
       </c>
       <c r="B173" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18982,40 +18981,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>480813</v>
+        <v>481263</v>
       </c>
       <c r="R173" t="n">
-        <v>6790675</v>
+        <v>6790561</v>
       </c>
       <c r="S173" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19042,47 +19038,36 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>122916212</v>
+        <v>122906123</v>
       </c>
       <c r="B174" t="n">
         <v>78766</v>
@@ -19122,10 +19107,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>481263</v>
+        <v>480697</v>
       </c>
       <c r="R174" t="n">
-        <v>6790561</v>
+        <v>6790703</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19184,7 +19169,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122906123</v>
+        <v>122908019</v>
       </c>
       <c r="B175" t="n">
         <v>78766</v>
@@ -19224,10 +19209,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>480697</v>
+        <v>480719</v>
       </c>
       <c r="R175" t="n">
-        <v>6790703</v>
+        <v>6790571</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19286,10 +19271,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122908019</v>
+        <v>122915104</v>
       </c>
       <c r="B176" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19298,41 +19283,46 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>480719</v>
+        <v>480783</v>
       </c>
       <c r="R176" t="n">
-        <v>6790571</v>
+        <v>6790712</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19359,9 +19349,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19376,12 +19376,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
@@ -19500,10 +19500,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122914153</v>
+        <v>122908588</v>
       </c>
       <c r="B178" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19516,34 +19516,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>480850</v>
+        <v>480638</v>
       </c>
       <c r="R178" t="n">
-        <v>6790697</v>
+        <v>6790738</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19573,9 +19573,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19590,22 +19600,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122907291</v>
+        <v>122914153</v>
       </c>
       <c r="B179" t="n">
-        <v>90972</v>
+        <v>78766</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19618,21 +19628,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19642,10 +19652,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>480712</v>
+        <v>480850</v>
       </c>
       <c r="R179" t="n">
-        <v>6790625</v>
+        <v>6790697</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19704,10 +19714,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122908588</v>
+        <v>122907291</v>
       </c>
       <c r="B180" t="n">
-        <v>78503</v>
+        <v>90972</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19720,34 +19730,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>480638</v>
+        <v>480712</v>
       </c>
       <c r="R180" t="n">
-        <v>6790738</v>
+        <v>6790625</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19777,19 +19787,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>12:21</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19804,12 +19804,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -22613,10 +22613,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122967764</v>
+        <v>122975234</v>
       </c>
       <c r="B207" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22629,37 +22629,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>481304</v>
+        <v>481459</v>
       </c>
       <c r="R207" t="n">
-        <v>6790615</v>
+        <v>6790740</v>
       </c>
       <c r="S207" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22686,19 +22686,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22713,19 +22703,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122962111</v>
+        <v>122967764</v>
       </c>
       <c r="B208" t="n">
         <v>78766</v>
@@ -22761,17 +22751,17 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>480804</v>
+        <v>481304</v>
       </c>
       <c r="R208" t="n">
-        <v>6790650</v>
+        <v>6790615</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22798,9 +22788,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22815,19 +22815,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122960241</v>
+        <v>122962111</v>
       </c>
       <c r="B209" t="n">
         <v>78766</v>
@@ -22867,10 +22867,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>480794</v>
+        <v>480804</v>
       </c>
       <c r="R209" t="n">
-        <v>6790801</v>
+        <v>6790650</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22929,7 +22929,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122967506</v>
+        <v>122960241</v>
       </c>
       <c r="B210" t="n">
         <v>78766</v>
@@ -22965,17 +22965,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>481250</v>
+        <v>480794</v>
       </c>
       <c r="R210" t="n">
-        <v>6790669</v>
+        <v>6790801</v>
       </c>
       <c r="S210" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23002,19 +23002,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23029,19 +23019,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122977930</v>
+        <v>122967506</v>
       </c>
       <c r="B211" t="n">
         <v>78766</v>
@@ -23077,17 +23067,17 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>481202</v>
+        <v>481250</v>
       </c>
       <c r="R211" t="n">
-        <v>6790769</v>
+        <v>6790669</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23114,14 +23104,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Garn inom synfältet, ca 50 meter i radie.</t>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23136,19 +23131,19 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122966180</v>
+        <v>122977930</v>
       </c>
       <c r="B212" t="n">
         <v>78766</v>
@@ -23184,17 +23179,17 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>481151</v>
+        <v>481202</v>
       </c>
       <c r="R212" t="n">
-        <v>6790709</v>
+        <v>6790769</v>
       </c>
       <c r="S212" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23221,19 +23216,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Garn inom synfältet, ca 50 meter i radie.</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23248,19 +23238,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122965694</v>
+        <v>122966180</v>
       </c>
       <c r="B213" t="n">
         <v>78766</v>
@@ -23300,10 +23290,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>481111</v>
+        <v>481151</v>
       </c>
       <c r="R213" t="n">
-        <v>6790702</v>
+        <v>6790709</v>
       </c>
       <c r="S213" t="n">
         <v>9</v>
@@ -23335,7 +23325,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23345,7 +23335,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23372,7 +23362,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122975263</v>
+        <v>122965694</v>
       </c>
       <c r="B214" t="n">
         <v>78766</v>
@@ -23412,10 +23402,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>481394</v>
+        <v>481111</v>
       </c>
       <c r="R214" t="n">
-        <v>6790770</v>
+        <v>6790702</v>
       </c>
       <c r="S214" t="n">
         <v>9</v>
@@ -23447,7 +23437,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23457,7 +23447,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23484,10 +23474,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122975234</v>
+        <v>122975263</v>
       </c>
       <c r="B215" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23500,37 +23490,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>481459</v>
+        <v>481394</v>
       </c>
       <c r="R215" t="n">
-        <v>6790740</v>
+        <v>6790770</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -23557,9 +23547,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23574,12 +23574,12 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
@@ -24116,10 +24116,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122961613</v>
+        <v>122968198</v>
       </c>
       <c r="B221" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24128,41 +24128,46 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>480767</v>
+        <v>481373</v>
       </c>
       <c r="R221" t="n">
-        <v>6790673</v>
+        <v>6790551</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24189,9 +24194,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24206,19 +24221,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122964950</v>
+        <v>122961613</v>
       </c>
       <c r="B222" t="n">
         <v>78766</v>
@@ -24254,17 +24269,17 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>481026</v>
+        <v>480767</v>
       </c>
       <c r="R222" t="n">
-        <v>6790700</v>
+        <v>6790673</v>
       </c>
       <c r="S222" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24291,19 +24306,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24318,19 +24323,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122968577</v>
+        <v>122964950</v>
       </c>
       <c r="B223" t="n">
         <v>78766</v>
@@ -24370,10 +24375,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>481434</v>
+        <v>481026</v>
       </c>
       <c r="R223" t="n">
-        <v>6790538</v>
+        <v>6790700</v>
       </c>
       <c r="S223" t="n">
         <v>9</v>
@@ -24405,7 +24410,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24415,7 +24420,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24442,7 +24447,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122959766</v>
+        <v>122968577</v>
       </c>
       <c r="B224" t="n">
         <v>78766</v>
@@ -24482,10 +24487,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>480779</v>
+        <v>481434</v>
       </c>
       <c r="R224" t="n">
-        <v>6790803</v>
+        <v>6790538</v>
       </c>
       <c r="S224" t="n">
         <v>9</v>
@@ -24517,7 +24522,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24527,7 +24532,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24554,10 +24559,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122968198</v>
+        <v>122959766</v>
       </c>
       <c r="B225" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24566,43 +24571,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>481373</v>
+        <v>480779</v>
       </c>
       <c r="R225" t="n">
-        <v>6790551</v>
+        <v>6790803</v>
       </c>
       <c r="S225" t="n">
         <v>9</v>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -28787,10 +28787,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122970166</v>
+        <v>122974049</v>
       </c>
       <c r="B264" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -28803,27 +28803,27 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="M264" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -28832,10 +28832,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>481546</v>
+        <v>481427</v>
       </c>
       <c r="R264" t="n">
-        <v>6790501</v>
+        <v>6790669</v>
       </c>
       <c r="S264" t="n">
         <v>9</v>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -28877,7 +28877,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28904,10 +28904,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122974049</v>
+        <v>122970166</v>
       </c>
       <c r="B265" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -28920,27 +28920,27 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="M265" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
@@ -28949,10 +28949,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>481427</v>
+        <v>481546</v>
       </c>
       <c r="R265" t="n">
-        <v>6790669</v>
+        <v>6790501</v>
       </c>
       <c r="S265" t="n">
         <v>9</v>
@@ -28984,7 +28984,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -33518,10 +33518,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122965865</v>
+        <v>122969887</v>
       </c>
       <c r="B307" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -33534,39 +33534,34 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>481118</v>
+        <v>481534</v>
       </c>
       <c r="R307" t="n">
-        <v>6790699</v>
+        <v>6790501</v>
       </c>
       <c r="S307" t="n">
         <v>9</v>
@@ -33598,7 +33593,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -33608,7 +33603,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33635,7 +33630,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122969887</v>
+        <v>122966647</v>
       </c>
       <c r="B308" t="n">
         <v>78766</v>
@@ -33671,17 +33666,17 @@
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>481534</v>
+        <v>481216</v>
       </c>
       <c r="R308" t="n">
-        <v>6790501</v>
+        <v>6790707</v>
       </c>
       <c r="S308" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -33708,19 +33703,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>14:01</t>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>Torrakor återkommer i området och lågor som visar sig där snön tinat.</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33735,22 +33725,22 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122966647</v>
+        <v>122962565</v>
       </c>
       <c r="B309" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -33763,37 +33753,37 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>481216</v>
+        <v>480854</v>
       </c>
       <c r="R309" t="n">
-        <v>6790707</v>
+        <v>6790625</v>
       </c>
       <c r="S309" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -33820,14 +33810,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC309" t="inlineStr">
-        <is>
-          <t>Torrakor återkommer i området och lågor som visar sig där snön tinat.</t>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33842,22 +33837,22 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122962565</v>
+        <v>122962123</v>
       </c>
       <c r="B310" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -33870,37 +33865,37 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>480854</v>
+        <v>480826</v>
       </c>
       <c r="R310" t="n">
-        <v>6790625</v>
+        <v>6790638</v>
       </c>
       <c r="S310" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -33927,19 +33922,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33954,22 +33939,22 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122962123</v>
+        <v>122965865</v>
       </c>
       <c r="B311" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -33982,37 +33967,42 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>480826</v>
+        <v>481118</v>
       </c>
       <c r="R311" t="n">
-        <v>6790638</v>
+        <v>6790699</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -34039,9 +34029,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA311" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -34056,12 +34056,12 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122915083</v>
+        <v>122908063</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,42 +1858,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480681</v>
+        <v>480571</v>
       </c>
       <c r="R13" t="n">
-        <v>6790816</v>
+        <v>6790798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1935,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,19 +1942,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122913918</v>
+        <v>122908671</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1998,17 +1990,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481291</v>
+        <v>480766</v>
       </c>
       <c r="R14" t="n">
-        <v>6790740</v>
+        <v>6790505</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2035,19 +2027,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,22 +2044,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122908063</v>
+        <v>122913095</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,38 +2068,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480571</v>
+        <v>480874</v>
       </c>
       <c r="R15" t="n">
-        <v>6790798</v>
+        <v>6790659</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,19 +2129,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,19 +2146,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122908671</v>
+        <v>122909041</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2226,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480766</v>
+        <v>480660</v>
       </c>
       <c r="R16" t="n">
-        <v>6790505</v>
+        <v>6790681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,9 +2231,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,19 +2258,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122913095</v>
+        <v>122907325</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2324,14 +2306,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480874</v>
+        <v>480575</v>
       </c>
       <c r="R17" t="n">
-        <v>6790659</v>
+        <v>6790808</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,9 +2343,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,19 +2370,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122909041</v>
+        <v>122906911</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2426,14 +2418,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480660</v>
+        <v>480638</v>
       </c>
       <c r="R18" t="n">
-        <v>6790681</v>
+        <v>6790783</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2475,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122907325</v>
+        <v>122910575</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2538,14 +2530,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480575</v>
+        <v>480772</v>
       </c>
       <c r="R19" t="n">
-        <v>6790808</v>
+        <v>6790602</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,19 +2567,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2602,19 +2584,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122906911</v>
+        <v>122913854</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2654,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480638</v>
+        <v>481200</v>
       </c>
       <c r="R20" t="n">
-        <v>6790783</v>
+        <v>6790675</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2689,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2699,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,19 +2696,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122910575</v>
+        <v>122917054</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2766,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480772</v>
+        <v>481414</v>
       </c>
       <c r="R21" t="n">
-        <v>6790602</v>
+        <v>6790487</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122913854</v>
+        <v>122913962</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2868,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481200</v>
+        <v>481216</v>
       </c>
       <c r="R22" t="n">
         <v>6790675</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2903,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2913,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122917054</v>
+        <v>122915083</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,38 +2934,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481414</v>
+        <v>480681</v>
       </c>
       <c r="R23" t="n">
-        <v>6790487</v>
+        <v>6790816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,9 +3003,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3030,19 +3030,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122913962</v>
+        <v>122913918</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481216</v>
+        <v>481291</v>
       </c>
       <c r="R24" t="n">
-        <v>6790675</v>
+        <v>6790740</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3142,22 +3142,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908784</v>
+        <v>122917610</v>
       </c>
       <c r="B25" t="n">
-        <v>78411</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,38 +3166,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480639</v>
+        <v>480786</v>
       </c>
       <c r="R25" t="n">
-        <v>6790797</v>
+        <v>6790628</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,19 +3232,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,22 +3249,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122907867</v>
+        <v>122913869</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3282,34 +3277,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480744</v>
+        <v>480861</v>
       </c>
       <c r="R26" t="n">
-        <v>6790595</v>
+        <v>6790634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,7 +3368,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122914964</v>
+        <v>122905638</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3404,17 +3404,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480805</v>
+        <v>480687</v>
       </c>
       <c r="R27" t="n">
-        <v>6790675</v>
+        <v>6790754</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3441,19 +3441,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,22 +3458,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122906981</v>
+        <v>122908658</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3492,41 +3482,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480725</v>
+        <v>480701</v>
       </c>
       <c r="R28" t="n">
-        <v>6790654</v>
+        <v>6790532</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3553,9 +3543,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3570,22 +3570,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908392</v>
+        <v>122908784</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3598,37 +3598,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480628</v>
+        <v>480639</v>
       </c>
       <c r="R29" t="n">
-        <v>6790661</v>
+        <v>6790797</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,19 +3682,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122912843</v>
+        <v>122907867</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3730,17 +3730,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481068</v>
+        <v>480744</v>
       </c>
       <c r="R30" t="n">
-        <v>6790734</v>
+        <v>6790595</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3767,19 +3767,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,19 +3784,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122908033</v>
+        <v>122914964</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3842,17 +3832,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480735</v>
+        <v>480805</v>
       </c>
       <c r="R31" t="n">
-        <v>6790566</v>
+        <v>6790675</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3879,9 +3869,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3896,19 +3896,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122910046</v>
+        <v>122906981</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3951,7 +3951,7 @@
         <v>480725</v>
       </c>
       <c r="R32" t="n">
-        <v>6790756</v>
+        <v>6790654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122916802</v>
+        <v>122908392</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4046,17 +4046,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481344</v>
+        <v>480628</v>
       </c>
       <c r="R33" t="n">
-        <v>6790501</v>
+        <v>6790661</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4083,9 +4083,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4100,19 +4110,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122915538</v>
+        <v>122912843</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4148,17 +4158,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481062</v>
+        <v>481068</v>
       </c>
       <c r="R34" t="n">
-        <v>6790598</v>
+        <v>6790734</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4185,9 +4195,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4202,19 +4222,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122914138</v>
+        <v>122908033</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4254,10 +4274,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480858</v>
+        <v>480735</v>
       </c>
       <c r="R35" t="n">
-        <v>6790672</v>
+        <v>6790566</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122917610</v>
+        <v>122910046</v>
       </c>
       <c r="B36" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4328,43 +4348,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480786</v>
+        <v>480725</v>
       </c>
       <c r="R36" t="n">
-        <v>6790628</v>
+        <v>6790756</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4423,10 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122913869</v>
+        <v>122916802</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4439,39 +4454,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480861</v>
+        <v>481344</v>
       </c>
       <c r="R37" t="n">
-        <v>6790634</v>
+        <v>6790501</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4530,7 +4540,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122905638</v>
+        <v>122915538</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4570,10 +4580,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480687</v>
+        <v>481062</v>
       </c>
       <c r="R38" t="n">
-        <v>6790754</v>
+        <v>6790598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4632,10 +4642,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908658</v>
+        <v>122914138</v>
       </c>
       <c r="B39" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4644,41 +4654,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480701</v>
+        <v>480858</v>
       </c>
       <c r="R39" t="n">
-        <v>6790532</v>
+        <v>6790672</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4705,19 +4715,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4732,12 +4732,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122905560</v>
+        <v>122905949</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480689</v>
+        <v>480710</v>
       </c>
       <c r="R46" t="n">
-        <v>6790776</v>
+        <v>6790729</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122910737</v>
+        <v>122905769</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480800</v>
+        <v>480697</v>
       </c>
       <c r="R47" t="n">
-        <v>6790542</v>
+        <v>6790747</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122913871</v>
+        <v>122907225</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481264</v>
+        <v>480622</v>
       </c>
       <c r="R48" t="n">
-        <v>6790709</v>
+        <v>6790776</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5680,19 +5680,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122914302</v>
+        <v>122907981</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5728,17 +5728,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480864</v>
+        <v>480580</v>
       </c>
       <c r="R49" t="n">
-        <v>6790682</v>
+        <v>6790754</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5765,9 +5765,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5782,19 +5792,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122905949</v>
+        <v>122914293</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5830,17 +5840,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480710</v>
+        <v>481318</v>
       </c>
       <c r="R50" t="n">
-        <v>6790729</v>
+        <v>6790679</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5867,9 +5877,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5884,19 +5904,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122905769</v>
+        <v>122910257</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5932,17 +5952,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480697</v>
+        <v>480680</v>
       </c>
       <c r="R51" t="n">
-        <v>6790747</v>
+        <v>6790662</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5969,9 +5989,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5986,19 +6016,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122907225</v>
+        <v>122906759</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6034,17 +6064,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480622</v>
+        <v>480726</v>
       </c>
       <c r="R52" t="n">
-        <v>6790776</v>
+        <v>6790689</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6071,19 +6101,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6098,19 +6118,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122907981</v>
+        <v>122907426</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6146,17 +6166,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480580</v>
+        <v>480611</v>
       </c>
       <c r="R53" t="n">
-        <v>6790754</v>
+        <v>6790803</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6185,7 +6205,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6195,7 +6215,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6210,19 +6230,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122914293</v>
+        <v>122910531</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6258,17 +6278,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481318</v>
+        <v>480772</v>
       </c>
       <c r="R54" t="n">
-        <v>6790679</v>
+        <v>6790619</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6295,19 +6315,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6322,19 +6332,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122910257</v>
+        <v>122914414</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6374,13 +6384,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480680</v>
+        <v>481039</v>
       </c>
       <c r="R55" t="n">
-        <v>6790662</v>
+        <v>6790686</v>
       </c>
       <c r="S55" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6409,7 +6419,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6419,7 +6429,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6434,19 +6444,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122906759</v>
+        <v>122911585</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6482,17 +6492,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480726</v>
+        <v>481035</v>
       </c>
       <c r="R56" t="n">
-        <v>6790689</v>
+        <v>6790750</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6519,9 +6529,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6536,19 +6556,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122907426</v>
+        <v>122905560</v>
       </c>
       <c r="B57" t="n">
         <v>78766</v>
@@ -6588,10 +6608,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480611</v>
+        <v>480689</v>
       </c>
       <c r="R57" t="n">
-        <v>6790803</v>
+        <v>6790776</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6621,19 +6641,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6648,19 +6658,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122910531</v>
+        <v>122910737</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6700,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480772</v>
+        <v>480800</v>
       </c>
       <c r="R58" t="n">
-        <v>6790619</v>
+        <v>6790542</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6762,7 +6772,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122914414</v>
+        <v>122913871</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6802,10 +6812,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481039</v>
+        <v>481264</v>
       </c>
       <c r="R59" t="n">
-        <v>6790686</v>
+        <v>6790709</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6837,7 +6847,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6847,7 +6857,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6874,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122911585</v>
+        <v>122914302</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6910,17 +6920,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481035</v>
+        <v>480864</v>
       </c>
       <c r="R60" t="n">
-        <v>6790750</v>
+        <v>6790682</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6947,19 +6957,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6974,12 +6974,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -8581,7 +8581,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122905989</v>
+        <v>122906205</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -8621,10 +8621,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480688</v>
+        <v>480708</v>
       </c>
       <c r="R76" t="n">
-        <v>6790702</v>
+        <v>6790701</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8683,7 +8683,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122914913</v>
+        <v>122912740</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480848</v>
+        <v>481151</v>
       </c>
       <c r="R77" t="n">
-        <v>6790704</v>
+        <v>6790720</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8795,7 +8795,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122906205</v>
+        <v>122907575</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8831,17 +8831,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480708</v>
+        <v>480571</v>
       </c>
       <c r="R78" t="n">
-        <v>6790701</v>
+        <v>6790798</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8868,9 +8868,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8885,19 +8895,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122912740</v>
+        <v>122908626</v>
       </c>
       <c r="B79" t="n">
         <v>78766</v>
@@ -8933,17 +8943,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481151</v>
+        <v>480639</v>
       </c>
       <c r="R79" t="n">
-        <v>6790720</v>
+        <v>6790797</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8972,7 +8982,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8982,7 +8992,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8997,19 +9007,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122907575</v>
+        <v>122905989</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -9045,17 +9055,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480571</v>
+        <v>480688</v>
       </c>
       <c r="R80" t="n">
-        <v>6790798</v>
+        <v>6790702</v>
       </c>
       <c r="S80" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9082,19 +9092,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9109,19 +9109,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122908626</v>
+        <v>122914913</v>
       </c>
       <c r="B81" t="n">
         <v>78766</v>
@@ -9157,17 +9157,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480639</v>
+        <v>480848</v>
       </c>
       <c r="R81" t="n">
-        <v>6790797</v>
+        <v>6790704</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9221,22 +9221,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122916590</v>
+        <v>122908368</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481290</v>
+        <v>480704</v>
       </c>
       <c r="R82" t="n">
-        <v>6790576</v>
+        <v>6790523</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122907579</v>
+        <v>122915141</v>
       </c>
       <c r="B83" t="n">
         <v>78766</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480739</v>
+        <v>480999</v>
       </c>
       <c r="R83" t="n">
-        <v>6790609</v>
+        <v>6790659</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122913923</v>
+        <v>122908430</v>
       </c>
       <c r="B84" t="n">
         <v>78766</v>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480817</v>
+        <v>480722</v>
       </c>
       <c r="R84" t="n">
-        <v>6790670</v>
+        <v>6790508</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9539,7 +9539,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122915252</v>
+        <v>122907562</v>
       </c>
       <c r="B85" t="n">
         <v>78766</v>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481010</v>
+        <v>480739</v>
       </c>
       <c r="R85" t="n">
-        <v>6790656</v>
+        <v>6790609</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9641,10 +9641,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122908690</v>
+        <v>122913909</v>
       </c>
       <c r="B86" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9657,37 +9657,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480626</v>
+        <v>480837</v>
       </c>
       <c r="R86" t="n">
-        <v>6790648</v>
+        <v>6790651</v>
       </c>
       <c r="S86" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9714,19 +9714,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9741,22 +9731,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122913735</v>
+        <v>122913714</v>
       </c>
       <c r="B87" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9769,37 +9759,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481068</v>
+        <v>480860</v>
       </c>
       <c r="R87" t="n">
-        <v>6790734</v>
+        <v>6790660</v>
       </c>
       <c r="S87" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9826,19 +9816,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9853,22 +9833,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122908368</v>
+        <v>122908177</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9881,37 +9861,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480704</v>
+        <v>480606</v>
       </c>
       <c r="R88" t="n">
-        <v>6790523</v>
+        <v>6790682</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9938,9 +9918,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9955,19 +9945,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122915141</v>
+        <v>122910695</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -10007,10 +9997,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480999</v>
+        <v>480801</v>
       </c>
       <c r="R89" t="n">
-        <v>6790659</v>
+        <v>6790557</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10069,10 +10059,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122908430</v>
+        <v>122916590</v>
       </c>
       <c r="B90" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10085,21 +10075,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10109,10 +10099,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480722</v>
+        <v>481290</v>
       </c>
       <c r="R90" t="n">
-        <v>6790508</v>
+        <v>6790576</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,7 +10161,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122913909</v>
+        <v>122913923</v>
       </c>
       <c r="B91" t="n">
         <v>78766</v>
@@ -10211,10 +10201,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480837</v>
+        <v>480817</v>
       </c>
       <c r="R91" t="n">
-        <v>6790651</v>
+        <v>6790670</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10273,7 +10263,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122913714</v>
+        <v>122915252</v>
       </c>
       <c r="B92" t="n">
         <v>78766</v>
@@ -10313,10 +10303,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480860</v>
+        <v>481010</v>
       </c>
       <c r="R92" t="n">
-        <v>6790660</v>
+        <v>6790656</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10375,10 +10365,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122908177</v>
+        <v>122908690</v>
       </c>
       <c r="B93" t="n">
-        <v>78502</v>
+        <v>78411</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10391,21 +10381,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10415,13 +10405,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480606</v>
+        <v>480626</v>
       </c>
       <c r="R93" t="n">
-        <v>6790682</v>
+        <v>6790648</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10450,7 +10440,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10460,7 +10450,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10475,22 +10465,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122910695</v>
+        <v>122913735</v>
       </c>
       <c r="B94" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10503,37 +10493,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480801</v>
+        <v>481068</v>
       </c>
       <c r="R94" t="n">
-        <v>6790557</v>
+        <v>6790734</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10560,9 +10550,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10577,12 +10577,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11550,7 +11550,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122907941</v>
+        <v>122914329</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11586,17 +11586,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>480736</v>
+        <v>481184</v>
       </c>
       <c r="R104" t="n">
-        <v>6790589</v>
+        <v>6790659</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11623,9 +11623,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11640,19 +11650,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122905837</v>
+        <v>122908564</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -11688,17 +11698,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480679</v>
+        <v>480648</v>
       </c>
       <c r="R105" t="n">
-        <v>6790740</v>
+        <v>6790546</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11725,9 +11735,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11742,19 +11762,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122914257</v>
+        <v>122914370</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -11794,13 +11814,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>481217</v>
+        <v>481130</v>
       </c>
       <c r="R106" t="n">
-        <v>6790566</v>
+        <v>6790661</v>
       </c>
       <c r="S106" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11829,7 +11849,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11839,7 +11859,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11854,19 +11874,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122914329</v>
+        <v>122915272</v>
       </c>
       <c r="B107" t="n">
         <v>78766</v>
@@ -11902,17 +11922,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>481184</v>
+        <v>481024</v>
       </c>
       <c r="R107" t="n">
-        <v>6790659</v>
+        <v>6790673</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11939,19 +11959,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11966,19 +11976,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122908564</v>
+        <v>122907818</v>
       </c>
       <c r="B108" t="n">
         <v>78766</v>
@@ -12018,10 +12028,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480648</v>
+        <v>480545</v>
       </c>
       <c r="R108" t="n">
-        <v>6790546</v>
+        <v>6790776</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12053,7 +12063,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12063,7 +12073,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12090,7 +12100,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122914370</v>
+        <v>122908082</v>
       </c>
       <c r="B109" t="n">
         <v>78766</v>
@@ -12130,10 +12140,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>481130</v>
+        <v>480607</v>
       </c>
       <c r="R109" t="n">
-        <v>6790661</v>
+        <v>6790687</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12165,7 +12175,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12175,7 +12185,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12202,7 +12212,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122915272</v>
+        <v>122908696</v>
       </c>
       <c r="B110" t="n">
         <v>78766</v>
@@ -12238,17 +12248,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>481024</v>
+        <v>480701</v>
       </c>
       <c r="R110" t="n">
-        <v>6790673</v>
+        <v>6790532</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12275,9 +12285,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12292,22 +12312,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122907818</v>
+        <v>122908121</v>
       </c>
       <c r="B111" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12316,25 +12336,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12344,13 +12364,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480545</v>
+        <v>480638</v>
       </c>
       <c r="R111" t="n">
-        <v>6790776</v>
+        <v>6790738</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12379,7 +12399,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12389,7 +12409,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12404,19 +12424,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122908082</v>
+        <v>122907941</v>
       </c>
       <c r="B112" t="n">
         <v>78766</v>
@@ -12452,17 +12472,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480607</v>
+        <v>480736</v>
       </c>
       <c r="R112" t="n">
-        <v>6790687</v>
+        <v>6790589</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12489,19 +12509,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12516,19 +12526,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122908696</v>
+        <v>122905837</v>
       </c>
       <c r="B113" t="n">
         <v>78766</v>
@@ -12564,17 +12574,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480701</v>
+        <v>480679</v>
       </c>
       <c r="R113" t="n">
-        <v>6790532</v>
+        <v>6790740</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12601,19 +12611,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12628,22 +12628,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122908121</v>
+        <v>122914257</v>
       </c>
       <c r="B114" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12652,25 +12652,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12680,10 +12680,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>480638</v>
+        <v>481217</v>
       </c>
       <c r="R114" t="n">
-        <v>6790738</v>
+        <v>6790566</v>
       </c>
       <c r="S114" t="n">
         <v>11</v>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -16029,7 +16029,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122911477</v>
+        <v>122911259</v>
       </c>
       <c r="B146" t="n">
         <v>78766</v>
@@ -16069,10 +16069,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>481096</v>
+        <v>481008</v>
       </c>
       <c r="R146" t="n">
-        <v>6790743</v>
+        <v>6790695</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16141,7 +16141,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122910453</v>
+        <v>122910505</v>
       </c>
       <c r="B147" t="n">
         <v>78766</v>
@@ -16181,10 +16181,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>480761</v>
+        <v>480770</v>
       </c>
       <c r="R147" t="n">
-        <v>6790650</v>
+        <v>6790637</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16243,10 +16243,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122907348</v>
+        <v>122909048</v>
       </c>
       <c r="B148" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16255,38 +16255,47 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480716</v>
+        <v>480660</v>
       </c>
       <c r="R148" t="n">
-        <v>6790617</v>
+        <v>6790681</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16316,36 +16325,47 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122911259</v>
+        <v>122911477</v>
       </c>
       <c r="B149" t="n">
         <v>78766</v>
@@ -16385,10 +16405,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>481008</v>
+        <v>481096</v>
       </c>
       <c r="R149" t="n">
-        <v>6790695</v>
+        <v>6790743</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16420,7 +16440,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16430,7 +16450,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16457,7 +16477,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122910505</v>
+        <v>122910453</v>
       </c>
       <c r="B150" t="n">
         <v>78766</v>
@@ -16497,10 +16517,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>480770</v>
+        <v>480761</v>
       </c>
       <c r="R150" t="n">
-        <v>6790637</v>
+        <v>6790650</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16559,10 +16579,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122909048</v>
+        <v>122907348</v>
       </c>
       <c r="B151" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16571,47 +16591,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480660</v>
+        <v>480716</v>
       </c>
       <c r="R151" t="n">
-        <v>6790681</v>
+        <v>6790617</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16641,50 +16652,39 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122915190</v>
+        <v>122916175</v>
       </c>
       <c r="B152" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16697,37 +16697,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480830</v>
+        <v>481253</v>
       </c>
       <c r="R152" t="n">
-        <v>6790684</v>
+        <v>6790554</v>
       </c>
       <c r="S152" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16754,19 +16754,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16781,19 +16771,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122910652</v>
+        <v>122916996</v>
       </c>
       <c r="B153" t="n">
         <v>78766</v>
@@ -16833,10 +16823,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480780</v>
+        <v>481382</v>
       </c>
       <c r="R153" t="n">
-        <v>6790598</v>
+        <v>6790485</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16895,7 +16885,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122914846</v>
+        <v>122909144</v>
       </c>
       <c r="B154" t="n">
         <v>78766</v>
@@ -16931,17 +16921,17 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480895</v>
+        <v>480738</v>
       </c>
       <c r="R154" t="n">
-        <v>6790735</v>
+        <v>6790666</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16968,19 +16958,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16995,22 +16975,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122910462</v>
+        <v>122915190</v>
       </c>
       <c r="B155" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17023,21 +17003,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17047,13 +17027,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480753</v>
+        <v>480830</v>
       </c>
       <c r="R155" t="n">
-        <v>6790776</v>
+        <v>6790684</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17082,7 +17062,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17092,7 +17072,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17107,19 +17087,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122916175</v>
+        <v>122910652</v>
       </c>
       <c r="B156" t="n">
         <v>78766</v>
@@ -17159,10 +17139,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>481253</v>
+        <v>480780</v>
       </c>
       <c r="R156" t="n">
-        <v>6790554</v>
+        <v>6790598</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17221,7 +17201,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122916996</v>
+        <v>122914846</v>
       </c>
       <c r="B157" t="n">
         <v>78766</v>
@@ -17257,17 +17237,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>481382</v>
+        <v>480895</v>
       </c>
       <c r="R157" t="n">
-        <v>6790485</v>
+        <v>6790735</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17294,9 +17274,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17311,19 +17301,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122909144</v>
+        <v>122910462</v>
       </c>
       <c r="B158" t="n">
         <v>78766</v>
@@ -17359,14 +17349,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480738</v>
+        <v>480753</v>
       </c>
       <c r="R158" t="n">
-        <v>6790666</v>
+        <v>6790776</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17396,9 +17386,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17413,22 +17413,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122914092</v>
+        <v>122911238</v>
       </c>
       <c r="B159" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17437,25 +17437,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17465,13 +17465,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>481216</v>
+        <v>481009</v>
       </c>
       <c r="R159" t="n">
-        <v>6790675</v>
+        <v>6790696</v>
       </c>
       <c r="S159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17525,22 +17525,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122908196</v>
+        <v>122909092</v>
       </c>
       <c r="B160" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17549,38 +17549,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>480681</v>
+        <v>480626</v>
       </c>
       <c r="R160" t="n">
-        <v>6790816</v>
+        <v>6790648</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17612,7 +17612,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17637,19 +17637,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122911238</v>
+        <v>122913997</v>
       </c>
       <c r="B161" t="n">
         <v>78766</v>
@@ -17689,13 +17689,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>481009</v>
+        <v>481407</v>
       </c>
       <c r="R161" t="n">
-        <v>6790696</v>
+        <v>6790724</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17761,7 +17761,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122909092</v>
+        <v>122910124</v>
       </c>
       <c r="B162" t="n">
         <v>78766</v>
@@ -17797,14 +17797,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>480626</v>
+        <v>480730</v>
       </c>
       <c r="R162" t="n">
-        <v>6790648</v>
+        <v>6790750</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17834,19 +17834,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17861,19 +17851,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122913997</v>
+        <v>122914420</v>
       </c>
       <c r="B163" t="n">
         <v>78766</v>
@@ -17913,10 +17903,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>481407</v>
+        <v>481040</v>
       </c>
       <c r="R163" t="n">
-        <v>6790724</v>
+        <v>6790687</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -17948,7 +17938,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17958,7 +17948,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17985,10 +17975,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>122910124</v>
+        <v>122914092</v>
       </c>
       <c r="B164" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17997,41 +17987,41 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>480730</v>
+        <v>481216</v>
       </c>
       <c r="R164" t="n">
-        <v>6790750</v>
+        <v>6790675</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18058,9 +18048,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18075,22 +18075,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122913790</v>
+        <v>122908196</v>
       </c>
       <c r="B165" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18103,45 +18103,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>481264</v>
+        <v>480681</v>
       </c>
       <c r="R165" t="n">
-        <v>6790709</v>
+        <v>6790816</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18170,7 +18162,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18180,7 +18172,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18195,22 +18187,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122914420</v>
+        <v>122913790</v>
       </c>
       <c r="B166" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18219,38 +18211,46 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>481040</v>
+        <v>481264</v>
       </c>
       <c r="R166" t="n">
-        <v>6790687</v>
+        <v>6790709</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20458,7 +20458,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122962209</v>
+        <v>122970196</v>
       </c>
       <c r="B187" t="n">
         <v>78766</v>
@@ -20498,10 +20498,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>480818</v>
+        <v>481598</v>
       </c>
       <c r="R187" t="n">
-        <v>6790633</v>
+        <v>6790481</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20560,7 +20560,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122970196</v>
+        <v>122962209</v>
       </c>
       <c r="B188" t="n">
         <v>78766</v>
@@ -20600,10 +20600,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>481598</v>
+        <v>480818</v>
       </c>
       <c r="R188" t="n">
-        <v>6790481</v>
+        <v>6790633</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -22613,10 +22613,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122975234</v>
+        <v>122967764</v>
       </c>
       <c r="B207" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22629,37 +22629,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>481459</v>
+        <v>481304</v>
       </c>
       <c r="R207" t="n">
-        <v>6790740</v>
+        <v>6790615</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22686,9 +22686,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22703,19 +22713,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122967764</v>
+        <v>122962111</v>
       </c>
       <c r="B208" t="n">
         <v>78766</v>
@@ -22751,17 +22761,17 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>481304</v>
+        <v>480804</v>
       </c>
       <c r="R208" t="n">
-        <v>6790615</v>
+        <v>6790650</v>
       </c>
       <c r="S208" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22788,19 +22798,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22815,19 +22815,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122962111</v>
+        <v>122960241</v>
       </c>
       <c r="B209" t="n">
         <v>78766</v>
@@ -22867,10 +22867,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>480804</v>
+        <v>480794</v>
       </c>
       <c r="R209" t="n">
-        <v>6790650</v>
+        <v>6790801</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22929,7 +22929,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122960241</v>
+        <v>122967506</v>
       </c>
       <c r="B210" t="n">
         <v>78766</v>
@@ -22965,17 +22965,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>480794</v>
+        <v>481250</v>
       </c>
       <c r="R210" t="n">
-        <v>6790801</v>
+        <v>6790669</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23002,9 +23002,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23019,19 +23029,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122967506</v>
+        <v>122977930</v>
       </c>
       <c r="B211" t="n">
         <v>78766</v>
@@ -23067,17 +23077,17 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>481250</v>
+        <v>481202</v>
       </c>
       <c r="R211" t="n">
-        <v>6790669</v>
+        <v>6790769</v>
       </c>
       <c r="S211" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23104,19 +23114,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Garn inom synfältet, ca 50 meter i radie.</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23131,19 +23136,19 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122977930</v>
+        <v>122966180</v>
       </c>
       <c r="B212" t="n">
         <v>78766</v>
@@ -23179,17 +23184,17 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>481202</v>
+        <v>481151</v>
       </c>
       <c r="R212" t="n">
-        <v>6790769</v>
+        <v>6790709</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23216,14 +23221,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Garn inom synfältet, ca 50 meter i radie.</t>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23238,19 +23248,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>122966180</v>
+        <v>122965694</v>
       </c>
       <c r="B213" t="n">
         <v>78766</v>
@@ -23290,10 +23300,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>481151</v>
+        <v>481111</v>
       </c>
       <c r="R213" t="n">
-        <v>6790709</v>
+        <v>6790702</v>
       </c>
       <c r="S213" t="n">
         <v>9</v>
@@ -23325,7 +23335,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23335,7 +23345,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23362,7 +23372,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122965694</v>
+        <v>122975263</v>
       </c>
       <c r="B214" t="n">
         <v>78766</v>
@@ -23402,10 +23412,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>481111</v>
+        <v>481394</v>
       </c>
       <c r="R214" t="n">
-        <v>6790702</v>
+        <v>6790770</v>
       </c>
       <c r="S214" t="n">
         <v>9</v>
@@ -23437,7 +23447,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23447,7 +23457,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23474,10 +23484,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122975263</v>
+        <v>122975234</v>
       </c>
       <c r="B215" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23490,37 +23500,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>481394</v>
+        <v>481459</v>
       </c>
       <c r="R215" t="n">
-        <v>6790770</v>
+        <v>6790740</v>
       </c>
       <c r="S215" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -23547,19 +23557,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>16:28</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23574,12 +23574,12 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
@@ -24116,10 +24116,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122968198</v>
+        <v>122961613</v>
       </c>
       <c r="B221" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24128,46 +24128,41 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>481373</v>
+        <v>480767</v>
       </c>
       <c r="R221" t="n">
-        <v>6790551</v>
+        <v>6790673</v>
       </c>
       <c r="S221" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24194,19 +24189,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24221,19 +24206,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122961613</v>
+        <v>122964950</v>
       </c>
       <c r="B222" t="n">
         <v>78766</v>
@@ -24269,17 +24254,17 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>480767</v>
+        <v>481026</v>
       </c>
       <c r="R222" t="n">
-        <v>6790673</v>
+        <v>6790700</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24306,9 +24291,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24323,19 +24318,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122964950</v>
+        <v>122968577</v>
       </c>
       <c r="B223" t="n">
         <v>78766</v>
@@ -24375,10 +24370,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>481026</v>
+        <v>481434</v>
       </c>
       <c r="R223" t="n">
-        <v>6790700</v>
+        <v>6790538</v>
       </c>
       <c r="S223" t="n">
         <v>9</v>
@@ -24410,7 +24405,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24420,7 +24415,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24447,7 +24442,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122968577</v>
+        <v>122959766</v>
       </c>
       <c r="B224" t="n">
         <v>78766</v>
@@ -24487,10 +24482,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>481434</v>
+        <v>480779</v>
       </c>
       <c r="R224" t="n">
-        <v>6790538</v>
+        <v>6790803</v>
       </c>
       <c r="S224" t="n">
         <v>9</v>
@@ -24522,7 +24517,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24532,7 +24527,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24559,10 +24554,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122959766</v>
+        <v>122968198</v>
       </c>
       <c r="B225" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24571,38 +24566,43 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>480779</v>
+        <v>481373</v>
       </c>
       <c r="R225" t="n">
-        <v>6790803</v>
+        <v>6790551</v>
       </c>
       <c r="S225" t="n">
         <v>9</v>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26067,10 +26067,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>122977806</v>
+        <v>122965139</v>
       </c>
       <c r="B239" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -26079,38 +26079,38 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>481253</v>
+        <v>481024</v>
       </c>
       <c r="R239" t="n">
-        <v>6790770</v>
+        <v>6790713</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26143,11 +26143,6 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Gar inom synfältet i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26174,7 +26169,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>122968760</v>
+        <v>122977806</v>
       </c>
       <c r="B240" t="n">
         <v>78766</v>
@@ -26210,17 +26205,17 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>481444</v>
+        <v>481253</v>
       </c>
       <c r="R240" t="n">
-        <v>6790544</v>
+        <v>6790770</v>
       </c>
       <c r="S240" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -26247,19 +26242,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>Gar inom synfältet i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -26274,19 +26264,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>122973309</v>
+        <v>122968760</v>
       </c>
       <c r="B241" t="n">
         <v>78766</v>
@@ -26326,10 +26316,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>481568</v>
+        <v>481444</v>
       </c>
       <c r="R241" t="n">
-        <v>6790545</v>
+        <v>6790544</v>
       </c>
       <c r="S241" t="n">
         <v>9</v>
@@ -26361,7 +26351,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -26371,7 +26361,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -26398,7 +26388,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>122960406</v>
+        <v>122973309</v>
       </c>
       <c r="B242" t="n">
         <v>78766</v>
@@ -26434,17 +26424,17 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>480766</v>
+        <v>481568</v>
       </c>
       <c r="R242" t="n">
-        <v>6790785</v>
+        <v>6790545</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -26471,9 +26461,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -26488,19 +26488,19 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122962130</v>
+        <v>122960406</v>
       </c>
       <c r="B243" t="n">
         <v>78766</v>
@@ -26536,17 +26536,17 @@
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>480812</v>
+        <v>480766</v>
       </c>
       <c r="R243" t="n">
-        <v>6790632</v>
+        <v>6790785</v>
       </c>
       <c r="S243" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -26573,19 +26573,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>11:25</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26600,22 +26590,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122978194</v>
+        <v>122962130</v>
       </c>
       <c r="B244" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -26624,43 +26614,38 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>481090</v>
+        <v>480812</v>
       </c>
       <c r="R244" t="n">
-        <v>6790709</v>
+        <v>6790632</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -26692,7 +26677,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -26702,7 +26687,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26729,10 +26714,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122965139</v>
+        <v>122978194</v>
       </c>
       <c r="B245" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -26745,37 +26730,42 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>481024</v>
+        <v>481090</v>
       </c>
       <c r="R245" t="n">
-        <v>6790713</v>
+        <v>6790709</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -26802,9 +26792,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26819,12 +26819,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
@@ -28237,10 +28237,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122969848</v>
+        <v>122968533</v>
       </c>
       <c r="B259" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -28253,16 +28253,16 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -28273,17 +28273,17 @@
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>481544</v>
+        <v>481432</v>
       </c>
       <c r="R259" t="n">
-        <v>6790494</v>
+        <v>6790537</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -28310,14 +28310,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -28332,19 +28337,19 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122968533</v>
+        <v>122975494</v>
       </c>
       <c r="B260" t="n">
         <v>78766</v>
@@ -28380,17 +28385,17 @@
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>481432</v>
+        <v>481441</v>
       </c>
       <c r="R260" t="n">
-        <v>6790537</v>
+        <v>6790760</v>
       </c>
       <c r="S260" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -28417,19 +28422,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>13:34</t>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Garn med miljöbild</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -28444,22 +28444,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122975494</v>
+        <v>122965948</v>
       </c>
       <c r="B261" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -28468,41 +28468,41 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>481441</v>
+        <v>481142</v>
       </c>
       <c r="R261" t="n">
-        <v>6790760</v>
+        <v>6790715</v>
       </c>
       <c r="S261" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -28529,14 +28529,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Garn med miljöbild</t>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -28551,22 +28556,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122965948</v>
+        <v>122977985</v>
       </c>
       <c r="B262" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -28575,25 +28580,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -28603,10 +28608,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>481142</v>
+        <v>481229</v>
       </c>
       <c r="R262" t="n">
-        <v>6790715</v>
+        <v>6790728</v>
       </c>
       <c r="S262" t="n">
         <v>9</v>
@@ -28638,7 +28643,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -28648,7 +28653,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28675,10 +28680,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122977985</v>
+        <v>122969848</v>
       </c>
       <c r="B263" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -28691,16 +28696,16 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -28711,17 +28716,17 @@
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>481229</v>
+        <v>481544</v>
       </c>
       <c r="R263" t="n">
-        <v>6790728</v>
+        <v>6790494</v>
       </c>
       <c r="S263" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -28748,19 +28753,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>17:20</t>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28775,22 +28775,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122974049</v>
+        <v>122969800</v>
       </c>
       <c r="B264" t="n">
-        <v>56688</v>
+        <v>78790</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -28803,39 +28803,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>481427</v>
+        <v>481538</v>
       </c>
       <c r="R264" t="n">
-        <v>6790669</v>
+        <v>6790506</v>
       </c>
       <c r="S264" t="n">
         <v>9</v>
@@ -28867,7 +28862,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -28877,7 +28872,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29021,10 +29016,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122969800</v>
+        <v>122974049</v>
       </c>
       <c r="B266" t="n">
-        <v>78790</v>
+        <v>56688</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -29037,34 +29032,39 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>481538</v>
+        <v>481427</v>
       </c>
       <c r="R266" t="n">
-        <v>6790506</v>
+        <v>6790669</v>
       </c>
       <c r="S266" t="n">
         <v>9</v>
@@ -29096,7 +29096,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -29106,7 +29106,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -33518,10 +33518,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122969887</v>
+        <v>122965865</v>
       </c>
       <c r="B307" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -33534,34 +33534,39 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>481534</v>
+        <v>481118</v>
       </c>
       <c r="R307" t="n">
-        <v>6790501</v>
+        <v>6790699</v>
       </c>
       <c r="S307" t="n">
         <v>9</v>
@@ -33593,7 +33598,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -33603,7 +33608,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33630,7 +33635,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122966647</v>
+        <v>122969887</v>
       </c>
       <c r="B308" t="n">
         <v>78766</v>
@@ -33666,17 +33671,17 @@
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>481216</v>
+        <v>481534</v>
       </c>
       <c r="R308" t="n">
-        <v>6790707</v>
+        <v>6790501</v>
       </c>
       <c r="S308" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -33703,14 +33708,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>Torrakor återkommer i området och lågor som visar sig där snön tinat.</t>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33725,22 +33735,22 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122962565</v>
+        <v>122966647</v>
       </c>
       <c r="B309" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -33753,37 +33763,37 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>480854</v>
+        <v>481216</v>
       </c>
       <c r="R309" t="n">
-        <v>6790625</v>
+        <v>6790707</v>
       </c>
       <c r="S309" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -33810,19 +33820,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB309" t="inlineStr">
-        <is>
-          <t>11:37</t>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>Torrakor återkommer i området och lågor som visar sig där snön tinat.</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33837,22 +33842,22 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122962123</v>
+        <v>122962565</v>
       </c>
       <c r="B310" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -33865,37 +33870,37 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>480826</v>
+        <v>480854</v>
       </c>
       <c r="R310" t="n">
-        <v>6790638</v>
+        <v>6790625</v>
       </c>
       <c r="S310" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -33922,9 +33927,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33939,22 +33954,22 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122965865</v>
+        <v>122962123</v>
       </c>
       <c r="B311" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -33967,42 +33982,37 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>481118</v>
+        <v>480826</v>
       </c>
       <c r="R311" t="n">
-        <v>6790699</v>
+        <v>6790638</v>
       </c>
       <c r="S311" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -34029,19 +34039,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA311" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB311" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -34056,12 +34056,12 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122915083</v>
+        <v>122916858</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,46 +1854,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480681</v>
+        <v>481356</v>
       </c>
       <c r="R13" t="n">
-        <v>6790816</v>
+        <v>6790502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,19 +1920,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,22 +1937,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122908690</v>
+        <v>122914329</v>
       </c>
       <c r="B14" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,13 +1989,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480626</v>
+        <v>481184</v>
       </c>
       <c r="R14" t="n">
-        <v>6790648</v>
+        <v>6790659</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,7 +2024,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2034,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,19 +2049,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122916728</v>
+        <v>122914178</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2114,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481324</v>
+        <v>480864</v>
       </c>
       <c r="R15" t="n">
-        <v>6790518</v>
+        <v>6790682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122915071</v>
+        <v>122908301</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2216,13 +2203,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480830</v>
+        <v>480606</v>
       </c>
       <c r="R16" t="n">
-        <v>6790684</v>
+        <v>6790682</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2261,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,22 +2263,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122915163</v>
+        <v>122908690</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,37 +2291,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480988</v>
+        <v>480626</v>
       </c>
       <c r="R17" t="n">
-        <v>6790673</v>
+        <v>6790648</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,9 +2348,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,19 +2375,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122906981</v>
+        <v>122916728</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2430,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480725</v>
+        <v>481324</v>
       </c>
       <c r="R18" t="n">
-        <v>6790654</v>
+        <v>6790518</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122907044</v>
+        <v>122915071</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2528,14 +2525,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480733</v>
+        <v>480830</v>
       </c>
       <c r="R19" t="n">
-        <v>6790651</v>
+        <v>6790684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,9 +2562,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2582,19 +2589,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122916212</v>
+        <v>122915163</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2634,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481263</v>
+        <v>480988</v>
       </c>
       <c r="R20" t="n">
-        <v>6790561</v>
+        <v>6790673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122908551</v>
+        <v>122906981</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2736,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480639</v>
+        <v>480725</v>
       </c>
       <c r="R21" t="n">
-        <v>6790797</v>
+        <v>6790654</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,19 +2776,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,19 +2793,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122915490</v>
+        <v>122907044</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2848,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481062</v>
+        <v>480733</v>
       </c>
       <c r="R22" t="n">
-        <v>6790617</v>
+        <v>6790651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122907468</v>
+        <v>122916212</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2950,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480739</v>
+        <v>481263</v>
       </c>
       <c r="R23" t="n">
-        <v>6790609</v>
+        <v>6790561</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122910763</v>
+        <v>122908551</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3052,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480802</v>
+        <v>480639</v>
       </c>
       <c r="R24" t="n">
-        <v>6790516</v>
+        <v>6790797</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,9 +3082,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3102,19 +3109,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122917077</v>
+        <v>122915490</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3154,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481414</v>
+        <v>481062</v>
       </c>
       <c r="R25" t="n">
-        <v>6790487</v>
+        <v>6790617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122910625</v>
+        <v>122907468</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3256,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480776</v>
+        <v>480739</v>
       </c>
       <c r="R26" t="n">
-        <v>6790600</v>
+        <v>6790609</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122916858</v>
+        <v>122910763</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3334,39 +3341,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481356</v>
+        <v>480802</v>
       </c>
       <c r="R27" t="n">
-        <v>6790502</v>
+        <v>6790516</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122914329</v>
+        <v>122917077</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3461,17 +3463,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481184</v>
+        <v>481414</v>
       </c>
       <c r="R28" t="n">
-        <v>6790659</v>
+        <v>6790487</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3498,19 +3500,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3525,19 +3517,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122914178</v>
+        <v>122910625</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3577,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480864</v>
+        <v>480776</v>
       </c>
       <c r="R29" t="n">
-        <v>6790682</v>
+        <v>6790600</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122908301</v>
+        <v>122915083</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,41 +3643,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480606</v>
+        <v>480681</v>
       </c>
       <c r="R30" t="n">
-        <v>6790682</v>
+        <v>6790816</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3739,12 +3739,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -10643,7 +10643,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122916316</v>
+        <v>122909058</v>
       </c>
       <c r="B95" t="n">
         <v>78766</v>
@@ -10679,14 +10679,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481273</v>
+        <v>480660</v>
       </c>
       <c r="R95" t="n">
-        <v>6790567</v>
+        <v>6790681</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10716,9 +10716,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10733,19 +10743,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122906741</v>
+        <v>122915451</v>
       </c>
       <c r="B96" t="n">
         <v>78766</v>
@@ -10785,10 +10795,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480726</v>
+        <v>481063</v>
       </c>
       <c r="R96" t="n">
-        <v>6790689</v>
+        <v>6790636</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10847,7 +10857,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122914138</v>
+        <v>122916316</v>
       </c>
       <c r="B97" t="n">
         <v>78766</v>
@@ -10887,10 +10897,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480858</v>
+        <v>481273</v>
       </c>
       <c r="R97" t="n">
-        <v>6790672</v>
+        <v>6790567</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10949,7 +10959,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122909058</v>
+        <v>122906741</v>
       </c>
       <c r="B98" t="n">
         <v>78766</v>
@@ -10985,14 +10995,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480660</v>
+        <v>480726</v>
       </c>
       <c r="R98" t="n">
-        <v>6790681</v>
+        <v>6790689</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11022,19 +11032,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11049,19 +11049,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122915451</v>
+        <v>122914138</v>
       </c>
       <c r="B99" t="n">
         <v>78766</v>
@@ -11101,10 +11101,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481063</v>
+        <v>480858</v>
       </c>
       <c r="R99" t="n">
-        <v>6790636</v>
+        <v>6790672</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -16372,10 +16372,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122914913</v>
+        <v>122908784</v>
       </c>
       <c r="B149" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16388,37 +16388,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480848</v>
+        <v>480639</v>
       </c>
       <c r="R149" t="n">
-        <v>6790704</v>
+        <v>6790797</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16472,12 +16472,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16591,10 +16591,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122908784</v>
+        <v>122908737</v>
       </c>
       <c r="B151" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16607,34 +16607,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480639</v>
+        <v>480772</v>
       </c>
       <c r="R151" t="n">
-        <v>6790797</v>
+        <v>6790501</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16664,19 +16664,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16691,19 +16681,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122908737</v>
+        <v>122914493</v>
       </c>
       <c r="B152" t="n">
         <v>78766</v>
@@ -16743,13 +16733,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480772</v>
+        <v>481040</v>
       </c>
       <c r="R152" t="n">
-        <v>6790501</v>
+        <v>6790686</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16776,9 +16766,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16793,19 +16793,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122914493</v>
+        <v>122907575</v>
       </c>
       <c r="B153" t="n">
         <v>78766</v>
@@ -16845,13 +16845,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>481040</v>
+        <v>480571</v>
       </c>
       <c r="R153" t="n">
-        <v>6790686</v>
+        <v>6790798</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16905,19 +16905,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122907575</v>
+        <v>122910257</v>
       </c>
       <c r="B154" t="n">
         <v>78766</v>
@@ -16957,13 +16957,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480571</v>
+        <v>480680</v>
       </c>
       <c r="R154" t="n">
-        <v>6790798</v>
+        <v>6790662</v>
       </c>
       <c r="S154" t="n">
-        <v>11</v>
+        <v>141</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17029,7 +17029,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122910257</v>
+        <v>122907818</v>
       </c>
       <c r="B155" t="n">
         <v>78766</v>
@@ -17069,13 +17069,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480680</v>
+        <v>480545</v>
       </c>
       <c r="R155" t="n">
-        <v>6790662</v>
+        <v>6790776</v>
       </c>
       <c r="S155" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17129,19 +17129,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122907818</v>
+        <v>122916996</v>
       </c>
       <c r="B156" t="n">
         <v>78766</v>
@@ -17177,17 +17177,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480545</v>
+        <v>481382</v>
       </c>
       <c r="R156" t="n">
-        <v>6790776</v>
+        <v>6790485</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17214,19 +17214,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17241,19 +17231,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122916996</v>
+        <v>122907225</v>
       </c>
       <c r="B157" t="n">
         <v>78766</v>
@@ -17289,17 +17279,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>481382</v>
+        <v>480622</v>
       </c>
       <c r="R157" t="n">
-        <v>6790485</v>
+        <v>6790776</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17326,9 +17316,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17343,19 +17343,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122907225</v>
+        <v>122914913</v>
       </c>
       <c r="B158" t="n">
         <v>78766</v>
@@ -17395,13 +17395,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480622</v>
+        <v>480848</v>
       </c>
       <c r="R158" t="n">
-        <v>6790776</v>
+        <v>6790704</v>
       </c>
       <c r="S158" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17455,12 +17455,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -18094,10 +18094,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122908316</v>
+        <v>122908892</v>
       </c>
       <c r="B165" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18106,41 +18106,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>480628</v>
+        <v>480771</v>
       </c>
       <c r="R165" t="n">
-        <v>6790662</v>
+        <v>6790522</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18167,19 +18167,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18194,22 +18184,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122913095</v>
+        <v>122909048</v>
       </c>
       <c r="B166" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18218,38 +18208,47 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>480874</v>
+        <v>480660</v>
       </c>
       <c r="R166" t="n">
-        <v>6790659</v>
+        <v>6790681</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18279,36 +18278,47 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>122911259</v>
+        <v>122908316</v>
       </c>
       <c r="B167" t="n">
         <v>78766</v>
@@ -18348,13 +18358,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>481008</v>
+        <v>480628</v>
       </c>
       <c r="R167" t="n">
-        <v>6790695</v>
+        <v>6790662</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18383,7 +18393,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18393,7 +18403,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18420,10 +18430,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>122909048</v>
+        <v>122913095</v>
       </c>
       <c r="B168" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18432,47 +18442,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>480660</v>
+        <v>480874</v>
       </c>
       <c r="R168" t="n">
-        <v>6790681</v>
+        <v>6790659</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18502,50 +18503,39 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>122908892</v>
+        <v>122911259</v>
       </c>
       <c r="B169" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18554,38 +18544,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>480771</v>
+        <v>481008</v>
       </c>
       <c r="R169" t="n">
-        <v>6790522</v>
+        <v>6790695</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18615,9 +18605,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18632,12 +18632,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -21200,10 +21200,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122965792</v>
+        <v>122970062</v>
       </c>
       <c r="B194" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21212,43 +21212,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>481118</v>
+        <v>481533</v>
       </c>
       <c r="R194" t="n">
-        <v>6790699</v>
+        <v>6790513</v>
       </c>
       <c r="S194" t="n">
         <v>9</v>
@@ -21280,7 +21275,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21290,7 +21285,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21317,7 +21312,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122970062</v>
+        <v>122973371</v>
       </c>
       <c r="B195" t="n">
         <v>78766</v>
@@ -21357,10 +21352,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>481533</v>
+        <v>481551</v>
       </c>
       <c r="R195" t="n">
-        <v>6790513</v>
+        <v>6790539</v>
       </c>
       <c r="S195" t="n">
         <v>9</v>
@@ -21392,7 +21387,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21402,7 +21397,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21429,7 +21424,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122973371</v>
+        <v>122976875</v>
       </c>
       <c r="B196" t="n">
         <v>78766</v>
@@ -21465,17 +21460,17 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>481551</v>
+        <v>481334</v>
       </c>
       <c r="R196" t="n">
-        <v>6790539</v>
+        <v>6790765</v>
       </c>
       <c r="S196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21502,19 +21497,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>15:42</t>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Garnlav överallt i en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21529,19 +21519,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122976875</v>
+        <v>122965887</v>
       </c>
       <c r="B197" t="n">
         <v>78766</v>
@@ -21577,14 +21567,14 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>481334</v>
+        <v>481195</v>
       </c>
       <c r="R197" t="n">
-        <v>6790765</v>
+        <v>6790707</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21621,7 +21611,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Garnlav överallt i en radie av 50 meter.</t>
+          <t>Garnlav runt omkring mig så långt jag kan se!</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21648,7 +21638,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122965887</v>
+        <v>122965760</v>
       </c>
       <c r="B198" t="n">
         <v>78766</v>
@@ -21684,17 +21674,17 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>481195</v>
+        <v>481118</v>
       </c>
       <c r="R198" t="n">
-        <v>6790707</v>
+        <v>6790699</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21721,14 +21711,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig så långt jag kan se!</t>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21743,22 +21738,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122965760</v>
+        <v>122965792</v>
       </c>
       <c r="B199" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21767,28 +21762,33 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -28703,10 +28703,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122965694</v>
+        <v>122966313</v>
       </c>
       <c r="B263" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -28715,25 +28715,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -28743,10 +28743,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>481111</v>
+        <v>481151</v>
       </c>
       <c r="R263" t="n">
-        <v>6790702</v>
+        <v>6790709</v>
       </c>
       <c r="S263" t="n">
         <v>9</v>
@@ -28778,7 +28778,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28815,7 +28815,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122973912</v>
+        <v>122968097</v>
       </c>
       <c r="B264" t="n">
         <v>78766</v>
@@ -28851,17 +28851,17 @@
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>481468</v>
+        <v>481372</v>
       </c>
       <c r="R264" t="n">
-        <v>6790601</v>
+        <v>6790559</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -28888,9 +28888,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28905,19 +28915,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122975172</v>
+        <v>122968760</v>
       </c>
       <c r="B265" t="n">
         <v>78766</v>
@@ -28953,17 +28963,17 @@
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>481465</v>
+        <v>481444</v>
       </c>
       <c r="R265" t="n">
-        <v>6790730</v>
+        <v>6790544</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -28990,14 +29000,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>Garn med miljöbild.</t>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -29012,22 +29027,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122970166</v>
+        <v>122968051</v>
       </c>
       <c r="B266" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -29036,43 +29051,38 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>481546</v>
+        <v>481370</v>
       </c>
       <c r="R266" t="n">
-        <v>6790501</v>
+        <v>6790557</v>
       </c>
       <c r="S266" t="n">
         <v>9</v>
@@ -29104,7 +29114,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -29114,7 +29124,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -29141,10 +29151,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122966313</v>
+        <v>122965694</v>
       </c>
       <c r="B267" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -29153,25 +29163,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -29181,10 +29191,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>481151</v>
+        <v>481111</v>
       </c>
       <c r="R267" t="n">
-        <v>6790709</v>
+        <v>6790702</v>
       </c>
       <c r="S267" t="n">
         <v>9</v>
@@ -29216,7 +29226,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -29226,7 +29236,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -29253,7 +29263,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122968097</v>
+        <v>122973912</v>
       </c>
       <c r="B268" t="n">
         <v>78766</v>
@@ -29289,17 +29299,17 @@
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>481372</v>
+        <v>481468</v>
       </c>
       <c r="R268" t="n">
-        <v>6790559</v>
+        <v>6790601</v>
       </c>
       <c r="S268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -29326,19 +29336,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -29353,19 +29353,19 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122968760</v>
+        <v>122975172</v>
       </c>
       <c r="B269" t="n">
         <v>78766</v>
@@ -29401,17 +29401,17 @@
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>481444</v>
+        <v>481465</v>
       </c>
       <c r="R269" t="n">
-        <v>6790544</v>
+        <v>6790730</v>
       </c>
       <c r="S269" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -29438,19 +29438,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Garn med miljöbild.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29465,22 +29460,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122968051</v>
+        <v>122970166</v>
       </c>
       <c r="B270" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -29489,38 +29484,43 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>481370</v>
+        <v>481546</v>
       </c>
       <c r="R270" t="n">
-        <v>6790557</v>
+        <v>6790501</v>
       </c>
       <c r="S270" t="n">
         <v>9</v>
@@ -29552,7 +29552,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -29706,10 +29706,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122974351</v>
+        <v>122973404</v>
       </c>
       <c r="B272" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -29722,37 +29722,37 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>481398</v>
+        <v>481525</v>
       </c>
       <c r="R272" t="n">
-        <v>6790689</v>
+        <v>6790521</v>
       </c>
       <c r="S272" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -29779,19 +29779,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29806,19 +29796,19 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122973404</v>
+        <v>122968143</v>
       </c>
       <c r="B273" t="n">
         <v>78766</v>
@@ -29854,17 +29844,17 @@
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>481525</v>
+        <v>481374</v>
       </c>
       <c r="R273" t="n">
-        <v>6790521</v>
+        <v>6790558</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -29891,9 +29881,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -29908,19 +29908,19 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122968143</v>
+        <v>122966180</v>
       </c>
       <c r="B274" t="n">
         <v>78766</v>
@@ -29960,10 +29960,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>481374</v>
+        <v>481151</v>
       </c>
       <c r="R274" t="n">
-        <v>6790558</v>
+        <v>6790709</v>
       </c>
       <c r="S274" t="n">
         <v>9</v>
@@ -29995,7 +29995,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30032,7 +30032,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122966180</v>
+        <v>122977985</v>
       </c>
       <c r="B275" t="n">
         <v>78766</v>
@@ -30072,10 +30072,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>481151</v>
+        <v>481229</v>
       </c>
       <c r="R275" t="n">
-        <v>6790709</v>
+        <v>6790728</v>
       </c>
       <c r="S275" t="n">
         <v>9</v>
@@ -30107,7 +30107,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -30117,7 +30117,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -30144,7 +30144,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122977985</v>
+        <v>122973693</v>
       </c>
       <c r="B276" t="n">
         <v>78766</v>
@@ -30184,10 +30184,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>481229</v>
+        <v>481472</v>
       </c>
       <c r="R276" t="n">
-        <v>6790728</v>
+        <v>6790535</v>
       </c>
       <c r="S276" t="n">
         <v>9</v>
@@ -30219,7 +30219,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -30229,7 +30229,12 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>På Granar</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -30256,10 +30261,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122973693</v>
+        <v>122974351</v>
       </c>
       <c r="B277" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -30272,21 +30277,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -30296,10 +30301,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>481472</v>
+        <v>481398</v>
       </c>
       <c r="R277" t="n">
-        <v>6790535</v>
+        <v>6790689</v>
       </c>
       <c r="S277" t="n">
         <v>9</v>
@@ -30331,7 +30336,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -30341,12 +30346,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>På Granar</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -32548,7 +32548,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122961573</v>
+        <v>122968666</v>
       </c>
       <c r="B298" t="n">
         <v>78766</v>
@@ -32584,17 +32584,17 @@
       <c r="I298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>480767</v>
+        <v>481436</v>
       </c>
       <c r="R298" t="n">
-        <v>6790685</v>
+        <v>6790540</v>
       </c>
       <c r="S298" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -32621,9 +32621,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA298" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -32638,22 +32653,22 @@
       <c r="AT298" t="inlineStr"/>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122978194</v>
+        <v>122961573</v>
       </c>
       <c r="B299" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -32662,46 +32677,41 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>481090</v>
+        <v>480767</v>
       </c>
       <c r="R299" t="n">
-        <v>6790709</v>
+        <v>6790685</v>
       </c>
       <c r="S299" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -32728,19 +32738,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB299" t="inlineStr">
-        <is>
-          <t>17:25</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -32755,22 +32755,22 @@
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122968666</v>
+        <v>122978194</v>
       </c>
       <c r="B300" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -32779,38 +32779,43 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P300" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>481436</v>
+        <v>481090</v>
       </c>
       <c r="R300" t="n">
-        <v>6790540</v>
+        <v>6790709</v>
       </c>
       <c r="S300" t="n">
         <v>9</v>
@@ -32842,7 +32847,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -32852,12 +32857,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC300" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -32884,10 +32884,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122968577</v>
+        <v>122968800</v>
       </c>
       <c r="B301" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -32896,41 +32896,41 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>481434</v>
+        <v>481460</v>
       </c>
       <c r="R301" t="n">
-        <v>6790538</v>
+        <v>6790499</v>
       </c>
       <c r="S301" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -32957,19 +32957,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA301" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB301" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -32984,22 +32974,22 @@
       <c r="AT301" t="inlineStr"/>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122959889</v>
+        <v>122975322</v>
       </c>
       <c r="B302" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -33008,41 +32998,41 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>480792</v>
+        <v>481394</v>
       </c>
       <c r="R302" t="n">
-        <v>6790812</v>
+        <v>6790771</v>
       </c>
       <c r="S302" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -33069,9 +33059,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -33086,19 +33086,19 @@
       <c r="AT302" t="inlineStr"/>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122960001</v>
+        <v>122968577</v>
       </c>
       <c r="B303" t="n">
         <v>78766</v>
@@ -33134,17 +33134,17 @@
       <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>480805</v>
+        <v>481434</v>
       </c>
       <c r="R303" t="n">
-        <v>6790809</v>
+        <v>6790538</v>
       </c>
       <c r="S303" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -33171,9 +33171,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA303" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -33188,19 +33198,19 @@
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122975021</v>
+        <v>122959889</v>
       </c>
       <c r="B304" t="n">
         <v>78766</v>
@@ -33236,17 +33246,17 @@
       <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>481422</v>
+        <v>480792</v>
       </c>
       <c r="R304" t="n">
-        <v>6790752</v>
+        <v>6790812</v>
       </c>
       <c r="S304" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -33273,24 +33283,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB304" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC304" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -33305,19 +33300,19 @@
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122970352</v>
+        <v>122960001</v>
       </c>
       <c r="B305" t="n">
         <v>78766</v>
@@ -33353,17 +33348,17 @@
       <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>481566</v>
+        <v>480805</v>
       </c>
       <c r="R305" t="n">
-        <v>6790511</v>
+        <v>6790809</v>
       </c>
       <c r="S305" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -33390,19 +33385,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA305" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB305" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -33417,19 +33402,19 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122973389</v>
+        <v>122975021</v>
       </c>
       <c r="B306" t="n">
         <v>78766</v>
@@ -33469,10 +33454,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>481565</v>
+        <v>481422</v>
       </c>
       <c r="R306" t="n">
-        <v>6790545</v>
+        <v>6790752</v>
       </c>
       <c r="S306" t="n">
         <v>9</v>
@@ -33504,7 +33489,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -33514,7 +33499,12 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -33541,10 +33531,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122968800</v>
+        <v>122970352</v>
       </c>
       <c r="B307" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -33553,41 +33543,41 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>481460</v>
+        <v>481566</v>
       </c>
       <c r="R307" t="n">
-        <v>6790499</v>
+        <v>6790511</v>
       </c>
       <c r="S307" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -33614,9 +33604,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA307" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33631,22 +33631,22 @@
       <c r="AT307" t="inlineStr"/>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122975322</v>
+        <v>122973389</v>
       </c>
       <c r="B308" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -33655,25 +33655,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -33683,10 +33683,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>481394</v>
+        <v>481565</v>
       </c>
       <c r="R308" t="n">
-        <v>6790771</v>
+        <v>6790545</v>
       </c>
       <c r="S308" t="n">
         <v>9</v>
@@ -33718,7 +33718,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD308" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -6771,10 +6771,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122907535</v>
+        <v>122910507</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6783,41 +6783,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480604</v>
+        <v>480751</v>
       </c>
       <c r="R59" t="n">
-        <v>6790798</v>
+        <v>6790806</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6871,22 +6871,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122908196</v>
+        <v>122905560</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6895,25 +6895,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480681</v>
+        <v>480689</v>
       </c>
       <c r="R60" t="n">
-        <v>6790816</v>
+        <v>6790776</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6956,19 +6956,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6983,22 +6973,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122908658</v>
+        <v>122910737</v>
       </c>
       <c r="B61" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7007,41 +6997,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480701</v>
+        <v>480800</v>
       </c>
       <c r="R61" t="n">
-        <v>6790532</v>
+        <v>6790542</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7068,19 +7058,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,19 +7075,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122907981</v>
+        <v>122911585</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -7147,13 +7127,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480580</v>
+        <v>481035</v>
       </c>
       <c r="R62" t="n">
-        <v>6790754</v>
+        <v>6790750</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7182,7 +7162,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7192,7 +7172,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7207,19 +7187,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122910507</v>
+        <v>122916548</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -7255,17 +7235,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480751</v>
+        <v>481290</v>
       </c>
       <c r="R63" t="n">
-        <v>6790806</v>
+        <v>6790576</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7292,19 +7272,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7319,19 +7289,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122905560</v>
+        <v>122907326</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7371,10 +7341,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480689</v>
+        <v>480712</v>
       </c>
       <c r="R64" t="n">
-        <v>6790776</v>
+        <v>6790625</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7433,7 +7403,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122910737</v>
+        <v>122913931</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7473,10 +7443,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480800</v>
+        <v>480817</v>
       </c>
       <c r="R65" t="n">
-        <v>6790542</v>
+        <v>6790670</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7535,7 +7505,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122911585</v>
+        <v>122909144</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -7571,17 +7541,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481035</v>
+        <v>480738</v>
       </c>
       <c r="R66" t="n">
-        <v>6790750</v>
+        <v>6790666</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7608,19 +7578,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7635,19 +7595,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122916548</v>
+        <v>122914177</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7683,17 +7643,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481290</v>
+        <v>481318</v>
       </c>
       <c r="R67" t="n">
-        <v>6790576</v>
+        <v>6790679</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7720,9 +7680,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7737,19 +7707,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122907326</v>
+        <v>122908082</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7785,17 +7755,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480712</v>
+        <v>480607</v>
       </c>
       <c r="R68" t="n">
-        <v>6790625</v>
+        <v>6790687</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7822,9 +7792,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7839,19 +7819,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122913931</v>
+        <v>122915091</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7891,10 +7871,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480817</v>
+        <v>480681</v>
       </c>
       <c r="R69" t="n">
-        <v>6790670</v>
+        <v>6790816</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7924,9 +7904,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7941,19 +7931,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122909144</v>
+        <v>122908242</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7993,10 +7983,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480738</v>
+        <v>480743</v>
       </c>
       <c r="R70" t="n">
-        <v>6790666</v>
+        <v>6790542</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8055,7 +8045,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122914177</v>
+        <v>122907981</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8095,10 +8085,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481318</v>
+        <v>480580</v>
       </c>
       <c r="R71" t="n">
-        <v>6790679</v>
+        <v>6790754</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8130,7 +8120,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8140,7 +8130,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,10 +8157,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122908082</v>
+        <v>122907535</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8179,41 +8169,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480607</v>
+        <v>480604</v>
       </c>
       <c r="R72" t="n">
-        <v>6790687</v>
+        <v>6790798</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8242,7 +8232,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8252,7 +8242,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8267,22 +8257,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122915091</v>
+        <v>122908196</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8291,25 +8281,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8354,7 +8344,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8364,7 +8354,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8391,10 +8381,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122908242</v>
+        <v>122908658</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8403,41 +8393,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480743</v>
+        <v>480701</v>
       </c>
       <c r="R74" t="n">
-        <v>6790542</v>
+        <v>6790532</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8464,9 +8454,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8481,12 +8481,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -10643,7 +10643,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122909058</v>
+        <v>122916316</v>
       </c>
       <c r="B95" t="n">
         <v>78766</v>
@@ -10679,14 +10679,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480660</v>
+        <v>481273</v>
       </c>
       <c r="R95" t="n">
-        <v>6790681</v>
+        <v>6790567</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10716,19 +10716,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,19 +10733,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122915451</v>
+        <v>122906741</v>
       </c>
       <c r="B96" t="n">
         <v>78766</v>
@@ -10795,10 +10785,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481063</v>
+        <v>480726</v>
       </c>
       <c r="R96" t="n">
-        <v>6790636</v>
+        <v>6790689</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10857,7 +10847,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122916316</v>
+        <v>122914138</v>
       </c>
       <c r="B97" t="n">
         <v>78766</v>
@@ -10897,10 +10887,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481273</v>
+        <v>480858</v>
       </c>
       <c r="R97" t="n">
-        <v>6790567</v>
+        <v>6790672</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10959,7 +10949,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122906741</v>
+        <v>122909058</v>
       </c>
       <c r="B98" t="n">
         <v>78766</v>
@@ -10995,14 +10985,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480726</v>
+        <v>480660</v>
       </c>
       <c r="R98" t="n">
-        <v>6790689</v>
+        <v>6790681</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11032,9 +11022,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11049,19 +11049,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122914138</v>
+        <v>122915451</v>
       </c>
       <c r="B99" t="n">
         <v>78766</v>
@@ -11101,10 +11101,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>480858</v>
+        <v>481063</v>
       </c>
       <c r="R99" t="n">
-        <v>6790672</v>
+        <v>6790636</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -16372,10 +16372,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122908784</v>
+        <v>122914913</v>
       </c>
       <c r="B149" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16388,37 +16388,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480639</v>
+        <v>480848</v>
       </c>
       <c r="R149" t="n">
-        <v>6790797</v>
+        <v>6790704</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16472,12 +16472,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16591,10 +16591,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122908737</v>
+        <v>122908784</v>
       </c>
       <c r="B151" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16607,34 +16607,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480772</v>
+        <v>480639</v>
       </c>
       <c r="R151" t="n">
-        <v>6790501</v>
+        <v>6790797</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16664,9 +16664,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16681,19 +16691,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122914493</v>
+        <v>122908737</v>
       </c>
       <c r="B152" t="n">
         <v>78766</v>
@@ -16733,13 +16743,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>481040</v>
+        <v>480772</v>
       </c>
       <c r="R152" t="n">
-        <v>6790686</v>
+        <v>6790501</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16766,19 +16776,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>15:47</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16793,19 +16793,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122907575</v>
+        <v>122914493</v>
       </c>
       <c r="B153" t="n">
         <v>78766</v>
@@ -16845,13 +16845,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480571</v>
+        <v>481040</v>
       </c>
       <c r="R153" t="n">
-        <v>6790798</v>
+        <v>6790686</v>
       </c>
       <c r="S153" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16905,19 +16905,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122910257</v>
+        <v>122907575</v>
       </c>
       <c r="B154" t="n">
         <v>78766</v>
@@ -16957,13 +16957,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480680</v>
+        <v>480571</v>
       </c>
       <c r="R154" t="n">
-        <v>6790662</v>
+        <v>6790798</v>
       </c>
       <c r="S154" t="n">
-        <v>141</v>
+        <v>11</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17029,7 +17029,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122907818</v>
+        <v>122910257</v>
       </c>
       <c r="B155" t="n">
         <v>78766</v>
@@ -17069,13 +17069,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480545</v>
+        <v>480680</v>
       </c>
       <c r="R155" t="n">
-        <v>6790776</v>
+        <v>6790662</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17129,19 +17129,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122916996</v>
+        <v>122907818</v>
       </c>
       <c r="B156" t="n">
         <v>78766</v>
@@ -17177,17 +17177,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>481382</v>
+        <v>480545</v>
       </c>
       <c r="R156" t="n">
-        <v>6790485</v>
+        <v>6790776</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17214,9 +17214,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17231,19 +17241,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122907225</v>
+        <v>122916996</v>
       </c>
       <c r="B157" t="n">
         <v>78766</v>
@@ -17279,17 +17289,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480622</v>
+        <v>481382</v>
       </c>
       <c r="R157" t="n">
-        <v>6790776</v>
+        <v>6790485</v>
       </c>
       <c r="S157" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17316,19 +17326,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17343,19 +17343,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122914913</v>
+        <v>122907225</v>
       </c>
       <c r="B158" t="n">
         <v>78766</v>
@@ -17395,13 +17395,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480848</v>
+        <v>480622</v>
       </c>
       <c r="R158" t="n">
-        <v>6790704</v>
+        <v>6790776</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17455,12 +17455,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -21200,10 +21200,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122970062</v>
+        <v>122965792</v>
       </c>
       <c r="B194" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21212,38 +21212,43 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>481533</v>
+        <v>481118</v>
       </c>
       <c r="R194" t="n">
-        <v>6790513</v>
+        <v>6790699</v>
       </c>
       <c r="S194" t="n">
         <v>9</v>
@@ -21275,7 +21280,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21285,7 +21290,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21312,7 +21317,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122973371</v>
+        <v>122970062</v>
       </c>
       <c r="B195" t="n">
         <v>78766</v>
@@ -21352,10 +21357,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>481551</v>
+        <v>481533</v>
       </c>
       <c r="R195" t="n">
-        <v>6790539</v>
+        <v>6790513</v>
       </c>
       <c r="S195" t="n">
         <v>9</v>
@@ -21387,7 +21392,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21397,7 +21402,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21424,7 +21429,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122976875</v>
+        <v>122973371</v>
       </c>
       <c r="B196" t="n">
         <v>78766</v>
@@ -21460,17 +21465,17 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>481334</v>
+        <v>481551</v>
       </c>
       <c r="R196" t="n">
-        <v>6790765</v>
+        <v>6790539</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21497,14 +21502,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Garnlav överallt i en radie av 50 meter.</t>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21519,19 +21529,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122965887</v>
+        <v>122976875</v>
       </c>
       <c r="B197" t="n">
         <v>78766</v>
@@ -21567,14 +21577,14 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>481195</v>
+        <v>481334</v>
       </c>
       <c r="R197" t="n">
-        <v>6790707</v>
+        <v>6790765</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21611,7 +21621,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Garnlav runt omkring mig så långt jag kan se!</t>
+          <t>Garnlav överallt i en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21638,7 +21648,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122965760</v>
+        <v>122965887</v>
       </c>
       <c r="B198" t="n">
         <v>78766</v>
@@ -21674,17 +21684,17 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>481118</v>
+        <v>481195</v>
       </c>
       <c r="R198" t="n">
-        <v>6790699</v>
+        <v>6790707</v>
       </c>
       <c r="S198" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21711,19 +21721,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>12:49</t>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig så långt jag kan se!</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21738,22 +21743,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122965792</v>
+        <v>122965760</v>
       </c>
       <c r="B199" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21762,33 +21767,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21867,10 +21867,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122975526</v>
+        <v>122969848</v>
       </c>
       <c r="B200" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21883,16 +21883,16 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -21903,14 +21903,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>481420</v>
+        <v>481544</v>
       </c>
       <c r="R200" t="n">
-        <v>6790760</v>
+        <v>6790494</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21943,6 +21943,11 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21969,7 +21974,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122960414</v>
+        <v>122975526</v>
       </c>
       <c r="B201" t="n">
         <v>78766</v>
@@ -22005,14 +22010,14 @@
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>480766</v>
+        <v>481420</v>
       </c>
       <c r="R201" t="n">
-        <v>6790785</v>
+        <v>6790760</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22071,7 +22076,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122976543</v>
+        <v>122960414</v>
       </c>
       <c r="B202" t="n">
         <v>78766</v>
@@ -22107,17 +22112,17 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>481356</v>
+        <v>480766</v>
       </c>
       <c r="R202" t="n">
-        <v>6790736</v>
+        <v>6790785</v>
       </c>
       <c r="S202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22144,19 +22149,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>16:58</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22171,19 +22166,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122977806</v>
+        <v>122976543</v>
       </c>
       <c r="B203" t="n">
         <v>78766</v>
@@ -22219,17 +22214,17 @@
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>481253</v>
+        <v>481356</v>
       </c>
       <c r="R203" t="n">
-        <v>6790770</v>
+        <v>6790736</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22256,14 +22251,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Gar inom synfältet i en radie av ca 50 meter.</t>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22278,19 +22278,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122976687</v>
+        <v>122977806</v>
       </c>
       <c r="B204" t="n">
         <v>78766</v>
@@ -22326,17 +22326,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>481338</v>
+        <v>481253</v>
       </c>
       <c r="R204" t="n">
-        <v>6790724</v>
+        <v>6790770</v>
       </c>
       <c r="S204" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22363,24 +22363,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>På Gran</t>
+          <t>Gar inom synfältet i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22395,19 +22385,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122977907</v>
+        <v>122976687</v>
       </c>
       <c r="B205" t="n">
         <v>78766</v>
@@ -22447,10 +22437,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>481302</v>
+        <v>481338</v>
       </c>
       <c r="R205" t="n">
-        <v>6790744</v>
+        <v>6790724</v>
       </c>
       <c r="S205" t="n">
         <v>9</v>
@@ -22482,7 +22472,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22492,7 +22482,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22519,10 +22514,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122962565</v>
+        <v>122977907</v>
       </c>
       <c r="B206" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22535,21 +22530,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22559,10 +22554,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>480854</v>
+        <v>481302</v>
       </c>
       <c r="R206" t="n">
-        <v>6790625</v>
+        <v>6790744</v>
       </c>
       <c r="S206" t="n">
         <v>9</v>
@@ -22594,7 +22589,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22604,7 +22599,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22631,10 +22626,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122962123</v>
+        <v>122962565</v>
       </c>
       <c r="B207" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22647,37 +22642,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>480826</v>
+        <v>480854</v>
       </c>
       <c r="R207" t="n">
-        <v>6790638</v>
+        <v>6790625</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22704,9 +22699,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22721,19 +22726,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122975263</v>
+        <v>122962123</v>
       </c>
       <c r="B208" t="n">
         <v>78766</v>
@@ -22769,17 +22774,17 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>481394</v>
+        <v>480826</v>
       </c>
       <c r="R208" t="n">
-        <v>6790770</v>
+        <v>6790638</v>
       </c>
       <c r="S208" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22806,19 +22811,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>16:28</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22833,22 +22828,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122969848</v>
+        <v>122975263</v>
       </c>
       <c r="B209" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22861,16 +22856,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -22881,17 +22876,17 @@
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>481544</v>
+        <v>481394</v>
       </c>
       <c r="R209" t="n">
-        <v>6790494</v>
+        <v>6790770</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22918,14 +22913,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22940,12 +22940,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -6771,10 +6771,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122910507</v>
+        <v>122907535</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6783,41 +6783,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480751</v>
+        <v>480604</v>
       </c>
       <c r="R59" t="n">
-        <v>6790806</v>
+        <v>6790798</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6871,22 +6871,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122905560</v>
+        <v>122908196</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6895,25 +6895,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480689</v>
+        <v>480681</v>
       </c>
       <c r="R60" t="n">
-        <v>6790776</v>
+        <v>6790816</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6956,9 +6956,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6973,22 +6983,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122910737</v>
+        <v>122908658</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6997,41 +7007,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480800</v>
+        <v>480701</v>
       </c>
       <c r="R61" t="n">
-        <v>6790542</v>
+        <v>6790532</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7058,9 +7068,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7075,19 +7095,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122911585</v>
+        <v>122907981</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -7127,13 +7147,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481035</v>
+        <v>480580</v>
       </c>
       <c r="R62" t="n">
-        <v>6790750</v>
+        <v>6790754</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7162,7 +7182,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7172,7 +7192,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7187,19 +7207,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122916548</v>
+        <v>122910507</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -7235,17 +7255,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481290</v>
+        <v>480751</v>
       </c>
       <c r="R63" t="n">
-        <v>6790576</v>
+        <v>6790806</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7272,9 +7292,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7289,19 +7319,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122907326</v>
+        <v>122905560</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7341,10 +7371,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480712</v>
+        <v>480689</v>
       </c>
       <c r="R64" t="n">
-        <v>6790625</v>
+        <v>6790776</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7403,7 +7433,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122913931</v>
+        <v>122910737</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7443,10 +7473,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480817</v>
+        <v>480800</v>
       </c>
       <c r="R65" t="n">
-        <v>6790670</v>
+        <v>6790542</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7505,7 +7535,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122909144</v>
+        <v>122911585</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -7541,17 +7571,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480738</v>
+        <v>481035</v>
       </c>
       <c r="R66" t="n">
-        <v>6790666</v>
+        <v>6790750</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7578,9 +7608,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7595,19 +7635,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122914177</v>
+        <v>122916548</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7643,17 +7683,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481318</v>
+        <v>481290</v>
       </c>
       <c r="R67" t="n">
-        <v>6790679</v>
+        <v>6790576</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7680,19 +7720,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7707,19 +7737,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122908082</v>
+        <v>122907326</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7755,17 +7785,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480607</v>
+        <v>480712</v>
       </c>
       <c r="R68" t="n">
-        <v>6790687</v>
+        <v>6790625</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7792,19 +7822,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7819,19 +7839,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122915091</v>
+        <v>122913931</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7871,10 +7891,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480681</v>
+        <v>480817</v>
       </c>
       <c r="R69" t="n">
-        <v>6790816</v>
+        <v>6790670</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7904,19 +7924,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7931,19 +7941,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122908242</v>
+        <v>122909144</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7983,10 +7993,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480743</v>
+        <v>480738</v>
       </c>
       <c r="R70" t="n">
-        <v>6790542</v>
+        <v>6790666</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8045,7 +8055,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122907981</v>
+        <v>122914177</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8085,10 +8095,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480580</v>
+        <v>481318</v>
       </c>
       <c r="R71" t="n">
-        <v>6790754</v>
+        <v>6790679</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8120,7 +8130,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8130,7 +8140,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8157,10 +8167,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122907535</v>
+        <v>122908082</v>
       </c>
       <c r="B72" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8169,41 +8179,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480604</v>
+        <v>480607</v>
       </c>
       <c r="R72" t="n">
-        <v>6790798</v>
+        <v>6790687</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8232,7 +8242,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8242,7 +8252,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8257,22 +8267,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122908196</v>
+        <v>122915091</v>
       </c>
       <c r="B73" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8281,25 +8291,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8344,7 +8354,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8354,7 +8364,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8381,10 +8391,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122908658</v>
+        <v>122908242</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8393,41 +8403,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480701</v>
+        <v>480743</v>
       </c>
       <c r="R74" t="n">
-        <v>6790532</v>
+        <v>6790542</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8454,19 +8464,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8481,12 +8481,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -21867,10 +21867,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122969848</v>
+        <v>122975526</v>
       </c>
       <c r="B200" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21883,16 +21883,16 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -21903,14 +21903,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>481544</v>
+        <v>481420</v>
       </c>
       <c r="R200" t="n">
-        <v>6790494</v>
+        <v>6790760</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21943,11 +21943,6 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21974,7 +21969,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122975526</v>
+        <v>122960414</v>
       </c>
       <c r="B201" t="n">
         <v>78766</v>
@@ -22010,14 +22005,14 @@
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>481420</v>
+        <v>480766</v>
       </c>
       <c r="R201" t="n">
-        <v>6790760</v>
+        <v>6790785</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22076,7 +22071,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122960414</v>
+        <v>122976543</v>
       </c>
       <c r="B202" t="n">
         <v>78766</v>
@@ -22112,17 +22107,17 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>480766</v>
+        <v>481356</v>
       </c>
       <c r="R202" t="n">
-        <v>6790785</v>
+        <v>6790736</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22149,9 +22144,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22166,19 +22171,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122976543</v>
+        <v>122977806</v>
       </c>
       <c r="B203" t="n">
         <v>78766</v>
@@ -22214,17 +22219,17 @@
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>481356</v>
+        <v>481253</v>
       </c>
       <c r="R203" t="n">
-        <v>6790736</v>
+        <v>6790770</v>
       </c>
       <c r="S203" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22251,19 +22256,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>16:58</t>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Gar inom synfältet i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22278,19 +22278,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122977806</v>
+        <v>122976687</v>
       </c>
       <c r="B204" t="n">
         <v>78766</v>
@@ -22326,17 +22326,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>481253</v>
+        <v>481338</v>
       </c>
       <c r="R204" t="n">
-        <v>6790770</v>
+        <v>6790724</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22363,14 +22363,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Gar inom synfältet i en radie av ca 50 meter.</t>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22385,19 +22395,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122976687</v>
+        <v>122977907</v>
       </c>
       <c r="B205" t="n">
         <v>78766</v>
@@ -22437,10 +22447,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>481338</v>
+        <v>481302</v>
       </c>
       <c r="R205" t="n">
-        <v>6790724</v>
+        <v>6790744</v>
       </c>
       <c r="S205" t="n">
         <v>9</v>
@@ -22472,7 +22482,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22482,12 +22492,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22514,10 +22519,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122977907</v>
+        <v>122962565</v>
       </c>
       <c r="B206" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22530,21 +22535,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22554,10 +22559,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>481302</v>
+        <v>480854</v>
       </c>
       <c r="R206" t="n">
-        <v>6790744</v>
+        <v>6790625</v>
       </c>
       <c r="S206" t="n">
         <v>9</v>
@@ -22589,7 +22594,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22599,7 +22604,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22626,10 +22631,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122962565</v>
+        <v>122962123</v>
       </c>
       <c r="B207" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22642,37 +22647,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>480854</v>
+        <v>480826</v>
       </c>
       <c r="R207" t="n">
-        <v>6790625</v>
+        <v>6790638</v>
       </c>
       <c r="S207" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22699,19 +22704,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22726,19 +22721,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122962123</v>
+        <v>122975263</v>
       </c>
       <c r="B208" t="n">
         <v>78766</v>
@@ -22774,17 +22769,17 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>480826</v>
+        <v>481394</v>
       </c>
       <c r="R208" t="n">
-        <v>6790638</v>
+        <v>6790770</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22811,9 +22806,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22828,22 +22833,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122975263</v>
+        <v>122969848</v>
       </c>
       <c r="B209" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22856,16 +22861,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -22876,17 +22881,17 @@
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>481394</v>
+        <v>481544</v>
       </c>
       <c r="R209" t="n">
-        <v>6790770</v>
+        <v>6790494</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22913,19 +22918,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22940,12 +22940,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
@@ -26533,10 +26533,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122963417</v>
+        <v>122967628</v>
       </c>
       <c r="B243" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -26549,37 +26549,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>481011</v>
+        <v>481264</v>
       </c>
       <c r="R243" t="n">
-        <v>6790699</v>
+        <v>6790665</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -26606,9 +26611,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26623,19 +26638,19 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122978123</v>
+        <v>122963417</v>
       </c>
       <c r="B244" t="n">
         <v>78766</v>
@@ -26671,17 +26686,17 @@
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>481144</v>
+        <v>481011</v>
       </c>
       <c r="R244" t="n">
-        <v>6790730</v>
+        <v>6790699</v>
       </c>
       <c r="S244" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -26708,19 +26723,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26735,22 +26740,22 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122967628</v>
+        <v>122978123</v>
       </c>
       <c r="B245" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -26763,42 +26768,37 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>481264</v>
+        <v>481144</v>
       </c>
       <c r="R245" t="n">
-        <v>6790665</v>
+        <v>6790730</v>
       </c>
       <c r="S245" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -26837,7 +26837,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -30373,10 +30373,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122968089</v>
+        <v>122961952</v>
       </c>
       <c r="B278" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -30385,41 +30385,46 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>481376</v>
+        <v>480782</v>
       </c>
       <c r="R278" t="n">
-        <v>6790518</v>
+        <v>6790637</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -30446,9 +30451,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>Grov tall</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30463,12 +30483,12 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
@@ -30577,10 +30597,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122965948</v>
+        <v>122967445</v>
       </c>
       <c r="B280" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -30589,25 +30609,25 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -30617,10 +30637,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>481142</v>
+        <v>481249</v>
       </c>
       <c r="R280" t="n">
-        <v>6790715</v>
+        <v>6790669</v>
       </c>
       <c r="S280" t="n">
         <v>9</v>
@@ -30652,7 +30672,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -30662,7 +30682,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30689,10 +30709,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122969601</v>
+        <v>122965948</v>
       </c>
       <c r="B281" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -30701,41 +30721,41 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>481528</v>
+        <v>481142</v>
       </c>
       <c r="R281" t="n">
-        <v>6790490</v>
+        <v>6790715</v>
       </c>
       <c r="S281" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -30762,9 +30782,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30779,19 +30809,19 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122962130</v>
+        <v>122969601</v>
       </c>
       <c r="B282" t="n">
         <v>78766</v>
@@ -30827,17 +30857,17 @@
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>480812</v>
+        <v>481528</v>
       </c>
       <c r="R282" t="n">
-        <v>6790632</v>
+        <v>6790490</v>
       </c>
       <c r="S282" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -30864,19 +30894,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB282" t="inlineStr">
-        <is>
-          <t>11:25</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30891,19 +30911,19 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122960562</v>
+        <v>122962130</v>
       </c>
       <c r="B283" t="n">
         <v>78766</v>
@@ -30939,17 +30959,17 @@
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>480756</v>
+        <v>480812</v>
       </c>
       <c r="R283" t="n">
-        <v>6790775</v>
+        <v>6790632</v>
       </c>
       <c r="S283" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -30976,9 +30996,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -30993,22 +31023,22 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122974049</v>
+        <v>122960562</v>
       </c>
       <c r="B284" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -31017,46 +31047,41 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>481427</v>
+        <v>480756</v>
       </c>
       <c r="R284" t="n">
-        <v>6790669</v>
+        <v>6790775</v>
       </c>
       <c r="S284" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -31083,19 +31108,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -31110,22 +31125,22 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122961952</v>
+        <v>122968089</v>
       </c>
       <c r="B285" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31134,46 +31149,41 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>480782</v>
+        <v>481376</v>
       </c>
       <c r="R285" t="n">
-        <v>6790637</v>
+        <v>6790518</v>
       </c>
       <c r="S285" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -31200,24 +31210,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB285" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC285" t="inlineStr">
-        <is>
-          <t>Grov tall</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -31232,22 +31227,22 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122967445</v>
+        <v>122974049</v>
       </c>
       <c r="B286" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -31256,35 +31251,40 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>481249</v>
+        <v>481427</v>
       </c>
       <c r="R286" t="n">
         <v>6790669</v>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -31329,7 +31329,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD286" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -6771,10 +6771,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122907535</v>
+        <v>122910507</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6783,41 +6783,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480604</v>
+        <v>480751</v>
       </c>
       <c r="R59" t="n">
-        <v>6790798</v>
+        <v>6790806</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6871,22 +6871,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122908196</v>
+        <v>122905560</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6895,25 +6895,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480681</v>
+        <v>480689</v>
       </c>
       <c r="R60" t="n">
-        <v>6790816</v>
+        <v>6790776</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6956,19 +6956,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6983,22 +6973,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122908658</v>
+        <v>122910737</v>
       </c>
       <c r="B61" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7007,41 +6997,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480701</v>
+        <v>480800</v>
       </c>
       <c r="R61" t="n">
-        <v>6790532</v>
+        <v>6790542</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7068,19 +7058,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,19 +7075,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122907981</v>
+        <v>122911585</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -7147,13 +7127,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480580</v>
+        <v>481035</v>
       </c>
       <c r="R62" t="n">
-        <v>6790754</v>
+        <v>6790750</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7182,7 +7162,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7192,7 +7172,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7207,19 +7187,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122910507</v>
+        <v>122916548</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -7255,17 +7235,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480751</v>
+        <v>481290</v>
       </c>
       <c r="R63" t="n">
-        <v>6790806</v>
+        <v>6790576</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7292,19 +7272,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7319,19 +7289,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122905560</v>
+        <v>122907326</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7371,10 +7341,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480689</v>
+        <v>480712</v>
       </c>
       <c r="R64" t="n">
-        <v>6790776</v>
+        <v>6790625</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7433,7 +7403,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122910737</v>
+        <v>122913931</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7473,10 +7443,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480800</v>
+        <v>480817</v>
       </c>
       <c r="R65" t="n">
-        <v>6790542</v>
+        <v>6790670</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7535,7 +7505,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122911585</v>
+        <v>122909144</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -7571,17 +7541,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481035</v>
+        <v>480738</v>
       </c>
       <c r="R66" t="n">
-        <v>6790750</v>
+        <v>6790666</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7608,19 +7578,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7635,19 +7595,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122916548</v>
+        <v>122914177</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7683,17 +7643,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481290</v>
+        <v>481318</v>
       </c>
       <c r="R67" t="n">
-        <v>6790576</v>
+        <v>6790679</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7720,9 +7680,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7737,19 +7707,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122907326</v>
+        <v>122908082</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7785,17 +7755,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480712</v>
+        <v>480607</v>
       </c>
       <c r="R68" t="n">
-        <v>6790625</v>
+        <v>6790687</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7822,9 +7792,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7839,19 +7819,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122913931</v>
+        <v>122915091</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7891,10 +7871,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480817</v>
+        <v>480681</v>
       </c>
       <c r="R69" t="n">
-        <v>6790670</v>
+        <v>6790816</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7924,9 +7904,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7941,19 +7931,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122909144</v>
+        <v>122908242</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7993,10 +7983,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480738</v>
+        <v>480743</v>
       </c>
       <c r="R70" t="n">
-        <v>6790666</v>
+        <v>6790542</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8055,7 +8045,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122914177</v>
+        <v>122907981</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8095,10 +8085,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481318</v>
+        <v>480580</v>
       </c>
       <c r="R71" t="n">
-        <v>6790679</v>
+        <v>6790754</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8130,7 +8120,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8140,7 +8130,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,10 +8157,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122908082</v>
+        <v>122907535</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8179,41 +8169,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480607</v>
+        <v>480604</v>
       </c>
       <c r="R72" t="n">
-        <v>6790687</v>
+        <v>6790798</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8242,7 +8232,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8252,7 +8242,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8267,22 +8257,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122915091</v>
+        <v>122908196</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8291,25 +8281,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8354,7 +8344,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8364,7 +8354,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8391,10 +8381,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122908242</v>
+        <v>122908658</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8403,41 +8393,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480743</v>
+        <v>480701</v>
       </c>
       <c r="R74" t="n">
-        <v>6790542</v>
+        <v>6790532</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8464,9 +8454,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8481,12 +8481,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -10643,7 +10643,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122916316</v>
+        <v>122909058</v>
       </c>
       <c r="B95" t="n">
         <v>78766</v>
@@ -10679,14 +10679,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481273</v>
+        <v>480660</v>
       </c>
       <c r="R95" t="n">
-        <v>6790567</v>
+        <v>6790681</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10716,9 +10716,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10733,19 +10743,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122906741</v>
+        <v>122915451</v>
       </c>
       <c r="B96" t="n">
         <v>78766</v>
@@ -10785,10 +10795,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480726</v>
+        <v>481063</v>
       </c>
       <c r="R96" t="n">
-        <v>6790689</v>
+        <v>6790636</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10847,7 +10857,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122914138</v>
+        <v>122916316</v>
       </c>
       <c r="B97" t="n">
         <v>78766</v>
@@ -10887,10 +10897,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480858</v>
+        <v>481273</v>
       </c>
       <c r="R97" t="n">
-        <v>6790672</v>
+        <v>6790567</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10949,7 +10959,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122909058</v>
+        <v>122906741</v>
       </c>
       <c r="B98" t="n">
         <v>78766</v>
@@ -10985,14 +10995,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480660</v>
+        <v>480726</v>
       </c>
       <c r="R98" t="n">
-        <v>6790681</v>
+        <v>6790689</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11022,19 +11032,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11049,19 +11049,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122915451</v>
+        <v>122914138</v>
       </c>
       <c r="B99" t="n">
         <v>78766</v>
@@ -11101,10 +11101,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481063</v>
+        <v>480858</v>
       </c>
       <c r="R99" t="n">
-        <v>6790636</v>
+        <v>6790672</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -30373,10 +30373,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122961952</v>
+        <v>122968089</v>
       </c>
       <c r="B278" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -30385,46 +30385,41 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>480782</v>
+        <v>481376</v>
       </c>
       <c r="R278" t="n">
-        <v>6790637</v>
+        <v>6790518</v>
       </c>
       <c r="S278" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -30451,24 +30446,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC278" t="inlineStr">
-        <is>
-          <t>Grov tall</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30483,12 +30463,12 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
@@ -30597,10 +30577,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122967445</v>
+        <v>122965948</v>
       </c>
       <c r="B280" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -30609,25 +30589,25 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -30637,10 +30617,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>481249</v>
+        <v>481142</v>
       </c>
       <c r="R280" t="n">
-        <v>6790669</v>
+        <v>6790715</v>
       </c>
       <c r="S280" t="n">
         <v>9</v>
@@ -30672,7 +30652,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -30682,7 +30662,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30709,10 +30689,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122965948</v>
+        <v>122969601</v>
       </c>
       <c r="B281" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -30721,41 +30701,41 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>481142</v>
+        <v>481528</v>
       </c>
       <c r="R281" t="n">
-        <v>6790715</v>
+        <v>6790490</v>
       </c>
       <c r="S281" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -30782,19 +30762,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>12:54</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30809,19 +30779,19 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122969601</v>
+        <v>122962130</v>
       </c>
       <c r="B282" t="n">
         <v>78766</v>
@@ -30857,17 +30827,17 @@
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>481528</v>
+        <v>480812</v>
       </c>
       <c r="R282" t="n">
-        <v>6790490</v>
+        <v>6790632</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -30894,9 +30864,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30911,19 +30891,19 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122962130</v>
+        <v>122960562</v>
       </c>
       <c r="B283" t="n">
         <v>78766</v>
@@ -30959,17 +30939,17 @@
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>480812</v>
+        <v>480756</v>
       </c>
       <c r="R283" t="n">
-        <v>6790632</v>
+        <v>6790775</v>
       </c>
       <c r="S283" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -30996,19 +30976,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB283" t="inlineStr">
-        <is>
-          <t>11:25</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -31023,22 +30993,22 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122960562</v>
+        <v>122974049</v>
       </c>
       <c r="B284" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -31047,41 +31017,46 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>480756</v>
+        <v>481427</v>
       </c>
       <c r="R284" t="n">
-        <v>6790775</v>
+        <v>6790669</v>
       </c>
       <c r="S284" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -31108,9 +31083,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -31125,22 +31110,22 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122968089</v>
+        <v>122961952</v>
       </c>
       <c r="B285" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31149,41 +31134,46 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>481376</v>
+        <v>480782</v>
       </c>
       <c r="R285" t="n">
-        <v>6790518</v>
+        <v>6790637</v>
       </c>
       <c r="S285" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -31210,9 +31200,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>Grov tall</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -31227,22 +31232,22 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122974049</v>
+        <v>122967445</v>
       </c>
       <c r="B286" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -31251,40 +31256,35 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>481427</v>
+        <v>481249</v>
       </c>
       <c r="R286" t="n">
         <v>6790669</v>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -31329,7 +31329,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -31356,10 +31356,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122975396</v>
+        <v>122965139</v>
       </c>
       <c r="B287" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -31368,41 +31368,41 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>481394</v>
+        <v>481024</v>
       </c>
       <c r="R287" t="n">
-        <v>6790771</v>
+        <v>6790713</v>
       </c>
       <c r="S287" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -31429,19 +31429,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>16:32</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -31456,19 +31446,19 @@
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122962270</v>
+        <v>122975396</v>
       </c>
       <c r="B288" t="n">
         <v>78766</v>
@@ -31504,17 +31494,17 @@
       <c r="I288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>480818</v>
+        <v>481394</v>
       </c>
       <c r="R288" t="n">
-        <v>6790615</v>
+        <v>6790771</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -31541,9 +31531,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -31558,22 +31558,22 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122965139</v>
+        <v>122962270</v>
       </c>
       <c r="B289" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -31582,25 +31582,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -31610,10 +31610,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>481024</v>
+        <v>480818</v>
       </c>
       <c r="R289" t="n">
-        <v>6790713</v>
+        <v>6790615</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122899836</v>
+        <v>122899520</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,39 +1338,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480517</v>
+        <v>480479</v>
       </c>
       <c r="R8" t="n">
-        <v>6790688</v>
+        <v>6790654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122899520</v>
+        <v>122899836</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,34 +1440,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480479</v>
+        <v>480517</v>
       </c>
       <c r="R9" t="n">
-        <v>6790654</v>
+        <v>6790688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122913744</v>
+        <v>122914092</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481158</v>
+        <v>481216</v>
       </c>
       <c r="R13" t="n">
-        <v>6790716</v>
+        <v>6790675</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,19 +1942,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122913962</v>
+        <v>122913744</v>
       </c>
       <c r="B14" t="n">
         <v>78771</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481216</v>
+        <v>481158</v>
       </c>
       <c r="R14" t="n">
-        <v>6790675</v>
+        <v>6790716</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,19 +2054,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122913923</v>
+        <v>122913962</v>
       </c>
       <c r="B15" t="n">
         <v>78771</v>
@@ -2102,17 +2102,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480817</v>
+        <v>481216</v>
       </c>
       <c r="R15" t="n">
-        <v>6790670</v>
+        <v>6790675</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,9 +2139,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,19 +2166,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122911611</v>
+        <v>122913923</v>
       </c>
       <c r="B16" t="n">
         <v>78771</v>
@@ -2204,17 +2214,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481072</v>
+        <v>480817</v>
       </c>
       <c r="R16" t="n">
-        <v>6790731</v>
+        <v>6790670</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,19 +2251,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,19 +2268,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908454</v>
+        <v>122911611</v>
       </c>
       <c r="B17" t="n">
         <v>78771</v>
@@ -2316,17 +2316,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480681</v>
+        <v>481072</v>
       </c>
       <c r="R17" t="n">
-        <v>6790816</v>
+        <v>6790731</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,19 +2380,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122907575</v>
+        <v>122908454</v>
       </c>
       <c r="B18" t="n">
         <v>78771</v>
@@ -2428,17 +2428,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480571</v>
+        <v>480681</v>
       </c>
       <c r="R18" t="n">
-        <v>6790798</v>
+        <v>6790816</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,22 +2492,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122907291</v>
+        <v>122907575</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480712</v>
+        <v>480571</v>
       </c>
       <c r="R19" t="n">
-        <v>6790625</v>
+        <v>6790798</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2577,9 +2577,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,22 +2604,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122915881</v>
+        <v>122907291</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481164</v>
+        <v>480712</v>
       </c>
       <c r="R20" t="n">
-        <v>6790573</v>
+        <v>6790625</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122905786</v>
+        <v>122915881</v>
       </c>
       <c r="B21" t="n">
         <v>78771</v>
@@ -2748,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480687</v>
+        <v>481164</v>
       </c>
       <c r="R21" t="n">
-        <v>6790754</v>
+        <v>6790573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122914092</v>
+        <v>122905786</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,41 +2832,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481216</v>
+        <v>480687</v>
       </c>
       <c r="R22" t="n">
-        <v>6790675</v>
+        <v>6790754</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2883,19 +2893,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,22 +2910,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122910464</v>
+        <v>122906741</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>78771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2934,38 +2934,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480751</v>
+        <v>480726</v>
       </c>
       <c r="R23" t="n">
-        <v>6790806</v>
+        <v>6790689</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,19 +2995,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,22 +3012,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908588</v>
+        <v>122911238</v>
       </c>
       <c r="B24" t="n">
-        <v>78508</v>
+        <v>78771</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3050,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3074,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480638</v>
+        <v>481009</v>
       </c>
       <c r="R24" t="n">
-        <v>6790738</v>
+        <v>6790696</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,19 +3124,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122906741</v>
+        <v>122907632</v>
       </c>
       <c r="B25" t="n">
         <v>78771</v>
@@ -3186,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480726</v>
+        <v>480720</v>
       </c>
       <c r="R25" t="n">
-        <v>6790689</v>
+        <v>6790586</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122911238</v>
+        <v>122915292</v>
       </c>
       <c r="B26" t="n">
         <v>78771</v>
@@ -3288,13 +3278,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481009</v>
+        <v>480729</v>
       </c>
       <c r="R26" t="n">
-        <v>6790696</v>
+        <v>6790767</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3323,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3360,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122907632</v>
+        <v>122907044</v>
       </c>
       <c r="B27" t="n">
         <v>78771</v>
@@ -3400,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480720</v>
+        <v>480733</v>
       </c>
       <c r="R27" t="n">
-        <v>6790586</v>
+        <v>6790651</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122915292</v>
+        <v>122910548</v>
       </c>
       <c r="B28" t="n">
         <v>78771</v>
@@ -3498,17 +3488,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480729</v>
+        <v>480772</v>
       </c>
       <c r="R28" t="n">
-        <v>6790767</v>
+        <v>6790619</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3535,19 +3525,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,19 +3542,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122907044</v>
+        <v>122914812</v>
       </c>
       <c r="B29" t="n">
         <v>78771</v>
@@ -3614,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480733</v>
+        <v>480982</v>
       </c>
       <c r="R29" t="n">
-        <v>6790651</v>
+        <v>6790653</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3656,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122910548</v>
+        <v>122907579</v>
       </c>
       <c r="B30" t="n">
         <v>78771</v>
@@ -3716,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480772</v>
+        <v>480739</v>
       </c>
       <c r="R30" t="n">
-        <v>6790619</v>
+        <v>6790609</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122914812</v>
+        <v>122917031</v>
       </c>
       <c r="B31" t="n">
         <v>78771</v>
@@ -3818,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480982</v>
+        <v>481382</v>
       </c>
       <c r="R31" t="n">
-        <v>6790653</v>
+        <v>6790485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3880,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122907579</v>
+        <v>122914302</v>
       </c>
       <c r="B32" t="n">
         <v>78771</v>
@@ -3920,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480739</v>
+        <v>480864</v>
       </c>
       <c r="R32" t="n">
-        <v>6790609</v>
+        <v>6790682</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3982,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122917031</v>
+        <v>122908588</v>
       </c>
       <c r="B33" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3998,34 +3978,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481382</v>
+        <v>480638</v>
       </c>
       <c r="R33" t="n">
-        <v>6790485</v>
+        <v>6790738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4055,9 +4035,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4072,22 +4062,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122914302</v>
+        <v>122910464</v>
       </c>
       <c r="B34" t="n">
-        <v>78771</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4096,38 +4086,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480864</v>
+        <v>480751</v>
       </c>
       <c r="R34" t="n">
-        <v>6790682</v>
+        <v>6790806</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4157,9 +4147,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4174,12 +4174,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122915141</v>
+        <v>122905901</v>
       </c>
       <c r="B66" t="n">
         <v>78771</v>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480999</v>
+        <v>480680</v>
       </c>
       <c r="R66" t="n">
-        <v>6790659</v>
+        <v>6790718</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7573,7 +7573,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122914329</v>
+        <v>122915141</v>
       </c>
       <c r="B67" t="n">
         <v>78771</v>
@@ -7609,17 +7609,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481184</v>
+        <v>480999</v>
       </c>
       <c r="R67" t="n">
         <v>6790659</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7646,19 +7646,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7673,19 +7663,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122908091</v>
+        <v>122914329</v>
       </c>
       <c r="B68" t="n">
         <v>78771</v>
@@ -7725,13 +7715,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480631</v>
+        <v>481184</v>
       </c>
       <c r="R68" t="n">
-        <v>6790746</v>
+        <v>6790659</v>
       </c>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7760,7 +7750,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7770,7 +7760,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7785,19 +7775,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122913918</v>
+        <v>122908091</v>
       </c>
       <c r="B69" t="n">
         <v>78771</v>
@@ -7837,13 +7827,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481291</v>
+        <v>480631</v>
       </c>
       <c r="R69" t="n">
-        <v>6790740</v>
+        <v>6790746</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7872,7 +7862,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7882,7 +7872,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7897,22 +7887,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122908063</v>
+        <v>122913918</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>78771</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7921,25 +7911,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7949,13 +7939,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480571</v>
+        <v>481291</v>
       </c>
       <c r="R70" t="n">
-        <v>6790798</v>
+        <v>6790740</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7984,7 +7974,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7994,7 +7984,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8009,22 +7999,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122905901</v>
+        <v>122908063</v>
       </c>
       <c r="B71" t="n">
-        <v>78771</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8033,38 +8023,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480680</v>
+        <v>480571</v>
       </c>
       <c r="R71" t="n">
-        <v>6790718</v>
+        <v>6790798</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8094,9 +8084,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8111,12 +8111,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -13729,10 +13729,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122915272</v>
+        <v>122908515</v>
       </c>
       <c r="B124" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13745,21 +13745,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13769,10 +13769,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>481024</v>
+        <v>480639</v>
       </c>
       <c r="R124" t="n">
-        <v>6790673</v>
+        <v>6790797</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13802,9 +13802,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13819,19 +13829,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122915451</v>
+        <v>122915272</v>
       </c>
       <c r="B125" t="n">
         <v>78771</v>
@@ -13871,10 +13881,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>481063</v>
+        <v>481024</v>
       </c>
       <c r="R125" t="n">
-        <v>6790636</v>
+        <v>6790673</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13933,7 +13943,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122905650</v>
+        <v>122915451</v>
       </c>
       <c r="B126" t="n">
         <v>78771</v>
@@ -13973,10 +13983,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480698</v>
+        <v>481063</v>
       </c>
       <c r="R126" t="n">
-        <v>6790762</v>
+        <v>6790636</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14035,7 +14045,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122914058</v>
+        <v>122905650</v>
       </c>
       <c r="B127" t="n">
         <v>78771</v>
@@ -14075,10 +14085,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480832</v>
+        <v>480698</v>
       </c>
       <c r="R127" t="n">
-        <v>6790668</v>
+        <v>6790762</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14137,7 +14147,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122907072</v>
+        <v>122914058</v>
       </c>
       <c r="B128" t="n">
         <v>78771</v>
@@ -14177,10 +14187,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480736</v>
+        <v>480832</v>
       </c>
       <c r="R128" t="n">
-        <v>6790634</v>
+        <v>6790668</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14239,7 +14249,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122910488</v>
+        <v>122907072</v>
       </c>
       <c r="B129" t="n">
         <v>78771</v>
@@ -14279,10 +14289,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480764</v>
+        <v>480736</v>
       </c>
       <c r="R129" t="n">
-        <v>6790646</v>
+        <v>6790634</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14341,7 +14351,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122907867</v>
+        <v>122910488</v>
       </c>
       <c r="B130" t="n">
         <v>78771</v>
@@ -14381,10 +14391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480744</v>
+        <v>480764</v>
       </c>
       <c r="R130" t="n">
-        <v>6790595</v>
+        <v>6790646</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14443,10 +14453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122908515</v>
+        <v>122907867</v>
       </c>
       <c r="B131" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14459,21 +14469,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14483,10 +14493,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480639</v>
+        <v>480744</v>
       </c>
       <c r="R131" t="n">
-        <v>6790797</v>
+        <v>6790595</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14516,19 +14526,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14543,12 +14543,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -21003,10 +21003,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122970166</v>
+        <v>122967530</v>
       </c>
       <c r="B192" t="n">
-        <v>8441</v>
+        <v>78771</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21015,43 +21015,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>481546</v>
+        <v>481263</v>
       </c>
       <c r="R192" t="n">
-        <v>6790501</v>
+        <v>6790687</v>
       </c>
       <c r="S192" t="n">
         <v>9</v>
@@ -21083,7 +21078,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21093,7 +21088,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21120,7 +21115,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122967530</v>
+        <v>122973371</v>
       </c>
       <c r="B193" t="n">
         <v>78771</v>
@@ -21160,10 +21155,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>481263</v>
+        <v>481551</v>
       </c>
       <c r="R193" t="n">
-        <v>6790687</v>
+        <v>6790539</v>
       </c>
       <c r="S193" t="n">
         <v>9</v>
@@ -21195,7 +21190,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21205,7 +21200,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21232,7 +21227,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122973371</v>
+        <v>122968577</v>
       </c>
       <c r="B194" t="n">
         <v>78771</v>
@@ -21272,10 +21267,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>481551</v>
+        <v>481434</v>
       </c>
       <c r="R194" t="n">
-        <v>6790539</v>
+        <v>6790538</v>
       </c>
       <c r="S194" t="n">
         <v>9</v>
@@ -21307,7 +21302,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21317,7 +21312,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21344,7 +21339,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122968577</v>
+        <v>122975272</v>
       </c>
       <c r="B195" t="n">
         <v>78771</v>
@@ -21380,17 +21375,17 @@
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>481434</v>
+        <v>481448</v>
       </c>
       <c r="R195" t="n">
-        <v>6790538</v>
+        <v>6790745</v>
       </c>
       <c r="S195" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21417,19 +21412,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21444,19 +21429,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122975272</v>
+        <v>122962270</v>
       </c>
       <c r="B196" t="n">
         <v>78771</v>
@@ -21492,14 +21477,14 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>481448</v>
+        <v>480818</v>
       </c>
       <c r="R196" t="n">
-        <v>6790745</v>
+        <v>6790615</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21558,7 +21543,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122962270</v>
+        <v>122960334</v>
       </c>
       <c r="B197" t="n">
         <v>78771</v>
@@ -21598,10 +21583,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>480818</v>
+        <v>480794</v>
       </c>
       <c r="R197" t="n">
-        <v>6790615</v>
+        <v>6790801</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21660,7 +21645,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122960334</v>
+        <v>122968715</v>
       </c>
       <c r="B198" t="n">
         <v>78771</v>
@@ -21700,10 +21685,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>480794</v>
+        <v>481459</v>
       </c>
       <c r="R198" t="n">
-        <v>6790801</v>
+        <v>6790483</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21762,7 +21747,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122968715</v>
+        <v>122960001</v>
       </c>
       <c r="B199" t="n">
         <v>78771</v>
@@ -21802,10 +21787,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>481459</v>
+        <v>480805</v>
       </c>
       <c r="R199" t="n">
-        <v>6790483</v>
+        <v>6790809</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21864,7 +21849,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122960001</v>
+        <v>122970352</v>
       </c>
       <c r="B200" t="n">
         <v>78771</v>
@@ -21900,17 +21885,17 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>480805</v>
+        <v>481566</v>
       </c>
       <c r="R200" t="n">
-        <v>6790809</v>
+        <v>6790511</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21937,9 +21922,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21954,22 +21949,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122970352</v>
+        <v>122976204</v>
       </c>
       <c r="B201" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21982,37 +21977,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>481566</v>
+        <v>481461</v>
       </c>
       <c r="R201" t="n">
-        <v>6790511</v>
+        <v>6790683</v>
       </c>
       <c r="S201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22039,19 +22034,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Spill och hackspår efter annan spett, miljöbilder.</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22066,22 +22056,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122976204</v>
+        <v>122970166</v>
       </c>
       <c r="B202" t="n">
-        <v>57497</v>
+        <v>8441</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22090,41 +22080,46 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>481461</v>
+        <v>481546</v>
       </c>
       <c r="R202" t="n">
-        <v>6790683</v>
+        <v>6790501</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22151,14 +22146,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Spill och hackspår efter annan spett, miljöbilder.</t>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22173,22 +22173,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122978194</v>
+        <v>122967764</v>
       </c>
       <c r="B203" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22197,43 +22197,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>481090</v>
+        <v>481304</v>
       </c>
       <c r="R203" t="n">
-        <v>6790709</v>
+        <v>6790615</v>
       </c>
       <c r="S203" t="n">
         <v>9</v>
@@ -22265,7 +22260,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22275,7 +22270,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22302,7 +22297,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122967764</v>
+        <v>122962209</v>
       </c>
       <c r="B204" t="n">
         <v>78771</v>
@@ -22338,17 +22333,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>481304</v>
+        <v>480818</v>
       </c>
       <c r="R204" t="n">
-        <v>6790615</v>
+        <v>6790633</v>
       </c>
       <c r="S204" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22375,19 +22370,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22402,19 +22387,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122962209</v>
+        <v>122968097</v>
       </c>
       <c r="B205" t="n">
         <v>78771</v>
@@ -22450,17 +22435,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>480818</v>
+        <v>481372</v>
       </c>
       <c r="R205" t="n">
-        <v>6790633</v>
+        <v>6790559</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -22487,9 +22472,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22504,22 +22499,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122968097</v>
+        <v>122978194</v>
       </c>
       <c r="B206" t="n">
-        <v>78771</v>
+        <v>56691</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22528,38 +22523,43 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>481372</v>
+        <v>481090</v>
       </c>
       <c r="R206" t="n">
-        <v>6790559</v>
+        <v>6790709</v>
       </c>
       <c r="S206" t="n">
         <v>9</v>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22601,7 +22601,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22628,10 +22628,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122964962</v>
+        <v>122961172</v>
       </c>
       <c r="B207" t="n">
-        <v>78795</v>
+        <v>78771</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22640,41 +22640,41 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>481026</v>
+        <v>480745</v>
       </c>
       <c r="R207" t="n">
-        <v>6790700</v>
+        <v>6790759</v>
       </c>
       <c r="S207" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22701,19 +22701,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22728,22 +22718,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122966313</v>
+        <v>122962067</v>
       </c>
       <c r="B208" t="n">
-        <v>78795</v>
+        <v>78771</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22752,25 +22742,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22780,10 +22770,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>481151</v>
+        <v>480821</v>
       </c>
       <c r="R208" t="n">
-        <v>6790709</v>
+        <v>6790633</v>
       </c>
       <c r="S208" t="n">
         <v>9</v>
@@ -22815,7 +22805,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22825,7 +22815,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22852,7 +22842,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122961172</v>
+        <v>122969047</v>
       </c>
       <c r="B209" t="n">
         <v>78771</v>
@@ -22892,10 +22882,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>480745</v>
+        <v>481468</v>
       </c>
       <c r="R209" t="n">
-        <v>6790759</v>
+        <v>6790486</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22928,6 +22918,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring på en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22954,7 +22949,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>122962067</v>
+        <v>122969543</v>
       </c>
       <c r="B210" t="n">
         <v>78771</v>
@@ -22990,17 +22985,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>480821</v>
+        <v>481496</v>
       </c>
       <c r="R210" t="n">
-        <v>6790633</v>
+        <v>6790486</v>
       </c>
       <c r="S210" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23027,19 +23022,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23054,22 +23044,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>122969047</v>
+        <v>122964962</v>
       </c>
       <c r="B211" t="n">
-        <v>78771</v>
+        <v>78795</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23078,41 +23068,41 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>481468</v>
+        <v>481026</v>
       </c>
       <c r="R211" t="n">
-        <v>6790486</v>
+        <v>6790700</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23139,14 +23129,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring på en radie av 40 meter.</t>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23161,22 +23156,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>122969543</v>
+        <v>122966313</v>
       </c>
       <c r="B212" t="n">
-        <v>78771</v>
+        <v>78795</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23185,41 +23180,41 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>481496</v>
+        <v>481151</v>
       </c>
       <c r="R212" t="n">
-        <v>6790486</v>
+        <v>6790709</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23246,14 +23241,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav.</t>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23268,12 +23268,12 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
@@ -26005,7 +26005,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>122968705</v>
+        <v>122967445</v>
       </c>
       <c r="B238" t="n">
         <v>78771</v>
@@ -26045,10 +26045,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>481441</v>
+        <v>481249</v>
       </c>
       <c r="R238" t="n">
-        <v>6790542</v>
+        <v>6790669</v>
       </c>
       <c r="S238" t="n">
         <v>9</v>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -26090,7 +26090,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26117,10 +26117,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>122962565</v>
+        <v>122966647</v>
       </c>
       <c r="B239" t="n">
-        <v>78507</v>
+        <v>78771</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -26133,37 +26133,37 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>480854</v>
+        <v>481216</v>
       </c>
       <c r="R239" t="n">
-        <v>6790625</v>
+        <v>6790707</v>
       </c>
       <c r="S239" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -26190,19 +26190,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>11:37</t>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Torrakor återkommer i området och lågor som visar sig där snön tinat.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26217,19 +26212,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>122967445</v>
+        <v>122968705</v>
       </c>
       <c r="B240" t="n">
         <v>78771</v>
@@ -26269,10 +26264,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>481249</v>
+        <v>481441</v>
       </c>
       <c r="R240" t="n">
-        <v>6790669</v>
+        <v>6790542</v>
       </c>
       <c r="S240" t="n">
         <v>9</v>
@@ -26304,7 +26299,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -26314,7 +26309,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -26341,7 +26336,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>122966647</v>
+        <v>122965694</v>
       </c>
       <c r="B241" t="n">
         <v>78771</v>
@@ -26377,17 +26372,17 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>481216</v>
+        <v>481111</v>
       </c>
       <c r="R241" t="n">
-        <v>6790707</v>
+        <v>6790702</v>
       </c>
       <c r="S241" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -26414,14 +26409,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>Torrakor återkommer i området och lågor som visar sig där snön tinat.</t>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -26436,22 +26436,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>122965694</v>
+        <v>122962565</v>
       </c>
       <c r="B242" t="n">
-        <v>78771</v>
+        <v>78507</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -26464,21 +26464,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -26488,10 +26488,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>481111</v>
+        <v>480854</v>
       </c>
       <c r="R242" t="n">
-        <v>6790702</v>
+        <v>6790625</v>
       </c>
       <c r="S242" t="n">
         <v>9</v>
@@ -26523,7 +26523,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -26533,7 +26533,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -26560,10 +26560,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>122975234</v>
+        <v>122961613</v>
       </c>
       <c r="B243" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -26576,34 +26576,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>481459</v>
+        <v>480767</v>
       </c>
       <c r="R243" t="n">
-        <v>6790740</v>
+        <v>6790673</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -26662,7 +26662,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122961613</v>
+        <v>122968533</v>
       </c>
       <c r="B244" t="n">
         <v>78771</v>
@@ -26698,17 +26698,17 @@
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>480767</v>
+        <v>481432</v>
       </c>
       <c r="R244" t="n">
-        <v>6790673</v>
+        <v>6790537</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -26735,9 +26735,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26752,19 +26762,19 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>122968533</v>
+        <v>122968143</v>
       </c>
       <c r="B245" t="n">
         <v>78771</v>
@@ -26804,10 +26814,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>481432</v>
+        <v>481374</v>
       </c>
       <c r="R245" t="n">
-        <v>6790537</v>
+        <v>6790558</v>
       </c>
       <c r="S245" t="n">
         <v>9</v>
@@ -26839,7 +26849,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -26849,7 +26859,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26876,7 +26886,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>122968143</v>
+        <v>122968666</v>
       </c>
       <c r="B246" t="n">
         <v>78771</v>
@@ -26916,10 +26926,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>481374</v>
+        <v>481436</v>
       </c>
       <c r="R246" t="n">
-        <v>6790558</v>
+        <v>6790540</v>
       </c>
       <c r="S246" t="n">
         <v>9</v>
@@ -26951,7 +26961,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -26961,7 +26971,12 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26988,7 +27003,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122968666</v>
+        <v>122973297</v>
       </c>
       <c r="B247" t="n">
         <v>78771</v>
@@ -27024,17 +27039,17 @@
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>481436</v>
+        <v>481575</v>
       </c>
       <c r="R247" t="n">
-        <v>6790540</v>
+        <v>6790530</v>
       </c>
       <c r="S247" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -27061,24 +27076,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27093,19 +27093,19 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122973297</v>
+        <v>122968168</v>
       </c>
       <c r="B248" t="n">
         <v>78771</v>
@@ -27141,14 +27141,14 @@
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>481575</v>
+        <v>481398</v>
       </c>
       <c r="R248" t="n">
-        <v>6790530</v>
+        <v>6790509</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -27181,6 +27181,11 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Garnlav med torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -27207,10 +27212,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122968168</v>
+        <v>122975234</v>
       </c>
       <c r="B249" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -27223,34 +27228,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>481398</v>
+        <v>481459</v>
       </c>
       <c r="R249" t="n">
-        <v>6790509</v>
+        <v>6790740</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -27283,11 +27288,6 @@
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Garnlav med torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27436,10 +27436,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122962111</v>
+        <v>122970092</v>
       </c>
       <c r="B251" t="n">
-        <v>78771</v>
+        <v>78795</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -27448,41 +27448,41 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>480804</v>
+        <v>481532</v>
       </c>
       <c r="R251" t="n">
-        <v>6790650</v>
+        <v>6790516</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -27509,9 +27509,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -27526,19 +27536,19 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122976607</v>
+        <v>122962111</v>
       </c>
       <c r="B252" t="n">
         <v>78771</v>
@@ -27574,17 +27584,17 @@
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>481343</v>
+        <v>480804</v>
       </c>
       <c r="R252" t="n">
-        <v>6790726</v>
+        <v>6790650</v>
       </c>
       <c r="S252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -27611,19 +27621,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>17:00</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27638,19 +27638,19 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122968384</v>
+        <v>122976607</v>
       </c>
       <c r="B253" t="n">
         <v>78771</v>
@@ -27690,10 +27690,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>481429</v>
+        <v>481343</v>
       </c>
       <c r="R253" t="n">
-        <v>6790532</v>
+        <v>6790726</v>
       </c>
       <c r="S253" t="n">
         <v>9</v>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27762,7 +27762,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122973309</v>
+        <v>122968384</v>
       </c>
       <c r="B254" t="n">
         <v>78771</v>
@@ -27802,10 +27802,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>481568</v>
+        <v>481429</v>
       </c>
       <c r="R254" t="n">
-        <v>6790545</v>
+        <v>6790532</v>
       </c>
       <c r="S254" t="n">
         <v>9</v>
@@ -27837,7 +27837,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27874,7 +27874,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122975172</v>
+        <v>122973309</v>
       </c>
       <c r="B255" t="n">
         <v>78771</v>
@@ -27910,17 +27910,17 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>481465</v>
+        <v>481568</v>
       </c>
       <c r="R255" t="n">
-        <v>6790730</v>
+        <v>6790545</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -27947,14 +27947,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Garn med miljöbild.</t>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27969,19 +27974,19 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122965617</v>
+        <v>122975172</v>
       </c>
       <c r="B256" t="n">
         <v>78771</v>
@@ -28017,14 +28022,14 @@
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>481109</v>
+        <v>481465</v>
       </c>
       <c r="R256" t="n">
-        <v>6790688</v>
+        <v>6790730</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28057,6 +28062,11 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Garn med miljöbild.</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -28083,7 +28093,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122970333</v>
+        <v>122965617</v>
       </c>
       <c r="B257" t="n">
         <v>78771</v>
@@ -28123,10 +28133,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>481622</v>
+        <v>481109</v>
       </c>
       <c r="R257" t="n">
-        <v>6790484</v>
+        <v>6790688</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28159,11 +28169,6 @@
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -28190,10 +28195,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122970092</v>
+        <v>122970333</v>
       </c>
       <c r="B258" t="n">
-        <v>78795</v>
+        <v>78771</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -28202,41 +28207,41 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>481532</v>
+        <v>481622</v>
       </c>
       <c r="R258" t="n">
-        <v>6790516</v>
+        <v>6790484</v>
       </c>
       <c r="S258" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -28263,19 +28268,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>14:05</t>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -28290,22 +28290,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122969800</v>
+        <v>122960352</v>
       </c>
       <c r="B259" t="n">
-        <v>78795</v>
+        <v>78771</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -28314,41 +28314,41 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>481538</v>
+        <v>480778</v>
       </c>
       <c r="R259" t="n">
-        <v>6790506</v>
+        <v>6790784</v>
       </c>
       <c r="S259" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -28375,19 +28375,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -28402,19 +28392,19 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122960352</v>
+        <v>122965035</v>
       </c>
       <c r="B260" t="n">
         <v>78771</v>
@@ -28450,17 +28440,17 @@
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>480778</v>
+        <v>481031</v>
       </c>
       <c r="R260" t="n">
-        <v>6790784</v>
+        <v>6790714</v>
       </c>
       <c r="S260" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -28487,9 +28477,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -28504,19 +28504,19 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122965035</v>
+        <v>122968724</v>
       </c>
       <c r="B261" t="n">
         <v>78771</v>
@@ -28556,10 +28556,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>481031</v>
+        <v>481443</v>
       </c>
       <c r="R261" t="n">
-        <v>6790714</v>
+        <v>6790544</v>
       </c>
       <c r="S261" t="n">
         <v>9</v>
@@ -28591,7 +28591,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -28601,7 +28601,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -28628,7 +28628,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122968724</v>
+        <v>122959766</v>
       </c>
       <c r="B262" t="n">
         <v>78771</v>
@@ -28668,10 +28668,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>481443</v>
+        <v>480779</v>
       </c>
       <c r="R262" t="n">
-        <v>6790544</v>
+        <v>6790803</v>
       </c>
       <c r="S262" t="n">
         <v>9</v>
@@ -28703,7 +28703,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28740,10 +28740,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122959766</v>
+        <v>122969800</v>
       </c>
       <c r="B263" t="n">
-        <v>78771</v>
+        <v>78795</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -28752,25 +28752,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -28780,10 +28780,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>480779</v>
+        <v>481538</v>
       </c>
       <c r="R263" t="n">
-        <v>6790803</v>
+        <v>6790506</v>
       </c>
       <c r="S263" t="n">
         <v>9</v>
@@ -28815,7 +28815,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -28825,7 +28825,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29392,10 +29392,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122962208</v>
+        <v>122970062</v>
       </c>
       <c r="B269" t="n">
-        <v>8441</v>
+        <v>78771</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -29404,43 +29404,38 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>480810</v>
+        <v>481533</v>
       </c>
       <c r="R269" t="n">
-        <v>6790631</v>
+        <v>6790513</v>
       </c>
       <c r="S269" t="n">
         <v>9</v>
@@ -29472,7 +29467,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -29482,7 +29477,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29509,7 +29504,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122970062</v>
+        <v>122968760</v>
       </c>
       <c r="B270" t="n">
         <v>78771</v>
@@ -29549,10 +29544,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>481533</v>
+        <v>481444</v>
       </c>
       <c r="R270" t="n">
-        <v>6790513</v>
+        <v>6790544</v>
       </c>
       <c r="S270" t="n">
         <v>9</v>
@@ -29584,7 +29579,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -29594,7 +29589,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -29621,7 +29616,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122968760</v>
+        <v>122977907</v>
       </c>
       <c r="B271" t="n">
         <v>78771</v>
@@ -29661,10 +29656,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>481444</v>
+        <v>481302</v>
       </c>
       <c r="R271" t="n">
-        <v>6790544</v>
+        <v>6790744</v>
       </c>
       <c r="S271" t="n">
         <v>9</v>
@@ -29696,7 +29691,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -29706,7 +29701,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29733,7 +29728,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122977907</v>
+        <v>122964451</v>
       </c>
       <c r="B272" t="n">
         <v>78771</v>
@@ -29769,17 +29764,17 @@
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>481302</v>
+        <v>481009</v>
       </c>
       <c r="R272" t="n">
-        <v>6790744</v>
+        <v>6790709</v>
       </c>
       <c r="S272" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -29806,19 +29801,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>17:17</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29833,19 +29818,19 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122964451</v>
+        <v>122977985</v>
       </c>
       <c r="B273" t="n">
         <v>78771</v>
@@ -29881,17 +29866,17 @@
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>481009</v>
+        <v>481229</v>
       </c>
       <c r="R273" t="n">
-        <v>6790709</v>
+        <v>6790728</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -29918,9 +29903,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -29935,19 +29930,19 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122977985</v>
+        <v>122973693</v>
       </c>
       <c r="B274" t="n">
         <v>78771</v>
@@ -29987,10 +29982,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>481229</v>
+        <v>481472</v>
       </c>
       <c r="R274" t="n">
-        <v>6790728</v>
+        <v>6790535</v>
       </c>
       <c r="S274" t="n">
         <v>9</v>
@@ -30022,7 +30017,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -30032,7 +30027,12 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>På Granar</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30059,10 +30059,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122973693</v>
+        <v>122962208</v>
       </c>
       <c r="B275" t="n">
-        <v>78771</v>
+        <v>8441</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -30071,38 +30071,43 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>481472</v>
+        <v>480810</v>
       </c>
       <c r="R275" t="n">
-        <v>6790535</v>
+        <v>6790631</v>
       </c>
       <c r="S275" t="n">
         <v>9</v>
@@ -30134,7 +30139,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -30144,12 +30149,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>På Granar</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD275" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122912843</v>
+        <v>122910507</v>
       </c>
       <c r="B13" t="n">
         <v>78775</v>
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481068</v>
+        <v>480751</v>
       </c>
       <c r="R13" t="n">
-        <v>6790734</v>
+        <v>6790806</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122915259</v>
+        <v>122913095</v>
       </c>
       <c r="B14" t="n">
-        <v>78511</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,40 +1970,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480813</v>
+        <v>480874</v>
       </c>
       <c r="R14" t="n">
-        <v>6790675</v>
+        <v>6790659</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2030,47 +2027,36 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122910417</v>
+        <v>122908448</v>
       </c>
       <c r="B15" t="n">
         <v>78775</v>
@@ -2106,17 +2092,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480759</v>
+        <v>480628</v>
       </c>
       <c r="R15" t="n">
-        <v>6790654</v>
+        <v>6790661</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2143,9 +2129,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,19 +2156,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122910753</v>
+        <v>122906981</v>
       </c>
       <c r="B16" t="n">
         <v>78775</v>
@@ -2212,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480802</v>
+        <v>480725</v>
       </c>
       <c r="R16" t="n">
-        <v>6790516</v>
+        <v>6790654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122911585</v>
+        <v>122916369</v>
       </c>
       <c r="B17" t="n">
         <v>78775</v>
@@ -2310,17 +2306,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481035</v>
+        <v>481274</v>
       </c>
       <c r="R17" t="n">
-        <v>6790750</v>
+        <v>6790592</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2347,19 +2343,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2374,19 +2360,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122910507</v>
+        <v>122908087</v>
       </c>
       <c r="B18" t="n">
         <v>78775</v>
@@ -2422,17 +2408,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480751</v>
+        <v>480758</v>
       </c>
       <c r="R18" t="n">
-        <v>6790806</v>
+        <v>6790557</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,19 +2445,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,19 +2462,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122913095</v>
+        <v>122908724</v>
       </c>
       <c r="B19" t="n">
         <v>78775</v>
@@ -2538,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480874</v>
+        <v>480766</v>
       </c>
       <c r="R19" t="n">
-        <v>6790659</v>
+        <v>6790505</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122908448</v>
+        <v>122912843</v>
       </c>
       <c r="B20" t="n">
         <v>78775</v>
@@ -2640,13 +2616,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480628</v>
+        <v>481068</v>
       </c>
       <c r="R20" t="n">
-        <v>6790661</v>
+        <v>6790734</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2675,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2685,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,22 +2676,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122906981</v>
+        <v>122915259</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>78511</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,37 +2704,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480725</v>
+        <v>480813</v>
       </c>
       <c r="R21" t="n">
-        <v>6790654</v>
+        <v>6790675</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2785,36 +2764,47 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122916369</v>
+        <v>122910417</v>
       </c>
       <c r="B22" t="n">
         <v>78775</v>
@@ -2854,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481274</v>
+        <v>480759</v>
       </c>
       <c r="R22" t="n">
-        <v>6790592</v>
+        <v>6790654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,7 +2906,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122908087</v>
+        <v>122910753</v>
       </c>
       <c r="B23" t="n">
         <v>78775</v>
@@ -2956,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480758</v>
+        <v>480802</v>
       </c>
       <c r="R23" t="n">
-        <v>6790557</v>
+        <v>6790516</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3008,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908724</v>
+        <v>122911585</v>
       </c>
       <c r="B24" t="n">
         <v>78775</v>
@@ -3054,17 +3044,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480766</v>
+        <v>481035</v>
       </c>
       <c r="R24" t="n">
-        <v>6790505</v>
+        <v>6790750</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3091,9 +3081,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3108,12 +3108,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -9048,7 +9048,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122907981</v>
+        <v>122916316</v>
       </c>
       <c r="B80" t="n">
         <v>78775</v>
@@ -9084,17 +9084,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480580</v>
+        <v>481273</v>
       </c>
       <c r="R80" t="n">
-        <v>6790754</v>
+        <v>6790567</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9121,19 +9121,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9148,19 +9138,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122915881</v>
+        <v>122910695</v>
       </c>
       <c r="B81" t="n">
         <v>78775</v>
@@ -9200,10 +9190,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481164</v>
+        <v>480801</v>
       </c>
       <c r="R81" t="n">
-        <v>6790573</v>
+        <v>6790557</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9262,7 +9252,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122915163</v>
+        <v>122907981</v>
       </c>
       <c r="B82" t="n">
         <v>78775</v>
@@ -9298,17 +9288,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480988</v>
+        <v>480580</v>
       </c>
       <c r="R82" t="n">
-        <v>6790673</v>
+        <v>6790754</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9335,9 +9325,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9352,19 +9352,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122905837</v>
+        <v>122915881</v>
       </c>
       <c r="B83" t="n">
         <v>78775</v>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480679</v>
+        <v>481164</v>
       </c>
       <c r="R83" t="n">
-        <v>6790740</v>
+        <v>6790573</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9466,7 +9466,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122909988</v>
+        <v>122915163</v>
       </c>
       <c r="B84" t="n">
         <v>78775</v>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480725</v>
+        <v>480988</v>
       </c>
       <c r="R84" t="n">
-        <v>6790756</v>
+        <v>6790673</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9568,7 +9568,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122910695</v>
+        <v>122905837</v>
       </c>
       <c r="B85" t="n">
         <v>78775</v>
@@ -9608,10 +9608,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480801</v>
+        <v>480679</v>
       </c>
       <c r="R85" t="n">
-        <v>6790557</v>
+        <v>6790740</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122916963</v>
+        <v>122907575</v>
       </c>
       <c r="B86" t="n">
         <v>78775</v>
@@ -9706,17 +9706,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481367</v>
+        <v>480571</v>
       </c>
       <c r="R86" t="n">
-        <v>6790497</v>
+        <v>6790798</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9743,14 +9743,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>I området här återkommer garnlaven konstant.</t>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9765,19 +9770,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122911564</v>
+        <v>122907899</v>
       </c>
       <c r="B87" t="n">
         <v>78775</v>
@@ -9813,17 +9818,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481081</v>
+        <v>480754</v>
       </c>
       <c r="R87" t="n">
-        <v>6790749</v>
+        <v>6790590</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9850,19 +9855,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9877,19 +9872,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122907575</v>
+        <v>122905918</v>
       </c>
       <c r="B88" t="n">
         <v>78775</v>
@@ -9925,17 +9920,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480571</v>
+        <v>480680</v>
       </c>
       <c r="R88" t="n">
-        <v>6790798</v>
+        <v>6790718</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9962,19 +9957,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9989,19 +9974,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122907899</v>
+        <v>122909988</v>
       </c>
       <c r="B89" t="n">
         <v>78775</v>
@@ -10041,10 +10026,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480754</v>
+        <v>480725</v>
       </c>
       <c r="R89" t="n">
-        <v>6790590</v>
+        <v>6790756</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10103,7 +10088,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122905918</v>
+        <v>122916963</v>
       </c>
       <c r="B90" t="n">
         <v>78775</v>
@@ -10143,10 +10128,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480680</v>
+        <v>481367</v>
       </c>
       <c r="R90" t="n">
-        <v>6790718</v>
+        <v>6790497</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10179,6 +10164,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>I området här återkommer garnlaven konstant.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10205,7 +10195,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122916316</v>
+        <v>122911564</v>
       </c>
       <c r="B91" t="n">
         <v>78775</v>
@@ -10241,17 +10231,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481273</v>
+        <v>481081</v>
       </c>
       <c r="R91" t="n">
-        <v>6790567</v>
+        <v>6790749</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10278,9 +10268,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10295,22 +10295,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122907844</v>
+        <v>122908690</v>
       </c>
       <c r="B92" t="n">
-        <v>78775</v>
+        <v>78420</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10323,37 +10323,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480744</v>
+        <v>480626</v>
       </c>
       <c r="R92" t="n">
-        <v>6790595</v>
+        <v>6790648</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10380,9 +10380,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10397,22 +10407,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122908163</v>
+        <v>122915025</v>
       </c>
       <c r="B93" t="n">
-        <v>78775</v>
+        <v>56691</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10421,28 +10431,36 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
@@ -10484,7 +10502,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10494,7 +10512,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10521,10 +10539,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122915025</v>
+        <v>122916590</v>
       </c>
       <c r="B94" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10533,46 +10551,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480681</v>
+        <v>481290</v>
       </c>
       <c r="R94" t="n">
-        <v>6790816</v>
+        <v>6790576</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10602,19 +10612,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>16:08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10629,19 +10629,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122916590</v>
+        <v>122913869</v>
       </c>
       <c r="B95" t="n">
         <v>57481</v>
@@ -10675,16 +10675,21 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481290</v>
+        <v>480861</v>
       </c>
       <c r="R95" t="n">
-        <v>6790576</v>
+        <v>6790634</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10743,10 +10748,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122913869</v>
+        <v>122907867</v>
       </c>
       <c r="B96" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10759,39 +10764,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480861</v>
+        <v>480744</v>
       </c>
       <c r="R96" t="n">
-        <v>6790634</v>
+        <v>6790595</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11696,10 +11696,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122908690</v>
+        <v>122908163</v>
       </c>
       <c r="B105" t="n">
-        <v>78420</v>
+        <v>78775</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11712,37 +11712,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480626</v>
+        <v>480681</v>
       </c>
       <c r="R105" t="n">
-        <v>6790648</v>
+        <v>6790816</v>
       </c>
       <c r="S105" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11796,22 +11796,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122908121</v>
+        <v>122908512</v>
       </c>
       <c r="B106" t="n">
-        <v>8441</v>
+        <v>78775</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11820,41 +11820,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480638</v>
+        <v>480749</v>
       </c>
       <c r="R106" t="n">
-        <v>6790738</v>
+        <v>6790500</v>
       </c>
       <c r="S106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11881,19 +11881,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11908,22 +11898,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122908892</v>
+        <v>122908239</v>
       </c>
       <c r="B107" t="n">
-        <v>8441</v>
+        <v>78775</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11932,25 +11922,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11960,10 +11950,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480771</v>
+        <v>480639</v>
       </c>
       <c r="R107" t="n">
-        <v>6790522</v>
+        <v>6790797</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11993,9 +11983,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12010,22 +12010,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122908512</v>
+        <v>122915190</v>
       </c>
       <c r="B108" t="n">
-        <v>78775</v>
+        <v>78511</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12038,37 +12038,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480749</v>
+        <v>480830</v>
       </c>
       <c r="R108" t="n">
-        <v>6790500</v>
+        <v>6790684</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12095,9 +12095,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12112,19 +12122,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122908239</v>
+        <v>122907326</v>
       </c>
       <c r="B109" t="n">
         <v>78775</v>
@@ -12164,10 +12174,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480639</v>
+        <v>480712</v>
       </c>
       <c r="R109" t="n">
-        <v>6790797</v>
+        <v>6790625</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12197,19 +12207,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12224,22 +12224,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122915190</v>
+        <v>122914153</v>
       </c>
       <c r="B110" t="n">
-        <v>78511</v>
+        <v>78775</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12252,37 +12252,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480830</v>
+        <v>480850</v>
       </c>
       <c r="R110" t="n">
-        <v>6790684</v>
+        <v>6790697</v>
       </c>
       <c r="S110" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12309,19 +12309,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>16:19</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12336,19 +12326,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122907326</v>
+        <v>122914846</v>
       </c>
       <c r="B111" t="n">
         <v>78775</v>
@@ -12384,17 +12374,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480712</v>
+        <v>480895</v>
       </c>
       <c r="R111" t="n">
-        <v>6790625</v>
+        <v>6790735</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12421,9 +12411,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12438,19 +12438,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122914153</v>
+        <v>122915451</v>
       </c>
       <c r="B112" t="n">
         <v>78775</v>
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480850</v>
+        <v>481063</v>
       </c>
       <c r="R112" t="n">
-        <v>6790697</v>
+        <v>6790636</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12552,7 +12552,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122914846</v>
+        <v>122908696</v>
       </c>
       <c r="B113" t="n">
         <v>78775</v>
@@ -12592,10 +12592,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480895</v>
+        <v>480701</v>
       </c>
       <c r="R113" t="n">
-        <v>6790735</v>
+        <v>6790532</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12664,7 +12664,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122915451</v>
+        <v>122908130</v>
       </c>
       <c r="B114" t="n">
         <v>78775</v>
@@ -12704,10 +12704,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>481063</v>
+        <v>480763</v>
       </c>
       <c r="R114" t="n">
-        <v>6790636</v>
+        <v>6790548</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12766,7 +12766,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122908696</v>
+        <v>122910124</v>
       </c>
       <c r="B115" t="n">
         <v>78775</v>
@@ -12802,17 +12802,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>480701</v>
+        <v>480730</v>
       </c>
       <c r="R115" t="n">
-        <v>6790532</v>
+        <v>6790750</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12839,19 +12839,9 @@
           <t>2025-03-06</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:25</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12866,22 +12856,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122908130</v>
+        <v>122908121</v>
       </c>
       <c r="B116" t="n">
-        <v>78775</v>
+        <v>8441</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12890,41 +12880,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>480763</v>
+        <v>480638</v>
       </c>
       <c r="R116" t="n">
-        <v>6790548</v>
+        <v>6790738</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12951,9 +12941,19 @@
           <t>2025-03-06</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12968,22 +12968,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122910124</v>
+        <v>122908892</v>
       </c>
       <c r="B117" t="n">
-        <v>78775</v>
+        <v>8441</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12992,25 +12992,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13020,10 +13020,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>480730</v>
+        <v>480771</v>
       </c>
       <c r="R117" t="n">
-        <v>6790750</v>
+        <v>6790522</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -22307,7 +22307,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122975322</v>
+        <v>122968800</v>
       </c>
       <c r="B204" t="n">
         <v>8441</v>
@@ -22343,17 +22343,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>481394</v>
+        <v>481460</v>
       </c>
       <c r="R204" t="n">
-        <v>6790771</v>
+        <v>6790499</v>
       </c>
       <c r="S204" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22380,19 +22380,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>16:31</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22407,22 +22397,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>122968143</v>
+        <v>122975322</v>
       </c>
       <c r="B205" t="n">
-        <v>78775</v>
+        <v>8441</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22431,25 +22421,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22459,10 +22449,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>481374</v>
+        <v>481394</v>
       </c>
       <c r="R205" t="n">
-        <v>6790558</v>
+        <v>6790771</v>
       </c>
       <c r="S205" t="n">
         <v>9</v>
@@ -22494,7 +22484,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22504,7 +22494,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22531,10 +22521,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122968800</v>
+        <v>122968143</v>
       </c>
       <c r="B206" t="n">
-        <v>8441</v>
+        <v>78775</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22543,41 +22533,41 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>481460</v>
+        <v>481374</v>
       </c>
       <c r="R206" t="n">
-        <v>6790499</v>
+        <v>6790558</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22604,9 +22594,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22621,12 +22621,12 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
@@ -25216,7 +25216,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>122962123</v>
+        <v>122968705</v>
       </c>
       <c r="B231" t="n">
         <v>78775</v>
@@ -25252,17 +25252,17 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>480826</v>
+        <v>481441</v>
       </c>
       <c r="R231" t="n">
-        <v>6790638</v>
+        <v>6790542</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -25289,9 +25289,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25306,22 +25316,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>122964451</v>
+        <v>122976204</v>
       </c>
       <c r="B232" t="n">
-        <v>78775</v>
+        <v>57497</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25334,34 +25344,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>481009</v>
+        <v>481461</v>
       </c>
       <c r="R232" t="n">
-        <v>6790709</v>
+        <v>6790683</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25394,6 +25404,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Spill och hackspår efter annan spett, miljöbilder.</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25420,7 +25435,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>122968705</v>
+        <v>122975494</v>
       </c>
       <c r="B233" t="n">
         <v>78775</v>
@@ -25456,17 +25471,17 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
         <v>481441</v>
       </c>
       <c r="R233" t="n">
-        <v>6790542</v>
+        <v>6790760</v>
       </c>
       <c r="S233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -25493,19 +25508,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>13:37</t>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Garn med miljöbild</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25520,19 +25530,19 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>122975494</v>
+        <v>122962123</v>
       </c>
       <c r="B234" t="n">
         <v>78775</v>
@@ -25568,14 +25578,14 @@
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>481441</v>
+        <v>480826</v>
       </c>
       <c r="R234" t="n">
-        <v>6790760</v>
+        <v>6790638</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25608,11 +25618,6 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Garn med miljöbild</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25639,10 +25644,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>122976204</v>
+        <v>122964451</v>
       </c>
       <c r="B235" t="n">
-        <v>57497</v>
+        <v>78775</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25655,34 +25660,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>481461</v>
+        <v>481009</v>
       </c>
       <c r="R235" t="n">
-        <v>6790683</v>
+        <v>6790709</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25715,11 +25720,6 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Spill och hackspår efter annan spett, miljöbilder.</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -27172,10 +27172,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122969848</v>
+        <v>122966180</v>
       </c>
       <c r="B249" t="n">
-        <v>78776</v>
+        <v>78775</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -27188,16 +27188,16 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -27208,17 +27208,17 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>481544</v>
+        <v>481151</v>
       </c>
       <c r="R249" t="n">
-        <v>6790494</v>
+        <v>6790709</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -27245,14 +27245,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27267,19 +27272,19 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122966180</v>
+        <v>122969543</v>
       </c>
       <c r="B250" t="n">
         <v>78775</v>
@@ -27315,17 +27320,17 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>481151</v>
+        <v>481496</v>
       </c>
       <c r="R250" t="n">
-        <v>6790709</v>
+        <v>6790486</v>
       </c>
       <c r="S250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -27352,19 +27357,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -27379,19 +27379,19 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122969543</v>
+        <v>122975021</v>
       </c>
       <c r="B251" t="n">
         <v>78775</v>
@@ -27427,17 +27427,17 @@
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>481496</v>
+        <v>481422</v>
       </c>
       <c r="R251" t="n">
-        <v>6790486</v>
+        <v>6790752</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -27464,14 +27464,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>Miljöbilder och garnlav.</t>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -27486,19 +27496,19 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122975021</v>
+        <v>122961573</v>
       </c>
       <c r="B252" t="n">
         <v>78775</v>
@@ -27534,17 +27544,17 @@
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>481422</v>
+        <v>480767</v>
       </c>
       <c r="R252" t="n">
-        <v>6790752</v>
+        <v>6790685</v>
       </c>
       <c r="S252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -27571,24 +27581,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27603,22 +27598,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122961573</v>
+        <v>122965865</v>
       </c>
       <c r="B253" t="n">
-        <v>78775</v>
+        <v>57497</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -27631,37 +27626,42 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>480767</v>
+        <v>481118</v>
       </c>
       <c r="R253" t="n">
-        <v>6790685</v>
+        <v>6790699</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -27688,9 +27688,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27705,22 +27715,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122965865</v>
+        <v>122969848</v>
       </c>
       <c r="B254" t="n">
-        <v>57497</v>
+        <v>78776</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -27733,42 +27743,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>481118</v>
+        <v>481544</v>
       </c>
       <c r="R254" t="n">
-        <v>6790699</v>
+        <v>6790494</v>
       </c>
       <c r="S254" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -27795,19 +27800,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>12:51</t>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27822,12 +27822,12 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -35853,10 +35853,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122972148</v>
+        <v>122970459</v>
       </c>
       <c r="B328" t="n">
-        <v>78776</v>
+        <v>57497</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -35869,34 +35869,34 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>481755</v>
+        <v>481658</v>
       </c>
       <c r="R328" t="n">
-        <v>6790500</v>
+        <v>6790493</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="AC328" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -35960,10 +35960,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122970459</v>
+        <v>122972148</v>
       </c>
       <c r="B329" t="n">
-        <v>57497</v>
+        <v>78776</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -35976,34 +35976,34 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>481658</v>
+        <v>481755</v>
       </c>
       <c r="R329" t="n">
-        <v>6790493</v>
+        <v>6790500</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>Miljöbilder och spillkråka.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD329" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -20787,10 +20787,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122973404</v>
+        <v>122965792</v>
       </c>
       <c r="B190" t="n">
-        <v>78781</v>
+        <v>8445</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20799,41 +20799,46 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>481525</v>
+        <v>481118</v>
       </c>
       <c r="R190" t="n">
-        <v>6790521</v>
+        <v>6790699</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20860,9 +20865,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20877,19 +20892,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122973297</v>
+        <v>122973404</v>
       </c>
       <c r="B191" t="n">
         <v>78781</v>
@@ -20929,10 +20944,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>481575</v>
+        <v>481525</v>
       </c>
       <c r="R191" t="n">
-        <v>6790530</v>
+        <v>6790521</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20991,7 +21006,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122977930</v>
+        <v>122973297</v>
       </c>
       <c r="B192" t="n">
         <v>78781</v>
@@ -21031,10 +21046,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>481202</v>
+        <v>481575</v>
       </c>
       <c r="R192" t="n">
-        <v>6790769</v>
+        <v>6790530</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21067,11 +21082,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Garn inom synfältet, ca 50 meter i radie.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21098,10 +21108,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122962565</v>
+        <v>122977930</v>
       </c>
       <c r="B193" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21114,37 +21124,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>480854</v>
+        <v>481202</v>
       </c>
       <c r="R193" t="n">
-        <v>6790625</v>
+        <v>6790769</v>
       </c>
       <c r="S193" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21171,19 +21181,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>11:37</t>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Garn inom synfältet, ca 50 meter i radie.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21198,22 +21203,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122965792</v>
+        <v>122962565</v>
       </c>
       <c r="B194" t="n">
-        <v>8445</v>
+        <v>78517</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21222,43 +21227,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>481118</v>
+        <v>480854</v>
       </c>
       <c r="R194" t="n">
-        <v>6790699</v>
+        <v>6790625</v>
       </c>
       <c r="S194" t="n">
         <v>9</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -29258,10 +29258,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122974049</v>
+        <v>122965865</v>
       </c>
       <c r="B268" t="n">
-        <v>56697</v>
+        <v>57503</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -29270,31 +29270,31 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
@@ -29303,10 +29303,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>481427</v>
+        <v>481118</v>
       </c>
       <c r="R268" t="n">
-        <v>6790669</v>
+        <v>6790699</v>
       </c>
       <c r="S268" t="n">
         <v>9</v>
@@ -29338,7 +29338,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -29375,10 +29375,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122960241</v>
+        <v>122974049</v>
       </c>
       <c r="B269" t="n">
-        <v>78781</v>
+        <v>56697</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -29387,41 +29387,46 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>480794</v>
+        <v>481427</v>
       </c>
       <c r="R269" t="n">
-        <v>6790801</v>
+        <v>6790669</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -29448,9 +29453,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29465,19 +29480,19 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122970152</v>
+        <v>122960241</v>
       </c>
       <c r="B270" t="n">
         <v>78781</v>
@@ -29517,10 +29532,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>481577</v>
+        <v>480794</v>
       </c>
       <c r="R270" t="n">
-        <v>6790481</v>
+        <v>6790801</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -29579,7 +29594,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122965035</v>
+        <v>122970152</v>
       </c>
       <c r="B271" t="n">
         <v>78781</v>
@@ -29615,17 +29630,17 @@
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>481031</v>
+        <v>481577</v>
       </c>
       <c r="R271" t="n">
-        <v>6790714</v>
+        <v>6790481</v>
       </c>
       <c r="S271" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -29652,19 +29667,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29679,19 +29684,19 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122959766</v>
+        <v>122965035</v>
       </c>
       <c r="B272" t="n">
         <v>78781</v>
@@ -29731,10 +29736,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>480779</v>
+        <v>481031</v>
       </c>
       <c r="R272" t="n">
-        <v>6790803</v>
+        <v>6790714</v>
       </c>
       <c r="S272" t="n">
         <v>9</v>
@@ -29766,7 +29771,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -29776,7 +29781,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29803,10 +29808,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122965865</v>
+        <v>122959766</v>
       </c>
       <c r="B273" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -29819,39 +29824,34 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>481118</v>
+        <v>480779</v>
       </c>
       <c r="R273" t="n">
-        <v>6790699</v>
+        <v>6790803</v>
       </c>
       <c r="S273" t="n">
         <v>9</v>
@@ -29883,7 +29883,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD273" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -20787,10 +20787,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122965792</v>
+        <v>122973404</v>
       </c>
       <c r="B190" t="n">
-        <v>8445</v>
+        <v>78781</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20799,46 +20799,41 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>481118</v>
+        <v>481525</v>
       </c>
       <c r="R190" t="n">
-        <v>6790699</v>
+        <v>6790521</v>
       </c>
       <c r="S190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20865,19 +20860,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20892,19 +20877,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122973404</v>
+        <v>122973297</v>
       </c>
       <c r="B191" t="n">
         <v>78781</v>
@@ -20944,10 +20929,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>481525</v>
+        <v>481575</v>
       </c>
       <c r="R191" t="n">
-        <v>6790521</v>
+        <v>6790530</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21006,7 +20991,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122973297</v>
+        <v>122977930</v>
       </c>
       <c r="B192" t="n">
         <v>78781</v>
@@ -21046,10 +21031,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>481575</v>
+        <v>481202</v>
       </c>
       <c r="R192" t="n">
-        <v>6790530</v>
+        <v>6790769</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21082,6 +21067,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Garn inom synfältet, ca 50 meter i radie.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21108,10 +21098,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122977930</v>
+        <v>122962565</v>
       </c>
       <c r="B193" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21124,37 +21114,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>481202</v>
+        <v>480854</v>
       </c>
       <c r="R193" t="n">
-        <v>6790769</v>
+        <v>6790625</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21181,14 +21171,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Garn inom synfältet, ca 50 meter i radie.</t>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21203,22 +21198,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122962565</v>
+        <v>122965792</v>
       </c>
       <c r="B194" t="n">
-        <v>78517</v>
+        <v>8445</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21227,38 +21222,43 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>480854</v>
+        <v>481118</v>
       </c>
       <c r="R194" t="n">
-        <v>6790625</v>
+        <v>6790699</v>
       </c>
       <c r="S194" t="n">
         <v>9</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25784,10 +25784,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>122969848</v>
+        <v>122975234</v>
       </c>
       <c r="B236" t="n">
-        <v>78782</v>
+        <v>57503</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25800,34 +25800,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>481544</v>
+        <v>481459</v>
       </c>
       <c r="R236" t="n">
-        <v>6790494</v>
+        <v>6790740</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25860,11 +25860,6 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26996,10 +26991,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>122975234</v>
+        <v>122969848</v>
       </c>
       <c r="B247" t="n">
-        <v>57503</v>
+        <v>78782</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27012,34 +27007,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>481459</v>
+        <v>481544</v>
       </c>
       <c r="R247" t="n">
-        <v>6790740</v>
+        <v>6790494</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27072,6 +27067,11 @@
       <c r="AA247" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27098,10 +27098,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>122967764</v>
+        <v>122968800</v>
       </c>
       <c r="B248" t="n">
-        <v>78781</v>
+        <v>8445</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -27110,41 +27110,41 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>481304</v>
+        <v>481460</v>
       </c>
       <c r="R248" t="n">
-        <v>6790615</v>
+        <v>6790499</v>
       </c>
       <c r="S248" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -27171,19 +27171,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -27198,19 +27188,19 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>122978156</v>
+        <v>122967764</v>
       </c>
       <c r="B249" t="n">
         <v>78781</v>
@@ -27246,17 +27236,17 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>481151</v>
+        <v>481304</v>
       </c>
       <c r="R249" t="n">
-        <v>6790744</v>
+        <v>6790615</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -27283,14 +27273,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Garn synligt i radie 50 meter.</t>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -27305,19 +27300,19 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>122965760</v>
+        <v>122978156</v>
       </c>
       <c r="B250" t="n">
         <v>78781</v>
@@ -27353,17 +27348,17 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>481118</v>
+        <v>481151</v>
       </c>
       <c r="R250" t="n">
-        <v>6790699</v>
+        <v>6790744</v>
       </c>
       <c r="S250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -27390,19 +27385,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>12:49</t>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Garn synligt i radie 50 meter.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -27417,19 +27407,19 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>122968724</v>
+        <v>122965760</v>
       </c>
       <c r="B251" t="n">
         <v>78781</v>
@@ -27469,10 +27459,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>481443</v>
+        <v>481118</v>
       </c>
       <c r="R251" t="n">
-        <v>6790544</v>
+        <v>6790699</v>
       </c>
       <c r="S251" t="n">
         <v>9</v>
@@ -27504,7 +27494,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -27514,7 +27504,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -27541,7 +27531,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122968760</v>
+        <v>122968724</v>
       </c>
       <c r="B252" t="n">
         <v>78781</v>
@@ -27581,7 +27571,7 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>481444</v>
+        <v>481443</v>
       </c>
       <c r="R252" t="n">
         <v>6790544</v>
@@ -27616,7 +27606,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -27626,7 +27616,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27653,7 +27643,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122960001</v>
+        <v>122968760</v>
       </c>
       <c r="B253" t="n">
         <v>78781</v>
@@ -27689,17 +27679,17 @@
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>480805</v>
+        <v>481444</v>
       </c>
       <c r="R253" t="n">
-        <v>6790809</v>
+        <v>6790544</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -27726,9 +27716,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27743,19 +27743,19 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>122976875</v>
+        <v>122960001</v>
       </c>
       <c r="B254" t="n">
         <v>78781</v>
@@ -27791,14 +27791,14 @@
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>481334</v>
+        <v>480805</v>
       </c>
       <c r="R254" t="n">
-        <v>6790765</v>
+        <v>6790809</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27831,11 +27831,6 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Garnlav överallt i en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27862,7 +27857,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>122960352</v>
+        <v>122976875</v>
       </c>
       <c r="B255" t="n">
         <v>78781</v>
@@ -27898,14 +27893,14 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>480778</v>
+        <v>481334</v>
       </c>
       <c r="R255" t="n">
-        <v>6790784</v>
+        <v>6790765</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27938,6 +27933,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Garnlav överallt i en radie av 50 meter.</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27964,7 +27964,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>122973309</v>
+        <v>122960352</v>
       </c>
       <c r="B256" t="n">
         <v>78781</v>
@@ -28000,17 +28000,17 @@
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>481568</v>
+        <v>480778</v>
       </c>
       <c r="R256" t="n">
-        <v>6790545</v>
+        <v>6790784</v>
       </c>
       <c r="S256" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -28037,19 +28037,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -28064,19 +28054,19 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>122962209</v>
+        <v>122973309</v>
       </c>
       <c r="B257" t="n">
         <v>78781</v>
@@ -28112,17 +28102,17 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>480818</v>
+        <v>481568</v>
       </c>
       <c r="R257" t="n">
-        <v>6790633</v>
+        <v>6790545</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -28149,9 +28139,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -28166,22 +28166,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122968800</v>
+        <v>122962209</v>
       </c>
       <c r="B258" t="n">
-        <v>8445</v>
+        <v>78781</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -28190,25 +28190,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -28218,10 +28218,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>481460</v>
+        <v>480818</v>
       </c>
       <c r="R258" t="n">
-        <v>6790499</v>
+        <v>6790633</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28280,10 +28280,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>122968198</v>
+        <v>122968666</v>
       </c>
       <c r="B259" t="n">
-        <v>8445</v>
+        <v>78781</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -28292,43 +28292,38 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>481373</v>
+        <v>481436</v>
       </c>
       <c r="R259" t="n">
-        <v>6790551</v>
+        <v>6790540</v>
       </c>
       <c r="S259" t="n">
         <v>9</v>
@@ -28360,7 +28355,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -28370,7 +28365,12 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -28397,7 +28397,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>122968666</v>
+        <v>122961613</v>
       </c>
       <c r="B260" t="n">
         <v>78781</v>
@@ -28433,17 +28433,17 @@
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>481436</v>
+        <v>480767</v>
       </c>
       <c r="R260" t="n">
-        <v>6790540</v>
+        <v>6790673</v>
       </c>
       <c r="S260" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -28470,24 +28470,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -28502,19 +28487,19 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>122961613</v>
+        <v>122970196</v>
       </c>
       <c r="B261" t="n">
         <v>78781</v>
@@ -28554,10 +28539,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>480767</v>
+        <v>481598</v>
       </c>
       <c r="R261" t="n">
-        <v>6790673</v>
+        <v>6790481</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -28616,7 +28601,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122970196</v>
+        <v>122968705</v>
       </c>
       <c r="B262" t="n">
         <v>78781</v>
@@ -28652,17 +28637,17 @@
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>481598</v>
+        <v>481441</v>
       </c>
       <c r="R262" t="n">
-        <v>6790481</v>
+        <v>6790542</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -28689,9 +28674,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28706,19 +28701,19 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122968705</v>
+        <v>122962123</v>
       </c>
       <c r="B263" t="n">
         <v>78781</v>
@@ -28754,17 +28749,17 @@
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>481441</v>
+        <v>480826</v>
       </c>
       <c r="R263" t="n">
-        <v>6790542</v>
+        <v>6790638</v>
       </c>
       <c r="S263" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -28791,19 +28786,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28818,19 +28803,19 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>122962123</v>
+        <v>122970156</v>
       </c>
       <c r="B264" t="n">
         <v>78781</v>
@@ -28866,17 +28851,17 @@
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>480826</v>
+        <v>481546</v>
       </c>
       <c r="R264" t="n">
-        <v>6790638</v>
+        <v>6790501</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -28903,9 +28888,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28920,19 +28915,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>122970156</v>
+        <v>122975072</v>
       </c>
       <c r="B265" t="n">
         <v>78781</v>
@@ -28968,17 +28963,17 @@
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>481546</v>
+        <v>481455</v>
       </c>
       <c r="R265" t="n">
-        <v>6790501</v>
+        <v>6790712</v>
       </c>
       <c r="S265" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -29005,19 +29000,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>14:08</t>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Garnlav och miljöbild.</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -29032,22 +29022,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122975072</v>
+        <v>122976204</v>
       </c>
       <c r="B266" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -29060,21 +29050,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -29084,10 +29074,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>481455</v>
+        <v>481461</v>
       </c>
       <c r="R266" t="n">
-        <v>6790712</v>
+        <v>6790683</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29124,7 +29114,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>Garnlav och miljöbild.</t>
+          <t>Spill och hackspår efter annan spett, miljöbilder.</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -29151,10 +29141,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122976204</v>
+        <v>122968198</v>
       </c>
       <c r="B267" t="n">
-        <v>57503</v>
+        <v>8445</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -29163,41 +29153,46 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>481461</v>
+        <v>481373</v>
       </c>
       <c r="R267" t="n">
-        <v>6790683</v>
+        <v>6790551</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -29224,14 +29219,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Spill och hackspår efter annan spett, miljöbilder.</t>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -29246,22 +29246,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122965865</v>
+        <v>122974049</v>
       </c>
       <c r="B268" t="n">
-        <v>57503</v>
+        <v>56697</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -29270,31 +29270,31 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
@@ -29303,10 +29303,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>481118</v>
+        <v>481427</v>
       </c>
       <c r="R268" t="n">
-        <v>6790699</v>
+        <v>6790669</v>
       </c>
       <c r="S268" t="n">
         <v>9</v>
@@ -29338,7 +29338,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -29375,10 +29375,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122974049</v>
+        <v>122960241</v>
       </c>
       <c r="B269" t="n">
-        <v>56697</v>
+        <v>78781</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -29387,46 +29387,41 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>481427</v>
+        <v>480794</v>
       </c>
       <c r="R269" t="n">
-        <v>6790669</v>
+        <v>6790801</v>
       </c>
       <c r="S269" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -29453,19 +29448,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29480,19 +29465,19 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122960241</v>
+        <v>122970152</v>
       </c>
       <c r="B270" t="n">
         <v>78781</v>
@@ -29532,10 +29517,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>480794</v>
+        <v>481577</v>
       </c>
       <c r="R270" t="n">
-        <v>6790801</v>
+        <v>6790481</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -29594,7 +29579,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122970152</v>
+        <v>122965035</v>
       </c>
       <c r="B271" t="n">
         <v>78781</v>
@@ -29630,17 +29615,17 @@
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>481577</v>
+        <v>481031</v>
       </c>
       <c r="R271" t="n">
-        <v>6790481</v>
+        <v>6790714</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -29667,9 +29652,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29684,19 +29679,19 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122965035</v>
+        <v>122959766</v>
       </c>
       <c r="B272" t="n">
         <v>78781</v>
@@ -29736,10 +29731,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>481031</v>
+        <v>480779</v>
       </c>
       <c r="R272" t="n">
-        <v>6790714</v>
+        <v>6790803</v>
       </c>
       <c r="S272" t="n">
         <v>9</v>
@@ -29771,7 +29766,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -29781,7 +29776,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29808,10 +29803,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122959766</v>
+        <v>122965865</v>
       </c>
       <c r="B273" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -29824,34 +29819,39 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>480779</v>
+        <v>481118</v>
       </c>
       <c r="R273" t="n">
-        <v>6790803</v>
+        <v>6790699</v>
       </c>
       <c r="S273" t="n">
         <v>9</v>
@@ -29883,7 +29883,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -33521,10 +33521,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122975526</v>
+        <v>122978194</v>
       </c>
       <c r="B307" t="n">
-        <v>78781</v>
+        <v>56697</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -33533,41 +33533,46 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>481420</v>
+        <v>481090</v>
       </c>
       <c r="R307" t="n">
-        <v>6790760</v>
+        <v>6790709</v>
       </c>
       <c r="S307" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -33594,9 +33599,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
       <c r="AA307" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33611,19 +33626,19 @@
       <c r="AT307" t="inlineStr"/>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122969836</v>
+        <v>122975526</v>
       </c>
       <c r="B308" t="n">
         <v>78781</v>
@@ -33659,17 +33674,17 @@
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>481538</v>
+        <v>481420</v>
       </c>
       <c r="R308" t="n">
-        <v>6790506</v>
+        <v>6790760</v>
       </c>
       <c r="S308" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -33696,19 +33711,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33723,19 +33728,19 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122976633</v>
+        <v>122969836</v>
       </c>
       <c r="B309" t="n">
         <v>78781</v>
@@ -33775,10 +33780,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>481342</v>
+        <v>481538</v>
       </c>
       <c r="R309" t="n">
-        <v>6790727</v>
+        <v>6790506</v>
       </c>
       <c r="S309" t="n">
         <v>9</v>
@@ -33810,7 +33815,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -33820,7 +33825,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33847,7 +33852,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122967445</v>
+        <v>122976633</v>
       </c>
       <c r="B310" t="n">
         <v>78781</v>
@@ -33887,10 +33892,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>481249</v>
+        <v>481342</v>
       </c>
       <c r="R310" t="n">
-        <v>6790669</v>
+        <v>6790727</v>
       </c>
       <c r="S310" t="n">
         <v>9</v>
@@ -33922,7 +33927,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -33932,7 +33937,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33959,10 +33964,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122978194</v>
+        <v>122967445</v>
       </c>
       <c r="B311" t="n">
-        <v>56697</v>
+        <v>78781</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -33971,43 +33976,38 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P311" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>481090</v>
+        <v>481249</v>
       </c>
       <c r="R311" t="n">
-        <v>6790709</v>
+        <v>6790669</v>
       </c>
       <c r="S311" t="n">
         <v>9</v>
@@ -34039,7 +34039,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD311" t="b">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -34789,7 +34789,7 @@
         <v>122899580</v>
       </c>
       <c r="B318" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -34888,10 +34888,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>123158710</v>
+        <v>123166625</v>
       </c>
       <c r="B319" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -34928,10 +34928,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>480558</v>
+        <v>480411</v>
       </c>
       <c r="R319" t="n">
-        <v>6790583</v>
+        <v>6790807</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -34990,10 +34990,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>123166625</v>
+        <v>123158710</v>
       </c>
       <c r="B320" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -35030,10 +35030,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>480411</v>
+        <v>480558</v>
       </c>
       <c r="R320" t="n">
-        <v>6790807</v>
+        <v>6790583</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -35095,7 +35095,7 @@
         <v>123158872</v>
       </c>
       <c r="B321" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -34888,10 +34888,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>123166625</v>
+        <v>123158710</v>
       </c>
       <c r="B319" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -34928,10 +34928,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>480411</v>
+        <v>480558</v>
       </c>
       <c r="R319" t="n">
-        <v>6790807</v>
+        <v>6790583</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -34990,10 +34990,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>123158710</v>
+        <v>123166625</v>
       </c>
       <c r="B320" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -35030,10 +35030,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>480558</v>
+        <v>480411</v>
       </c>
       <c r="R320" t="n">
-        <v>6790583</v>
+        <v>6790807</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -35095,7 +35095,7 @@
         <v>123158872</v>
       </c>
       <c r="B321" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY331"/>
+  <dimension ref="A1:AY336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35199,50 +35199,49 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122970459</v>
+        <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92794</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I322" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>481658</v>
+        <v>481063</v>
       </c>
       <c r="R322" t="n">
-        <v>6790493</v>
+        <v>6790747</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -35269,17 +35268,22 @@
       </c>
       <c r="Y322" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -35306,15 +35310,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122972025</v>
+        <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92794</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35322,42 +35321,41 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>481687</v>
+        <v>481294</v>
       </c>
       <c r="R323" t="n">
-        <v>6790643</v>
+        <v>6790587</v>
       </c>
       <c r="S323" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -35381,22 +35379,22 @@
       </c>
       <c r="Y323" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -35411,62 +35409,62 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122971698</v>
+        <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58146</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P324" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>481661</v>
+        <v>481294</v>
       </c>
       <c r="R324" t="n">
-        <v>6790503</v>
+        <v>6790587</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -35493,12 +35491,22 @@
       </c>
       <c r="Y324" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -35525,53 +35533,53 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122972089</v>
+        <v>128914529</v>
       </c>
       <c r="B325" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58086</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>481695</v>
+        <v>481260</v>
       </c>
       <c r="R325" t="n">
-        <v>6790593</v>
+        <v>6790667</v>
       </c>
       <c r="S325" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -35595,22 +35603,22 @@
       </c>
       <c r="Y325" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -35625,27 +35633,22 @@
       <c r="AT325" t="inlineStr"/>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122971852</v>
+        <v>128914416</v>
       </c>
       <c r="B326" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58086</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35653,42 +35656,42 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="M326" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>481678</v>
+        <v>481299</v>
       </c>
       <c r="R326" t="n">
-        <v>6790570</v>
+        <v>6790650</v>
       </c>
       <c r="S326" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -35712,22 +35715,22 @@
       </c>
       <c r="Y326" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -35742,22 +35745,22 @@
       <c r="AT326" t="inlineStr"/>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122972843</v>
+        <v>122970459</v>
       </c>
       <c r="B327" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -35770,34 +35773,34 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>481748</v>
+        <v>481658</v>
       </c>
       <c r="R327" t="n">
-        <v>6790465</v>
+        <v>6790493</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -35830,6 +35833,11 @@
       <c r="AA327" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -35856,10 +35864,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122971431</v>
+        <v>122972025</v>
       </c>
       <c r="B328" t="n">
-        <v>78517</v>
+        <v>8445</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -35868,38 +35876,43 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P328" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>481658</v>
+        <v>481687</v>
       </c>
       <c r="R328" t="n">
-        <v>6790494</v>
+        <v>6790643</v>
       </c>
       <c r="S328" t="n">
         <v>9</v>
@@ -35931,7 +35944,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -35941,7 +35954,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -35968,7 +35981,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122973048</v>
+        <v>122971698</v>
       </c>
       <c r="B329" t="n">
         <v>8445</v>
@@ -36004,14 +36017,14 @@
       <c r="I329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>481694</v>
+        <v>481661</v>
       </c>
       <c r="R329" t="n">
-        <v>6790479</v>
+        <v>6790503</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36044,11 +36057,6 @@
       <c r="AA329" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC329" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -36075,10 +36083,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122972148</v>
+        <v>122972089</v>
       </c>
       <c r="B330" t="n">
-        <v>78782</v>
+        <v>78781</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -36091,16 +36099,16 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -36111,17 +36119,17 @@
       <c r="I330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>481755</v>
+        <v>481695</v>
       </c>
       <c r="R330" t="n">
-        <v>6790500</v>
+        <v>6790593</v>
       </c>
       <c r="S330" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -36148,14 +36156,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA330" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC330" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -36170,22 +36183,22 @@
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122971770</v>
+        <v>122971852</v>
       </c>
       <c r="B331" t="n">
-        <v>78805</v>
+        <v>8445</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -36198,34 +36211,39 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P331" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>481677</v>
+        <v>481678</v>
       </c>
       <c r="R331" t="n">
-        <v>6790565</v>
+        <v>6790570</v>
       </c>
       <c r="S331" t="n">
         <v>9</v>
@@ -36257,7 +36275,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -36267,7 +36285,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -36291,6 +36309,546 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>122972843</v>
+      </c>
+      <c r="B332" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr"/>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>481748</v>
+      </c>
+      <c r="R332" t="n">
+        <v>6790465</v>
+      </c>
+      <c r="S332" t="n">
+        <v>10</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG332" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT332" t="inlineStr"/>
+      <c r="AW332" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>122971431</v>
+      </c>
+      <c r="B333" t="n">
+        <v>78517</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr"/>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>481658</v>
+      </c>
+      <c r="R333" t="n">
+        <v>6790494</v>
+      </c>
+      <c r="S333" t="n">
+        <v>9</v>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG333" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT333" t="inlineStr"/>
+      <c r="AW333" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX333" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>122973048</v>
+      </c>
+      <c r="B334" t="n">
+        <v>8445</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr"/>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q334" t="n">
+        <v>481694</v>
+      </c>
+      <c r="R334" t="n">
+        <v>6790479</v>
+      </c>
+      <c r="S334" t="n">
+        <v>10</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
+        </is>
+      </c>
+      <c r="AD334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG334" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT334" t="inlineStr"/>
+      <c r="AW334" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>122972148</v>
+      </c>
+      <c r="B335" t="n">
+        <v>78782</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr"/>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q335" t="n">
+        <v>481755</v>
+      </c>
+      <c r="R335" t="n">
+        <v>6790500</v>
+      </c>
+      <c r="S335" t="n">
+        <v>10</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
+        </is>
+      </c>
+      <c r="AD335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG335" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT335" t="inlineStr"/>
+      <c r="AW335" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX335" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>122971770</v>
+      </c>
+      <c r="B336" t="n">
+        <v>78805</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr"/>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q336" t="n">
+        <v>481677</v>
+      </c>
+      <c r="R336" t="n">
+        <v>6790565</v>
+      </c>
+      <c r="S336" t="n">
+        <v>9</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG336" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT336" t="inlineStr"/>
+      <c r="AW336" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX336" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY336" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY336"/>
+  <dimension ref="A1:AY340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35757,50 +35757,48 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122970459</v>
+        <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92794</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>481658</v>
+        <v>480990</v>
       </c>
       <c r="R327" t="n">
-        <v>6790493</v>
+        <v>6790657</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -35827,17 +35825,12 @@
       </c>
       <c r="Y327" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -35846,33 +35839,29 @@
       <c r="AE327" t="b">
         <v>0</v>
       </c>
+      <c r="AF327" t="inlineStr"/>
       <c r="AG327" t="b">
         <v>0</v>
       </c>
       <c r="AT327" t="inlineStr"/>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122972025</v>
+        <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92794</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35880,42 +35869,40 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>481687</v>
+        <v>480801</v>
       </c>
       <c r="R328" t="n">
-        <v>6790643</v>
+        <v>6790622</v>
       </c>
       <c r="S328" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -35939,22 +35926,12 @@
       </c>
       <c r="Y328" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB328" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -35963,68 +35940,67 @@
       <c r="AE328" t="b">
         <v>0</v>
       </c>
+      <c r="AF328" t="inlineStr"/>
       <c r="AG328" t="b">
         <v>0</v>
       </c>
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122971698</v>
+        <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79152</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>481661</v>
+        <v>481262</v>
       </c>
       <c r="R329" t="n">
-        <v>6790503</v>
+        <v>6790658</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36051,12 +36027,17 @@
       </c>
       <c r="Y329" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -36065,33 +36046,29 @@
       <c r="AE329" t="b">
         <v>0</v>
       </c>
+      <c r="AF329" t="inlineStr"/>
       <c r="AG329" t="b">
         <v>0</v>
       </c>
       <c r="AT329" t="inlineStr"/>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122972089</v>
+        <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79152</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -36099,37 +36076,40 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>481695</v>
+        <v>481058</v>
       </c>
       <c r="R330" t="n">
-        <v>6790593</v>
+        <v>6790686</v>
       </c>
       <c r="S330" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -36153,22 +36133,17 @@
       </c>
       <c r="Y330" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -36177,28 +36152,29 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
+      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122971852</v>
+        <v>122970459</v>
       </c>
       <c r="B331" t="n">
-        <v>8445</v>
+        <v>57503</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -36207,46 +36183,41 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>481678</v>
+        <v>481658</v>
       </c>
       <c r="R331" t="n">
-        <v>6790570</v>
+        <v>6790493</v>
       </c>
       <c r="S331" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -36273,19 +36244,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA331" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB331" t="inlineStr">
-        <is>
-          <t>14:56</t>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -36300,22 +36266,22 @@
       <c r="AT331" t="inlineStr"/>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122972843</v>
+        <v>122972025</v>
       </c>
       <c r="B332" t="n">
-        <v>78781</v>
+        <v>8445</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -36324,41 +36290,46 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>481748</v>
+        <v>481687</v>
       </c>
       <c r="R332" t="n">
-        <v>6790465</v>
+        <v>6790643</v>
       </c>
       <c r="S332" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -36385,9 +36356,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA332" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -36402,22 +36383,22 @@
       <c r="AT332" t="inlineStr"/>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122971431</v>
+        <v>122971698</v>
       </c>
       <c r="B333" t="n">
-        <v>78517</v>
+        <v>8445</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -36426,41 +36407,41 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>481658</v>
+        <v>481661</v>
       </c>
       <c r="R333" t="n">
-        <v>6790494</v>
+        <v>6790503</v>
       </c>
       <c r="S333" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -36487,19 +36468,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA333" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB333" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -36514,22 +36485,22 @@
       <c r="AT333" t="inlineStr"/>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122973048</v>
+        <v>122972089</v>
       </c>
       <c r="B334" t="n">
-        <v>8445</v>
+        <v>78781</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -36538,41 +36509,41 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>481694</v>
+        <v>481695</v>
       </c>
       <c r="R334" t="n">
-        <v>6790479</v>
+        <v>6790593</v>
       </c>
       <c r="S334" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -36599,14 +36570,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA334" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -36621,22 +36597,22 @@
       <c r="AT334" t="inlineStr"/>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122972148</v>
+        <v>122971852</v>
       </c>
       <c r="B335" t="n">
-        <v>78782</v>
+        <v>8445</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -36645,41 +36621,46 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>481755</v>
+        <v>481678</v>
       </c>
       <c r="R335" t="n">
-        <v>6790500</v>
+        <v>6790570</v>
       </c>
       <c r="S335" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -36706,14 +36687,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA335" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -36728,22 +36714,22 @@
       <c r="AT335" t="inlineStr"/>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122971770</v>
+        <v>122972843</v>
       </c>
       <c r="B336" t="n">
-        <v>78805</v>
+        <v>78781</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -36752,41 +36738,41 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>481677</v>
+        <v>481748</v>
       </c>
       <c r="R336" t="n">
-        <v>6790565</v>
+        <v>6790465</v>
       </c>
       <c r="S336" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -36813,19 +36799,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z336" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB336" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -36840,15 +36816,453 @@
       <c r="AT336" t="inlineStr"/>
       <c r="AW336" t="inlineStr">
         <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX336" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>122971431</v>
+      </c>
+      <c r="B337" t="n">
+        <v>78517</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr"/>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q337" t="n">
+        <v>481658</v>
+      </c>
+      <c r="R337" t="n">
+        <v>6790494</v>
+      </c>
+      <c r="S337" t="n">
+        <v>9</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG337" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT337" t="inlineStr"/>
+      <c r="AW337" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX336" t="inlineStr">
+      <c r="AX337" t="inlineStr">
         <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY336" t="inlineStr"/>
+      <c r="AY337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>122973048</v>
+      </c>
+      <c r="B338" t="n">
+        <v>8445</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q338" t="n">
+        <v>481694</v>
+      </c>
+      <c r="R338" t="n">
+        <v>6790479</v>
+      </c>
+      <c r="S338" t="n">
+        <v>10</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
+        </is>
+      </c>
+      <c r="AD338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG338" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT338" t="inlineStr"/>
+      <c r="AW338" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX338" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>122972148</v>
+      </c>
+      <c r="B339" t="n">
+        <v>78782</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr"/>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>481755</v>
+      </c>
+      <c r="R339" t="n">
+        <v>6790500</v>
+      </c>
+      <c r="S339" t="n">
+        <v>10</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
+        </is>
+      </c>
+      <c r="AD339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT339" t="inlineStr"/>
+      <c r="AW339" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX339" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>122971770</v>
+      </c>
+      <c r="B340" t="n">
+        <v>78805</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr"/>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>481677</v>
+      </c>
+      <c r="R340" t="n">
+        <v>6790565</v>
+      </c>
+      <c r="S340" t="n">
+        <v>9</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG340" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT340" t="inlineStr"/>
+      <c r="AW340" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY340" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>58146</v>
+        <v>58150</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>128914529</v>
       </c>
       <c r="B325" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>128914416</v>
       </c>
       <c r="B326" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>58150</v>
+        <v>58153</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>128914529</v>
       </c>
       <c r="B325" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>128914416</v>
       </c>
       <c r="B326" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35310,38 +35310,37 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>128914266</v>
+        <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>58153</v>
+        <v>92816</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -35422,37 +35421,38 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>128914354</v>
+        <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>92811</v>
+        <v>58153</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>58153</v>
+        <v>58155</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>128914529</v>
       </c>
       <c r="B325" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>128914416</v>
       </c>
       <c r="B326" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35310,37 +35310,38 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>128914354</v>
+        <v>128914266</v>
       </c>
       <c r="B323" t="n">
-        <v>92826</v>
+        <v>58155</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -35421,38 +35422,37 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>128914266</v>
+        <v>128914354</v>
       </c>
       <c r="B324" t="n">
-        <v>58155</v>
+        <v>92833</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr"/>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35310,38 +35310,37 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>128914266</v>
+        <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>58155</v>
+        <v>92835</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -35422,37 +35421,38 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>128914354</v>
+        <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>92833</v>
+        <v>58157</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -35536,7 +35536,7 @@
         <v>128914529</v>
       </c>
       <c r="B325" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>128914416</v>
       </c>
       <c r="B326" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35310,37 +35310,38 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>128914354</v>
+        <v>128914266</v>
       </c>
       <c r="B323" t="n">
-        <v>92835</v>
+        <v>58157</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -35421,38 +35422,37 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>128914266</v>
+        <v>128914354</v>
       </c>
       <c r="B324" t="n">
-        <v>58157</v>
+        <v>92835</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr"/>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35310,38 +35310,37 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>128914266</v>
+        <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>58157</v>
+        <v>92821</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -35422,37 +35421,38 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>128914354</v>
+        <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>92835</v>
+        <v>58157</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35310,37 +35310,38 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>128914354</v>
+        <v>128914266</v>
       </c>
       <c r="B323" t="n">
-        <v>92822</v>
+        <v>58157</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -35421,38 +35422,37 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>128914266</v>
+        <v>128914354</v>
       </c>
       <c r="B324" t="n">
-        <v>58157</v>
+        <v>92822</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr"/>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35310,38 +35310,37 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>128914266</v>
+        <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>58157</v>
+        <v>92825</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -35422,37 +35421,38 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>128914354</v>
+        <v>128914266</v>
       </c>
       <c r="B324" t="n">
-        <v>92822</v>
+        <v>58157</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>128930987</v>
       </c>
       <c r="B329" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>128930986</v>
       </c>
       <c r="B330" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35202,7 +35202,7 @@
         <v>128914862</v>
       </c>
       <c r="B322" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>128914354</v>
       </c>
       <c r="B323" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -35760,7 +35760,7 @@
         <v>128930934</v>
       </c>
       <c r="B327" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>128930932</v>
       </c>
       <c r="B328" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY340"/>
+  <dimension ref="A1:AY341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31085,12 +31085,7 @@
         <v>122974755</v>
       </c>
       <c r="B285" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31116,16 +31111,19 @@
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>481461</v>
+        <v>481463</v>
       </c>
       <c r="R285" t="n">
-        <v>6790683</v>
+        <v>6790665</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -31171,6 +31169,7 @@
       <c r="AE285" t="b">
         <v>0</v>
       </c>
+      <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
@@ -36171,15 +36170,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122970459</v>
+        <v>129963367</v>
       </c>
       <c r="B331" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57734</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -36205,16 +36199,24 @@
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>481658</v>
+        <v>481463</v>
       </c>
       <c r="R331" t="n">
-        <v>6790493</v>
+        <v>6790702</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -36247,11 +36249,6 @@
       <c r="AA331" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC331" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -36278,10 +36275,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122972025</v>
+        <v>122970459</v>
       </c>
       <c r="B332" t="n">
-        <v>8445</v>
+        <v>57503</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -36290,46 +36287,41 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>481687</v>
+        <v>481658</v>
       </c>
       <c r="R332" t="n">
-        <v>6790643</v>
+        <v>6790493</v>
       </c>
       <c r="S332" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -36356,19 +36348,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA332" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB332" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -36383,19 +36370,19 @@
       <c r="AT332" t="inlineStr"/>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122971698</v>
+        <v>122972025</v>
       </c>
       <c r="B333" t="n">
         <v>8445</v>
@@ -36429,19 +36416,24 @@
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>481661</v>
+        <v>481687</v>
       </c>
       <c r="R333" t="n">
-        <v>6790503</v>
+        <v>6790643</v>
       </c>
       <c r="S333" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -36468,9 +36460,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA333" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -36485,22 +36487,22 @@
       <c r="AT333" t="inlineStr"/>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122972089</v>
+        <v>122971698</v>
       </c>
       <c r="B334" t="n">
-        <v>78781</v>
+        <v>8445</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -36509,41 +36511,41 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>481695</v>
+        <v>481661</v>
       </c>
       <c r="R334" t="n">
-        <v>6790593</v>
+        <v>6790503</v>
       </c>
       <c r="S334" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -36570,19 +36572,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA334" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -36597,22 +36589,22 @@
       <c r="AT334" t="inlineStr"/>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122971852</v>
+        <v>122972089</v>
       </c>
       <c r="B335" t="n">
-        <v>8445</v>
+        <v>78781</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -36621,43 +36613,38 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P335" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>481678</v>
+        <v>481695</v>
       </c>
       <c r="R335" t="n">
-        <v>6790570</v>
+        <v>6790593</v>
       </c>
       <c r="S335" t="n">
         <v>9</v>
@@ -36689,7 +36676,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -36699,7 +36686,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -36726,10 +36713,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122972843</v>
+        <v>122971852</v>
       </c>
       <c r="B336" t="n">
-        <v>78781</v>
+        <v>8445</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -36738,41 +36725,46 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>481748</v>
+        <v>481678</v>
       </c>
       <c r="R336" t="n">
-        <v>6790465</v>
+        <v>6790570</v>
       </c>
       <c r="S336" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -36799,9 +36791,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -36816,22 +36818,22 @@
       <c r="AT336" t="inlineStr"/>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122971431</v>
+        <v>122972843</v>
       </c>
       <c r="B337" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -36844,37 +36846,37 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>481658</v>
+        <v>481748</v>
       </c>
       <c r="R337" t="n">
-        <v>6790494</v>
+        <v>6790465</v>
       </c>
       <c r="S337" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -36901,19 +36903,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z337" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA337" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB337" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -36928,22 +36920,22 @@
       <c r="AT337" t="inlineStr"/>
       <c r="AW337" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122973048</v>
+        <v>122971431</v>
       </c>
       <c r="B338" t="n">
-        <v>8445</v>
+        <v>78517</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -36952,41 +36944,41 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>481694</v>
+        <v>481658</v>
       </c>
       <c r="R338" t="n">
-        <v>6790479</v>
+        <v>6790494</v>
       </c>
       <c r="S338" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -37013,14 +37005,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC338" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -37035,22 +37032,22 @@
       <c r="AT338" t="inlineStr"/>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122972148</v>
+        <v>122973048</v>
       </c>
       <c r="B339" t="n">
-        <v>78782</v>
+        <v>8445</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -37059,25 +37056,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -37087,10 +37084,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>481755</v>
+        <v>481694</v>
       </c>
       <c r="R339" t="n">
-        <v>6790500</v>
+        <v>6790479</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -37127,7 +37124,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -37154,10 +37151,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122971770</v>
+        <v>122972148</v>
       </c>
       <c r="B340" t="n">
-        <v>78805</v>
+        <v>78782</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -37166,41 +37163,41 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>6434</v>
+        <v>230405</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>481677</v>
+        <v>481755</v>
       </c>
       <c r="R340" t="n">
-        <v>6790565</v>
+        <v>6790500</v>
       </c>
       <c r="S340" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -37227,19 +37224,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA340" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB340" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -37254,15 +37246,127 @@
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>122971770</v>
+      </c>
+      <c r="B341" t="n">
+        <v>78805</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr"/>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>481677</v>
+      </c>
+      <c r="R341" t="n">
+        <v>6790565</v>
+      </c>
+      <c r="S341" t="n">
+        <v>9</v>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG341" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT341" t="inlineStr"/>
+      <c r="AW341" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX340" t="inlineStr">
+      <c r="AX341" t="inlineStr">
         <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY340" t="inlineStr"/>
+      <c r="AY341" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -31085,7 +31085,7 @@
         <v>122974755</v>
       </c>
       <c r="B285" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>129963367</v>
       </c>
       <c r="B331" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -31085,7 +31085,7 @@
         <v>122974755</v>
       </c>
       <c r="B285" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -31085,7 +31085,7 @@
         <v>122974755</v>
       </c>
       <c r="B285" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -31085,7 +31085,7 @@
         <v>122974755</v>
       </c>
       <c r="B285" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>129963367</v>
       </c>
       <c r="B331" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>

--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY500"/>
+  <dimension ref="A1:AZ500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930935</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930958</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930966</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944953</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944958</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944971</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944982</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945104</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908690</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908784</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944999</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132628265</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944975</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,6 +2237,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944993</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2274,6 +2349,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944994</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2381,6 +2461,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944998</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944992</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2589,6 +2679,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930932</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2690,6 +2785,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930934</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2797,6 +2897,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944952</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2904,6 +3009,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944970</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3011,6 +3121,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944989</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3108,6 +3223,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899580</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3205,6 +3325,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907291</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3302,6 +3427,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907615</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3399,6 +3529,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907777</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3506,6 +3641,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945115</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3608,6 +3748,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122898874</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3710,6 +3855,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122898945</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3812,6 +3962,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899017</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3914,6 +4069,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899118</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4011,6 +4171,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899266</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4108,6 +4273,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899356</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4205,6 +4375,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899520</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4307,6 +4482,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122900187</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4404,6 +4584,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905474</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4501,6 +4686,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905638</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4598,6 +4788,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905650</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4695,6 +4890,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905737</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4792,6 +4992,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905837</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4889,6 +5094,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905869</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4986,6 +5196,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905949</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5083,6 +5298,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905974</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5180,6 +5400,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122905989</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5277,6 +5502,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122906123</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5374,6 +5604,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122906205</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5471,6 +5706,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122906741</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5568,6 +5808,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122906767</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5675,6 +5920,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122906779</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5782,6 +6032,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907225</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5879,6 +6134,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122906966</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5986,6 +6246,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907028</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6083,6 +6348,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907044</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6180,6 +6450,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907072</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6277,6 +6552,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907183</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6384,6 +6664,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907262</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6491,6 +6776,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907325</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6588,6 +6878,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907348</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6685,6 +6980,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907468</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6792,6 +7092,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907575</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6889,6 +7194,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907632</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6996,6 +7306,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907818</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7093,6 +7408,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907844</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7190,6 +7510,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907899</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7297,6 +7622,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907901</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7394,6 +7724,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907941</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7501,6 +7836,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907981</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7598,6 +7938,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908019</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7695,6 +8040,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908033</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7802,6 +8152,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908082</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7899,6 +8254,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908087</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8006,6 +8366,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908091</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8113,6 +8478,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908102</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8210,6 +8580,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908130</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8317,6 +8692,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908163</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8414,6 +8794,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908184</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8511,6 +8896,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908242</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8618,6 +9008,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908244</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8715,6 +9110,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908311</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8822,6 +9222,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908316</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8929,6 +9334,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908333</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9026,6 +9436,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908368</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9123,6 +9538,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908412</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9220,6 +9640,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908480</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9317,6 +9742,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908512</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9424,6 +9854,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908525</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9521,6 +9956,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908671</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9628,6 +10068,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908696</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9725,6 +10170,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908737</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9822,6 +10272,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908896</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9919,6 +10374,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908933</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10026,6 +10486,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909041</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10133,6 +10598,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909092</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10230,6 +10700,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909144</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10327,6 +10802,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909988</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10424,6 +10904,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910124</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10521,6 +11006,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910210</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10618,6 +11108,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910220</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10715,6 +11210,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910236</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10822,6 +11322,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910277</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10919,6 +11424,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910312</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11026,6 +11536,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910507</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11133,6 +11648,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910424</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11230,6 +11750,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910439</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11337,6 +11862,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910462</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11434,6 +11964,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910488</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11541,6 +12076,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910493</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11638,6 +12178,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910505</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11735,6 +12280,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910531</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11832,6 +12382,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910625</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11929,6 +12484,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910652</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12026,6 +12586,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910695</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12123,6 +12688,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910717</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12220,6 +12790,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910753</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12317,6 +12892,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910835</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12414,6 +12994,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910865</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12511,6 +13096,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910906</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12608,6 +13198,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910964</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12705,6 +13300,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911002</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12812,6 +13412,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911045</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12919,6 +13524,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911058</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13026,6 +13636,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911154</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13133,6 +13748,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911259</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13240,6 +13860,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911334</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13337,6 +13962,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122912665</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13434,6 +14064,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122912733</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13531,6 +14166,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913095</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13628,6 +14268,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913558</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13725,6 +14370,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913909</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13822,6 +14472,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913923</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13919,6 +14574,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913967</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14016,6 +14676,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914058</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14113,6 +14778,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914072</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14210,6 +14880,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914138</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14307,6 +14982,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914153</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14404,6 +15084,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914178</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14501,6 +15186,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914336</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14598,6 +15288,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914812</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14705,6 +15400,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914846</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14812,6 +15512,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914877</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14919,6 +15624,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914913</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15026,6 +15736,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914926</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15133,6 +15848,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914964</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15240,6 +15960,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915007</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15347,6 +16072,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915071</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15444,6 +16174,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915141</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15541,6 +16276,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915163</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15638,6 +16378,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915252</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15735,6 +16480,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915272</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15842,6 +16592,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915277</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15939,6 +16694,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959517</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16050,6 +16810,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959525</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16147,6 +16912,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959712</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16254,6 +17024,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959766</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16351,6 +17126,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959889</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16448,6 +17228,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122960001</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16545,6 +17330,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122960098</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16642,6 +17432,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122960241</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16739,6 +17534,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122960352</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16836,6 +17636,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122960406</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16933,6 +17738,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122960562</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17030,6 +17840,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961172</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17137,6 +17952,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961194</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17234,6 +18054,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961474</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17331,6 +18156,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961573</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17428,6 +18258,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961613</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17535,6 +18370,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961615</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17632,6 +18472,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961980</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17739,6 +18584,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962067</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17836,6 +18686,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962111</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17933,6 +18788,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962123</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18040,6 +18900,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962130</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18137,6 +19002,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962209</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18234,6 +19104,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962270</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18331,6 +19206,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122963417</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18428,6 +19308,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122963842</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18525,6 +19410,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964451</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18636,6 +19526,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964690</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18738,6 +19633,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964918</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18845,6 +19745,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964950</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18952,6 +19857,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965035</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19059,6 +19969,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965320</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19156,6 +20071,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122979174</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19268,6 +20188,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122979345</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19365,6 +20290,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123158710</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19467,6 +20397,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123158872</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19564,6 +20499,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123159161</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19661,6 +20601,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166625</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19768,6 +20713,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944937</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19875,6 +20825,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944945</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19982,6 +20937,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944950</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20089,6 +21049,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944956</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20196,6 +21161,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944957</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20303,6 +21273,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944965</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20410,6 +21385,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944967</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20517,6 +21497,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944968</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20624,6 +21609,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944973</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20731,6 +21721,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944978</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20838,6 +21833,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944988</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20945,6 +21945,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944991</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21052,6 +22057,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945092</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21159,6 +22169,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945093</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21266,6 +22281,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945098</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21373,6 +22393,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945099</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21480,6 +22505,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945100</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21587,6 +22617,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945102</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21694,6 +22729,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945105</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21801,6 +22841,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945110</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21908,6 +22953,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945117</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22015,6 +23065,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945151</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22122,6 +23177,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964962</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22229,6 +23289,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132630644</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22336,6 +23401,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908177</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22443,6 +23513,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915190</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22554,6 +23629,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915259</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22661,6 +23741,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962565</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22768,6 +23853,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944977</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22875,6 +23965,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944983</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22982,6 +24077,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944986</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23089,6 +24189,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944987</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23196,6 +24301,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944990</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23303,6 +24413,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944939</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23410,6 +24525,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944946</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23517,6 +24637,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944959</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23624,6 +24749,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945149</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23731,6 +24861,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944972</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23833,6 +24968,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899760</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23948,6 +25088,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908035</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24050,6 +25195,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964955</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24162,6 +25312,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944940</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24274,6 +25429,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944947</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24386,6 +25546,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944955</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24498,6 +25663,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944960</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24610,6 +25780,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945000</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24717,6 +25892,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899238</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24819,6 +25999,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899836</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24921,6 +26106,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913869</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25033,6 +26223,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944969</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25150,6 +26345,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944976</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25267,6 +26467,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944979</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25384,6 +26589,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944996</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25501,6 +26711,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945101</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25603,6 +26818,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911070</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25718,6 +26938,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913380</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25820,6 +27045,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914046</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25935,6 +27165,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914997</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26050,6 +27285,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915025</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26162,6 +27402,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915104</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26264,6 +27509,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122917610</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -26381,6 +27631,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961517</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -26501,6 +27756,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964814</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26613,6 +27873,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944954</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26725,6 +27990,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945107</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26846,6 +28116,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914542</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26953,6 +28228,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945096</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27060,6 +28340,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122907535</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27167,6 +28452,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908063</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27274,6 +28564,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908121</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27381,6 +28676,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908196</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27488,6 +28788,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908658</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -27585,6 +28890,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908892</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -27702,6 +29012,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909048</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27809,6 +29124,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909085</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27916,6 +29236,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910464</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28033,6 +29358,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961952</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28145,6 +29475,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122962208</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -28242,6 +29577,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965139</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -28354,6 +29694,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944936</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -28466,6 +29811,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944938</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -28578,6 +29928,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944943</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -28690,6 +30045,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944948</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -28802,6 +30162,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944949</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -28914,6 +30279,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944951</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29026,6 +30396,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944962</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -29138,6 +30513,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944963</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -29250,6 +30630,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944964</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -29362,6 +30747,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944966</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -29474,6 +30864,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944974</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -29586,6 +30981,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944980</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -29698,6 +31098,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944997</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -29810,6 +31215,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945095</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -29922,6 +31332,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945097</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -30034,6 +31449,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945103</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -30146,6 +31566,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945116</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -30258,6 +31683,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945118</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -30365,6 +31795,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945152</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -30467,6 +31902,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125314704</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -30574,6 +32014,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908588</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -30681,6 +32126,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122960658</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -30788,6 +32238,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944941</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -30895,6 +32350,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944961</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31002,6 +32462,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944981</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -31109,6 +32574,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944985</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -31216,6 +32686,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945106</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -31324,6 +32799,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945109</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -31430,6 +32910,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930986</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -31536,6 +33021,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930987</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -31643,6 +33133,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945129</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -31750,6 +33245,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913735</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -31857,6 +33357,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945137</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -31964,6 +33469,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945130</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32075,6 +33585,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128914354</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -32186,6 +33701,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128914862</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -32293,6 +33813,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945119</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -32400,6 +33925,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945126</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -32507,6 +34037,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911585</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -32614,6 +34149,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911477</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -32721,6 +34261,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911564</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -32828,6 +34373,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911611</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -32935,6 +34485,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911922</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33042,6 +34597,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122912740</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -33149,6 +34709,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913744</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -33256,6 +34821,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913854</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -33363,6 +34933,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913871</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -33470,6 +35045,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913893</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -33577,6 +35157,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913962</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -33684,6 +35269,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913918</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -33791,6 +35381,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913997</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -33898,6 +35493,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914120</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34005,6 +35605,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914177</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34112,6 +35717,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914257</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -34219,6 +35829,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914329</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -34326,6 +35941,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914370</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -34433,6 +36053,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914379</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -34540,6 +36165,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914414</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -34647,6 +36277,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914420</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -34754,6 +36389,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914493</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -34851,6 +36491,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915404</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -34948,6 +36593,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915451</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -35045,6 +36695,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915490</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -35142,6 +36797,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915538</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -35239,6 +36899,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915714</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -35336,6 +37001,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915813</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -35433,6 +37103,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915850</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -35530,6 +37205,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915881</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -35627,6 +37307,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915938</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -35724,6 +37409,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916013</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -35821,6 +37511,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916074</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -35918,6 +37613,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916175</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -36015,6 +37715,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916212</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -36112,6 +37817,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916304</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -36209,6 +37919,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916342</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -36306,6 +38021,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916381</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -36403,6 +38123,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916548</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -36500,6 +38225,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916689</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -36597,6 +38327,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916728</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -36694,6 +38429,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916802</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -36796,6 +38536,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916963</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -36893,6 +38638,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916996</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -36990,6 +38740,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122917054</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -37087,6 +38842,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965617</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -37194,6 +38954,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965694</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -37301,6 +39066,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965760</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -37403,6 +39173,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965887</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -37510,6 +39285,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122966180</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -37612,6 +39392,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122966647</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -37719,6 +39504,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122966701</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -37816,6 +39606,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967224</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -37923,6 +39718,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967445</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -38030,6 +39830,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967506</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -38137,6 +39942,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967530</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -38244,6 +40054,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967764</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -38341,6 +40156,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967817</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -38438,6 +40258,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967897</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -38540,6 +40365,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968048</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -38647,6 +40477,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968051</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -38754,6 +40589,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968065</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -38851,6 +40691,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968089</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -38958,6 +40803,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968097</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -39065,6 +40915,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968143</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -39167,6 +41022,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968168</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -39274,6 +41134,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968384</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -39386,6 +41251,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968517</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -39493,6 +41363,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968533</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -39595,6 +41470,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968541</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -39702,6 +41582,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968577</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -39814,6 +41699,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968666</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -39921,6 +41811,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968705</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -40018,6 +41913,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968715</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -40125,6 +42025,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968724</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -40232,6 +42137,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968760</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -40348,6 +42258,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968960</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -40450,6 +42365,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969047</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -40552,6 +42472,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969543</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -40649,6 +42574,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969601</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -40756,6 +42686,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969836</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -40863,6 +42798,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969887</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -40970,6 +42910,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970062</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -41067,6 +43012,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970152</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -41174,6 +43124,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970156</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -41271,6 +43226,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970196</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -41378,6 +43338,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970211</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -41480,6 +43445,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970333</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -41587,6 +43557,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970352</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -41694,6 +43669,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122972089</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -41791,6 +43771,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122972633</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -41888,6 +43873,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973297</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -41995,6 +43985,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973309</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -42102,6 +44097,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973371</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -42209,6 +44209,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973389</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -42306,6 +44311,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973404</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -42413,6 +44423,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973627</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -42510,6 +44525,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973653</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -42622,6 +44642,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973693</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -42719,6 +44744,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973700</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -42816,6 +44846,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973912</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -42922,6 +44957,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122974755</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -43019,6 +45059,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122974864</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -43131,6 +45176,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975021</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -43233,6 +45283,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975072</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -43335,6 +45390,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975172</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -43442,6 +45502,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975198</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -43549,6 +45614,11 @@
         </is>
       </c>
       <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975263</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -43646,6 +45716,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975272</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -43753,6 +45828,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975396</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -43855,6 +45935,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975494</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -43952,6 +46037,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975526</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -44059,6 +46149,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975535</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -44171,6 +46266,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975641</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -44278,6 +46378,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975765</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -44380,6 +46485,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975861</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -44487,6 +46597,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976484</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -44594,6 +46709,11 @@
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976543</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -44701,6 +46821,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976607</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -44803,6 +46928,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976610</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -44910,6 +47040,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976633</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -45022,6 +47157,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976687</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -45124,6 +47264,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976875</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -45226,6 +47371,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122977806</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -45333,6 +47483,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122977907</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -45435,6 +47590,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122977930</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -45542,6 +47702,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122977985</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -45649,6 +47814,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122978123</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -45751,6 +47921,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122978156</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -45863,6 +48038,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122979110</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -45970,6 +48150,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945120</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -46077,6 +48262,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945121</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -46184,6 +48374,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945124</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -46291,6 +48486,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945127</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -46398,6 +48598,11 @@
         </is>
       </c>
       <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945131</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -46505,6 +48710,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945139</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -46612,6 +48822,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945142</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -46719,6 +48934,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965948</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -46826,6 +49046,11 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122966313</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -46933,6 +49158,11 @@
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968130</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -47040,6 +49270,11 @@
         </is>
       </c>
       <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969800</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -47147,6 +49382,11 @@
         </is>
       </c>
       <c r="AY448" t="inlineStr"/>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970092</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -47254,6 +49494,11 @@
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122971770</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -47361,6 +49606,11 @@
         </is>
       </c>
       <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945140</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -47468,6 +49718,11 @@
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911766</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -47575,6 +49830,11 @@
         </is>
       </c>
       <c r="AY452" t="inlineStr"/>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122971431</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -47682,6 +49942,11 @@
         </is>
       </c>
       <c r="AY453" t="inlineStr"/>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945122</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -47789,6 +50054,11 @@
         </is>
       </c>
       <c r="AY454" t="inlineStr"/>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945135</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -47896,6 +50166,11 @@
         </is>
       </c>
       <c r="AY455" t="inlineStr"/>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945136</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -48003,6 +50278,11 @@
         </is>
       </c>
       <c r="AY456" t="inlineStr"/>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945138</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -48105,6 +50385,11 @@
         </is>
       </c>
       <c r="AY457" t="inlineStr"/>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916858</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -48217,6 +50502,11 @@
         </is>
       </c>
       <c r="AY458" t="inlineStr"/>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965865</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -48319,6 +50609,11 @@
         </is>
       </c>
       <c r="AY459" t="inlineStr"/>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970459</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -48416,6 +50711,11 @@
         </is>
       </c>
       <c r="AY460" t="inlineStr"/>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975234</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -48518,6 +50818,11 @@
         </is>
       </c>
       <c r="AY461" t="inlineStr"/>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976204</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -48620,6 +50925,11 @@
         </is>
       </c>
       <c r="AY462" t="inlineStr"/>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122976647</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -48725,6 +51035,11 @@
         </is>
       </c>
       <c r="AY463" t="inlineStr"/>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129963367</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -48822,6 +51137,11 @@
         </is>
       </c>
       <c r="AY464" t="inlineStr"/>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916590</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -48937,6 +51257,11 @@
         </is>
       </c>
       <c r="AY465" t="inlineStr"/>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122977167</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -49054,6 +51379,11 @@
         </is>
       </c>
       <c r="AY466" t="inlineStr"/>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945128</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -49166,6 +51496,11 @@
         </is>
       </c>
       <c r="AY467" t="inlineStr"/>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945132</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -49281,6 +51616,11 @@
         </is>
       </c>
       <c r="AY468" t="inlineStr"/>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913790</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -49393,6 +51733,11 @@
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122974049</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -49505,6 +51850,11 @@
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122978194</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -49617,6 +51967,11 @@
         </is>
       </c>
       <c r="AY471" t="inlineStr"/>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945125</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -49729,6 +52084,11 @@
         </is>
       </c>
       <c r="AY472" t="inlineStr"/>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128914266</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -49841,6 +52201,11 @@
         </is>
       </c>
       <c r="AY473" t="inlineStr"/>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128914416</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -49953,6 +52318,11 @@
         </is>
       </c>
       <c r="AY474" t="inlineStr"/>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128914529</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -50060,6 +52430,11 @@
         </is>
       </c>
       <c r="AY475" t="inlineStr"/>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914523</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -50172,6 +52547,11 @@
         </is>
       </c>
       <c r="AY476" t="inlineStr"/>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122967628</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -50279,6 +52659,11 @@
         </is>
       </c>
       <c r="AY477" t="inlineStr"/>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914092</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -50391,6 +52776,11 @@
         </is>
       </c>
       <c r="AY478" t="inlineStr"/>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122965792</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -50503,6 +52893,11 @@
         </is>
       </c>
       <c r="AY479" t="inlineStr"/>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968198</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -50600,6 +52995,11 @@
         </is>
       </c>
       <c r="AY480" t="inlineStr"/>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968800</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -50712,6 +53112,11 @@
         </is>
       </c>
       <c r="AY481" t="inlineStr"/>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122970166</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -50809,6 +53214,11 @@
         </is>
       </c>
       <c r="AY482" t="inlineStr"/>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122971698</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -50921,6 +53331,11 @@
         </is>
       </c>
       <c r="AY483" t="inlineStr"/>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122971852</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -51033,6 +53448,11 @@
         </is>
       </c>
       <c r="AY484" t="inlineStr"/>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122972025</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -51135,6 +53555,11 @@
         </is>
       </c>
       <c r="AY485" t="inlineStr"/>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122973048</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -51242,6 +53667,11 @@
         </is>
       </c>
       <c r="AY486" t="inlineStr"/>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122975322</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -51354,6 +53784,11 @@
         </is>
       </c>
       <c r="AY487" t="inlineStr"/>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945147</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -51461,6 +53896,11 @@
         </is>
       </c>
       <c r="AY488" t="inlineStr"/>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915373</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -51568,6 +54008,11 @@
         </is>
       </c>
       <c r="AY489" t="inlineStr"/>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945145</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -51675,6 +54120,11 @@
         </is>
       </c>
       <c r="AY490" t="inlineStr"/>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945148</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -51782,6 +54232,11 @@
         </is>
       </c>
       <c r="AY491" t="inlineStr"/>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945144</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -51889,6 +54344,11 @@
         </is>
       </c>
       <c r="AY492" t="inlineStr"/>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945134</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -51996,6 +54456,11 @@
         </is>
       </c>
       <c r="AY493" t="inlineStr"/>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122974351</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -52103,6 +54568,11 @@
         </is>
       </c>
       <c r="AY494" t="inlineStr"/>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945123</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -52210,6 +54680,11 @@
         </is>
       </c>
       <c r="AY495" t="inlineStr"/>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945141</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -52317,6 +54792,11 @@
         </is>
       </c>
       <c r="AY496" t="inlineStr"/>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945143</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -52424,6 +54904,11 @@
         </is>
       </c>
       <c r="AY497" t="inlineStr"/>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945146</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -52526,6 +55011,11 @@
         </is>
       </c>
       <c r="AY498" t="inlineStr"/>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969848</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -52628,6 +55118,11 @@
         </is>
       </c>
       <c r="AY499" t="inlineStr"/>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122969981</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -52730,8 +55225,514 @@
         </is>
       </c>
       <c r="AY500" t="inlineStr"/>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122972148</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7507-2025 artfynd.xlsx
+++ b/artfynd/A 7507-2025 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>134944953</v>
       </c>
       <c r="B5" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>134944958</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>134944971</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>134944982</v>
       </c>
       <c r="B8" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>134945104</v>
       </c>
       <c r="B9" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>134944999</v>
       </c>
       <c r="B12" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>134944975</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>134944993</v>
       </c>
       <c r="B15" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>134944994</v>
       </c>
       <c r="B16" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>134944998</v>
       </c>
       <c r="B17" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>134944992</v>
       </c>
       <c r="B18" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>134944952</v>
       </c>
       <c r="B21" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>134944970</v>
       </c>
       <c r="B22" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>134944989</v>
       </c>
       <c r="B23" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>134945115</v>
       </c>
       <c r="B28" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>134944937</v>
       </c>
       <c r="B190" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>134944945</v>
       </c>
       <c r="B191" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>134944950</v>
       </c>
       <c r="B192" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>134944956</v>
       </c>
       <c r="B193" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>134944957</v>
       </c>
       <c r="B194" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>134944965</v>
       </c>
       <c r="B195" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>134944967</v>
       </c>
       <c r="B196" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>134944968</v>
       </c>
       <c r="B197" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>134944973</v>
       </c>
       <c r="B198" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>134944978</v>
       </c>
       <c r="B199" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>134944988</v>
       </c>
       <c r="B200" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>134944991</v>
       </c>
       <c r="B201" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>134945092</v>
       </c>
       <c r="B202" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>134945093</v>
       </c>
       <c r="B203" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>134945098</v>
       </c>
       <c r="B204" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>134945099</v>
       </c>
       <c r="B205" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>134945100</v>
       </c>
       <c r="B206" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>134945102</v>
       </c>
       <c r="B207" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>134945105</v>
       </c>
       <c r="B208" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>134945110</v>
       </c>
       <c r="B209" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>134945117</v>
       </c>
       <c r="B210" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>134945151</v>
       </c>
       <c r="B211" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>134944977</v>
       </c>
       <c r="B218" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>134944983</v>
       </c>
       <c r="B219" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>134944986</v>
       </c>
       <c r="B220" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>134944987</v>
       </c>
       <c r="B221" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>134944990</v>
       </c>
       <c r="B222" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>134944939</v>
       </c>
       <c r="B223" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>134944946</v>
       </c>
       <c r="B224" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>134944959</v>
       </c>
       <c r="B225" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>134945149</v>
       </c>
       <c r="B226" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>134944972</v>
       </c>
       <c r="B227" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>134944940</v>
       </c>
       <c r="B231" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>134944947</v>
       </c>
       <c r="B232" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>134944955</v>
       </c>
       <c r="B233" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>134944960</v>
       </c>
       <c r="B234" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>134945000</v>
       </c>
       <c r="B235" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>134944969</v>
       </c>
       <c r="B239" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>134944976</v>
       </c>
       <c r="B240" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>134944979</v>
       </c>
       <c r="B241" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>134944996</v>
       </c>
       <c r="B242" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>134945101</v>
       </c>
       <c r="B243" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>134944954</v>
       </c>
       <c r="B253" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>134945107</v>
       </c>
       <c r="B254" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>134945096</v>
       </c>
       <c r="B256" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>134944936</v>
       </c>
       <c r="B269" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>134944938</v>
       </c>
       <c r="B270" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>134944943</v>
       </c>
       <c r="B271" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>134944948</v>
       </c>
       <c r="B272" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>134944949</v>
       </c>
       <c r="B273" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>134944951</v>
       </c>
       <c r="B274" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>134944962</v>
       </c>
       <c r="B275" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>134944963</v>
       </c>
       <c r="B276" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>134944964</v>
       </c>
       <c r="B277" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>134944966</v>
       </c>
       <c r="B278" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>134944974</v>
       </c>
       <c r="B279" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>134944980</v>
       </c>
       <c r="B280" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>134944997</v>
       </c>
       <c r="B281" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>134945095</v>
       </c>
       <c r="B282" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>134945097</v>
       </c>
       <c r="B283" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>134945103</v>
       </c>
       <c r="B284" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>134945116</v>
       </c>
       <c r="B285" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>134945118</v>
       </c>
       <c r="B286" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>134945152</v>
       </c>
       <c r="B287" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>134944941</v>
       </c>
       <c r="B291" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>134944961</v>
       </c>
       <c r="B292" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>134944981</v>
       </c>
       <c r="B293" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>134944985</v>
       </c>
       <c r="B294" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>134945106</v>
       </c>
       <c r="B295" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>134945109</v>
       </c>
       <c r="B296" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>134945129</v>
       </c>
       <c r="B299" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>134945137</v>
       </c>
       <c r="B301" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>134945130</v>
       </c>
       <c r="B302" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>134945119</v>
       </c>
       <c r="B305" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>134945126</v>
       </c>
       <c r="B306" t="n">
-        <v>93309</v>
+        <v>93351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>134945120</v>
       </c>
       <c r="B437" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>134945121</v>
       </c>
       <c r="B438" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -48273,7 +48273,7 @@
         <v>134945124</v>
       </c>
       <c r="B439" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>134945127</v>
       </c>
       <c r="B440" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -48497,7 +48497,7 @@
         <v>134945131</v>
       </c>
       <c r="B441" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>134945139</v>
       </c>
       <c r="B442" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>134945142</v>
       </c>
       <c r="B443" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>134945140</v>
       </c>
       <c r="B450" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>134945122</v>
       </c>
       <c r="B453" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>134945135</v>
       </c>
       <c r="B454" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>134945136</v>
       </c>
       <c r="B455" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>134945138</v>
       </c>
       <c r="B456" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>134945128</v>
       </c>
       <c r="B466" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>134945132</v>
       </c>
       <c r="B467" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>134945125</v>
       </c>
       <c r="B471" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -53678,7 +53678,7 @@
         <v>134945147</v>
       </c>
       <c r="B487" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>134945145</v>
       </c>
       <c r="B489" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>134945148</v>
       </c>
       <c r="B490" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>134945144</v>
       </c>
       <c r="B491" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>134945134</v>
       </c>
       <c r="B492" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>134945123</v>
       </c>
       <c r="B494" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>134945141</v>
       </c>
       <c r="B495" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>134945143</v>
       </c>
       <c r="B496" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>134945146</v>
       </c>
       <c r="B497" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
